--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="C2" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="D2" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I2" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="C2" t="n">
+      <c r="J2" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="D2" t="n">
+      <c r="K2" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="E2" t="n">
+      <c r="L2" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.0024</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>70.06999999999999</v>
-      </c>
-      <c r="J2" t="n">
-        <v>70.06999999999999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>70.06999999999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>70.06999999999999</v>
-      </c>
       <c r="M2" t="n">
-        <v>70.06999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>70.06999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>70.06999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -703,72 +703,82 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.31</v>
+        <v>66.25</v>
       </c>
       <c r="C3" t="n">
-        <v>70.95</v>
+        <v>66.25</v>
       </c>
       <c r="D3" t="n">
-        <v>68.76000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="E3" t="n">
-        <v>70.7</v>
+        <v>66.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>-4.44</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>69.90000000000001</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>69.90000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>69.90000000000001</v>
+        <v>70.28</v>
       </c>
       <c r="M3" t="n">
-        <v>69.90000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>69.90000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="O3" t="n">
-        <v>69.90000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
@@ -787,82 +797,72 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="C4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="D4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="E4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.44</v>
+        <v>-0.73</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>66.56999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="J4" t="n">
-        <v>68.93000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="K4" t="n">
-        <v>69.59999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="L4" t="n">
-        <v>70.28</v>
+        <v>66.25</v>
       </c>
       <c r="M4" t="n">
-        <v>71.79000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="N4" t="n">
-        <v>73.31</v>
+        <v>66.25</v>
       </c>
       <c r="O4" t="n">
-        <v>73.14</v>
+        <v>66.25</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -893,7 +893,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -903,50 +903,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="E5" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.0535</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I5" t="n">
         <v>65.53</v>
       </c>
-      <c r="C5" t="n">
+      <c r="J5" t="n">
         <v>65.53</v>
       </c>
-      <c r="D5" t="n">
+      <c r="K5" t="n">
         <v>65.53</v>
       </c>
-      <c r="E5" t="n">
+      <c r="L5" t="n">
         <v>65.53</v>
       </c>
-      <c r="F5" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="J5" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>66.25</v>
-      </c>
       <c r="M5" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="N5" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="O5" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -977,7 +977,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -987,50 +987,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.95</v>
+        <v>59.39</v>
       </c>
       <c r="C6" t="n">
-        <v>62.02</v>
+        <v>59.51</v>
       </c>
       <c r="D6" t="n">
-        <v>61.95</v>
+        <v>57.25</v>
       </c>
       <c r="E6" t="n">
-        <v>62.02</v>
+        <v>58.05</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.51</v>
+        <v>-3.97</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.064</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
-        <v>65.53</v>
+        <v>61.88</v>
       </c>
       <c r="J6" t="n">
-        <v>65.53</v>
+        <v>61.97</v>
       </c>
       <c r="K6" t="n">
-        <v>65.53</v>
+        <v>61.99</v>
       </c>
       <c r="L6" t="n">
-        <v>65.53</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
-        <v>65.53</v>
+        <v>62.06</v>
       </c>
       <c r="N6" t="n">
-        <v>65.53</v>
+        <v>62.11</v>
       </c>
       <c r="O6" t="n">
-        <v>65.53</v>
+        <v>62.09</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1061,7 +1061,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1071,69 +1071,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.39</v>
+        <v>58.38</v>
       </c>
       <c r="C7" t="n">
-        <v>59.51</v>
+        <v>58.38</v>
       </c>
       <c r="D7" t="n">
-        <v>57.25</v>
+        <v>58.35</v>
       </c>
       <c r="E7" t="n">
-        <v>58.05</v>
+        <v>58.35</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.97</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.0051</v>
       </c>
       <c r="H7" t="n">
-        <v>2.26</v>
+        <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>61.88</v>
+        <v>54.99</v>
       </c>
       <c r="J7" t="n">
-        <v>61.97</v>
+        <v>55.62</v>
       </c>
       <c r="K7" t="n">
-        <v>61.99</v>
+        <v>56.92</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>58.22</v>
       </c>
       <c r="M7" t="n">
-        <v>62.06</v>
+        <v>59.18</v>
       </c>
       <c r="N7" t="n">
-        <v>62.11</v>
+        <v>60.15</v>
       </c>
       <c r="O7" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>61.78</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1145,60 +1139,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I8" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J8" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L8" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M8" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N8" t="n">
         <v>58.38</v>
       </c>
-      <c r="C8" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D8" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E8" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I8" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J8" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K8" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L8" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M8" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N8" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O8" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1209,111 +1207,113 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C9" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D9" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E9" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F9" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I9" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J9" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K9" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L9" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M9" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N9" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O9" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>59.24</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1321,134 +1321,138 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C10" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D10" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E10" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H10" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I10" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J10" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K10" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L10" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M10" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N10" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O10" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C11" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D11" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E11" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H11" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I11" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J11" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K11" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L11" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M11" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N11" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O11" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1461,82 +1465,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C12" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D12" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E12" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I12" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J12" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K12" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L12" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M12" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N12" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O12" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1544,18 +1544,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1563,7 +1563,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1577,50 +1577,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C13" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D13" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E13" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H13" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J13" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K13" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L13" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M13" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N13" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O13" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1631,7 +1631,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1647,7 +1647,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1661,69 +1661,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C14" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D14" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E14" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F14" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H14" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J14" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K14" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L14" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M14" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N14" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O14" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>63.6</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1731,73 +1735,69 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C15" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D15" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E15" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H15" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J15" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K15" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L15" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M15" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N15" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O15" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -1805,7 +1805,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1819,7 +1819,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1829,134 +1829,136 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C16" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D16" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E16" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I16" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J16" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K16" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L16" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M16" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N16" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O16" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C17" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D17" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E17" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F17" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I17" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J17" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K17" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L17" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M17" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N17" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O17" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1969,93 +1971,95 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C18" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D18" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E18" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H18" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J18" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K18" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L18" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M18" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N18" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O18" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>60.97</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2067,249 +2071,241 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C19" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D19" t="n">
         <v>57.51</v>
       </c>
       <c r="E19" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H19" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I19" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J19" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K19" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L19" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M19" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N19" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O19" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C20" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D20" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E20" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F20" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H20" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I20" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J20" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K20" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L20" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M20" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N20" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O20" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C21" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D21" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E21" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H21" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J21" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K21" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L21" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M21" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N21" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O21" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2323,7 +2319,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2333,222 +2329,228 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C22" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D22" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E22" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H22" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J22" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K22" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L22" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M22" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N22" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O22" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C23" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D23" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E23" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H23" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J23" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K23" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L23" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M23" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N23" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O23" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C24" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D24" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E24" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H24" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I24" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J24" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K24" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L24" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M24" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N24" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O24" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2559,82 +2561,80 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C25" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D25" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E25" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F25" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H25" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I25" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J25" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K25" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L25" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M25" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N25" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O25" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2645,27 +2645,23 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2675,69 +2671,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C26" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D26" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E26" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F26" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H26" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J26" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K26" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L26" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M26" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N26" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O26" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>60.65</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2765,210 +2765,210 @@
         <v>58.66</v>
       </c>
       <c r="D27" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E27" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H27" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J27" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K27" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L27" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M27" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N27" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O27" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F28" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J28" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K28" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L28" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M28" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N28" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O28" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>58.66</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O29" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2999,7 +2999,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3009,83 +3009,85 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O30" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3093,63 +3095,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C31" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D31" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E31" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I31" t="n">
         <v>57.86</v>
       </c>
-      <c r="C31" t="n">
+      <c r="J31" t="n">
         <v>57.86</v>
       </c>
-      <c r="D31" t="n">
+      <c r="K31" t="n">
         <v>57.86</v>
       </c>
-      <c r="E31" t="n">
+      <c r="L31" t="n">
         <v>57.86</v>
       </c>
-      <c r="F31" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M31" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N31" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O31" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3169,154 +3175,148 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C32" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D32" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E32" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F32" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H32" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I32" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J32" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K32" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L32" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M32" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N32" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O32" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C33" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D33" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E33" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H33" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I33" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J33" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K33" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L33" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M33" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N33" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O33" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3324,14 +3324,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3343,65 +3341,65 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C34" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D34" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E34" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F34" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H34" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I34" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J34" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K34" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L34" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M34" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N34" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O34" t="n">
         <v>57.93</v>
       </c>
-      <c r="M34" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N34" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O34" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
@@ -3413,76 +3411,78 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C35" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D35" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E35" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F35" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H35" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I35" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J35" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K35" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L35" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M35" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N35" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O35" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3493,7 +3493,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3503,17 +3503,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3523,81 +3521,83 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C36" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D36" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E36" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F36" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H36" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I36" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J36" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K36" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L36" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M36" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N36" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O36" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>62.8</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3605,83 +3605,83 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C37" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D37" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E37" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H37" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I37" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J37" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K37" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L37" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M37" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N37" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O37" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3689,50 +3689,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C38" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D38" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E38" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F38" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H38" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J38" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K38" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L38" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M38" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N38" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O38" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3743,7 +3743,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3755,15 +3755,13 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3773,50 +3771,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C39" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D39" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E39" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F39" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J39" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M39" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O39" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3829,76 +3827,76 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C40" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E40" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J40" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L40" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O40" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3911,76 +3909,78 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C41" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D41" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E41" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F41" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I41" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K41" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M41" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O41" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3988,83 +3988,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H42" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J42" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K42" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L42" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N42" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4072,86 +4072,88 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C43" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D43" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I43" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C43" t="n">
+      <c r="J43" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D43" t="n">
+      <c r="K43" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E43" t="n">
+      <c r="L43" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J43" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K43" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L43" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M43" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
@@ -4159,7 +4161,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4171,7 +4173,7 @@
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V43" s="8" t="inlineStr">
@@ -4179,7 +4181,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4189,85 +4191,83 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>65.25</v>
       </c>
       <c r="C44" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D44" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E44" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F44" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H44" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I44" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J44" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N44" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O44" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4275,134 +4275,136 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C45" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E45" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H45" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I45" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J45" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K45" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L45" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O45" t="n">
-        <v>67</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C46" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D46" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D46" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E46" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F46" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H46" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I46" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J46" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K46" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L46" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M46" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O46" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4413,82 +4415,76 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F47" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H47" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I47" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J47" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L47" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N47" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O47" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4499,7 +4495,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4515,7 +4511,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4525,50 +4521,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H48" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J48" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L48" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M48" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N48" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O48" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4576,18 +4572,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4595,60 +4591,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C49" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D49" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E49" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I49" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J49" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K49" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L49" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N49" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4658,81 +4658,85 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C50" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D50" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H50" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I50" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K50" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L50" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M50" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N50" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4742,85 +4746,81 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H51" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J51" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K51" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L51" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O51" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4828,96 +4828,100 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C52" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D52" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E52" t="n">
+        <v>67</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I52" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C52" t="n">
+      <c r="J52" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D52" t="n">
+      <c r="K52" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E52" t="n">
+      <c r="L52" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F52" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J52" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K52" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L52" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M52" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4927,173 +4931,169 @@
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H53" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I53" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J53" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K53" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L53" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O53" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
+        <v>76.09</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E54" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H54" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I54" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L54" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M54" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N54" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O54" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>68.52</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5105,7 +5105,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5115,69 +5115,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C55" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D55" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E55" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H55" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I55" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J55" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K55" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L55" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O55" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>69.56</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5189,60 +5183,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C56" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D56" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E56" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F56" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H56" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I56" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J56" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K56" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L56" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O56" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5255,76 +5253,78 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C57" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F57" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H57" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I57" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J57" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K57" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M57" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O57" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5332,83 +5332,83 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C58" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D58" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H58" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I58" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J58" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M58" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N58" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O58" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5416,14 +5416,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5435,64 +5433,64 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C59" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D59" t="n">
         <v>66.3</v>
       </c>
-      <c r="D59" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E59" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F59" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I59" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J59" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K59" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L59" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M59" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O59" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5503,111 +5501,113 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C60" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D60" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E60" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F60" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H60" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I60" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J60" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N60" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O60" t="n">
-        <v>67</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>69.91</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5615,206 +5615,122 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64.19</v>
+        <v>64.14</v>
       </c>
       <c r="C61" t="n">
-        <v>64.41</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>64.14</v>
+        <v>63.15</v>
       </c>
       <c r="E61" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I61" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J61" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K61" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L61" t="n">
         <v>64.28</v>
       </c>
-      <c r="F61" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I61" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J61" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K61" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L61" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M61" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N61" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O61" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="C62" t="n">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="D62" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="E62" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0141</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="I62" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="J62" t="n">
-        <v>64.02</v>
-      </c>
-      <c r="K62" t="n">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="L62" t="n">
-        <v>64.28</v>
-      </c>
-      <c r="M62" t="n">
-        <v>64.42</v>
-      </c>
-      <c r="N62" t="n">
-        <v>64.55</v>
-      </c>
-      <c r="O62" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>60.48</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>62.87</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>63.85</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>64.84</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>66.52</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>68.20999999999999</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>68.48999999999999</v>
       </c>
     </row>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70.31</v>
+        <v>66.25</v>
       </c>
       <c r="C2" t="n">
-        <v>70.95</v>
+        <v>66.25</v>
       </c>
       <c r="D2" t="n">
-        <v>68.76000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="E2" t="n">
-        <v>70.7</v>
+        <v>66.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>-4.44</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>69.90000000000001</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>69.90000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>69.90000000000001</v>
+        <v>70.28</v>
       </c>
       <c r="M2" t="n">
-        <v>69.90000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>69.90000000000001</v>
+        <v>73.31</v>
       </c>
       <c r="O2" t="n">
-        <v>69.90000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -703,82 +703,72 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="C3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="D3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="E3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.44</v>
+        <v>-0.73</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>66.56999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="J3" t="n">
-        <v>68.93000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="K3" t="n">
-        <v>69.59999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="L3" t="n">
-        <v>70.28</v>
+        <v>66.25</v>
       </c>
       <c r="M3" t="n">
-        <v>71.79000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="N3" t="n">
-        <v>73.31</v>
+        <v>66.25</v>
       </c>
       <c r="O3" t="n">
-        <v>73.14</v>
+        <v>66.25</v>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
@@ -795,7 +785,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -809,7 +799,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -819,50 +809,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="D4" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.0535</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I4" t="n">
         <v>65.53</v>
       </c>
-      <c r="C4" t="n">
+      <c r="J4" t="n">
         <v>65.53</v>
       </c>
-      <c r="D4" t="n">
+      <c r="K4" t="n">
         <v>65.53</v>
       </c>
-      <c r="E4" t="n">
+      <c r="L4" t="n">
         <v>65.53</v>
       </c>
-      <c r="F4" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="J4" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="K4" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>66.25</v>
-      </c>
       <c r="M4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="N4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="O4" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
@@ -879,7 +869,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -893,7 +883,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -903,50 +893,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.95</v>
+        <v>59.39</v>
       </c>
       <c r="C5" t="n">
-        <v>62.02</v>
+        <v>59.51</v>
       </c>
       <c r="D5" t="n">
-        <v>61.95</v>
+        <v>57.25</v>
       </c>
       <c r="E5" t="n">
-        <v>62.02</v>
+        <v>58.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.51</v>
+        <v>-3.97</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.064</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>65.53</v>
+        <v>61.88</v>
       </c>
       <c r="J5" t="n">
-        <v>65.53</v>
+        <v>61.97</v>
       </c>
       <c r="K5" t="n">
-        <v>65.53</v>
+        <v>61.99</v>
       </c>
       <c r="L5" t="n">
-        <v>65.53</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>65.53</v>
+        <v>62.06</v>
       </c>
       <c r="N5" t="n">
-        <v>65.53</v>
+        <v>62.11</v>
       </c>
       <c r="O5" t="n">
-        <v>65.53</v>
+        <v>62.09</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -963,7 +953,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -977,7 +967,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -987,69 +977,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.39</v>
+        <v>58.38</v>
       </c>
       <c r="C6" t="n">
-        <v>59.51</v>
+        <v>58.38</v>
       </c>
       <c r="D6" t="n">
-        <v>57.25</v>
+        <v>58.35</v>
       </c>
       <c r="E6" t="n">
-        <v>58.05</v>
+        <v>58.35</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.97</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.0051</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26</v>
+        <v>0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>61.88</v>
+        <v>54.99</v>
       </c>
       <c r="J6" t="n">
-        <v>61.97</v>
+        <v>55.62</v>
       </c>
       <c r="K6" t="n">
-        <v>61.99</v>
+        <v>56.92</v>
       </c>
       <c r="L6" t="n">
-        <v>62</v>
+        <v>58.22</v>
       </c>
       <c r="M6" t="n">
-        <v>62.06</v>
+        <v>59.18</v>
       </c>
       <c r="N6" t="n">
-        <v>62.11</v>
+        <v>60.15</v>
       </c>
       <c r="O6" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>61.78</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1061,60 +1045,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C7" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E7" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I7" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N7" t="n">
         <v>58.38</v>
       </c>
-      <c r="C7" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D7" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E7" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I7" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J7" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K7" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L7" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M7" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N7" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O7" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1125,111 +1113,113 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C8" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D8" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E8" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F8" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I8" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J8" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K8" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L8" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M8" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N8" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O8" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>59.24</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1237,134 +1227,138 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C9" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D9" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E9" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H9" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I9" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J9" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K9" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L9" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M9" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N9" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O9" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C10" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D10" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E10" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H10" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I10" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J10" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K10" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L10" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M10" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N10" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O10" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1377,82 +1371,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C11" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D11" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E11" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F11" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I11" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J11" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K11" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L11" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M11" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N11" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O11" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1460,18 +1450,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1479,7 +1469,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1493,50 +1483,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C12" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D12" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E12" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H12" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I12" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J12" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K12" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L12" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M12" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N12" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O12" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1547,7 +1537,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1563,7 +1553,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1577,69 +1567,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C13" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D13" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E13" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F13" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H13" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J13" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K13" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L13" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M13" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N13" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O13" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>63.6</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1647,73 +1641,69 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C14" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D14" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E14" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H14" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I14" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J14" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K14" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L14" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M14" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N14" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O14" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -1721,7 +1711,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1735,7 +1725,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1745,134 +1735,136 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C15" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D15" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E15" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J15" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K15" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L15" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M15" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N15" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O15" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C16" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D16" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E16" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F16" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J16" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K16" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L16" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M16" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N16" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O16" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1885,93 +1877,95 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C17" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D17" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E17" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H17" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J17" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K17" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L17" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M17" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N17" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O17" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>60.97</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1983,249 +1977,241 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C18" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D18" t="n">
         <v>57.51</v>
       </c>
       <c r="E18" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H18" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I18" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J18" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K18" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L18" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M18" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N18" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O18" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C19" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D19" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E19" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H19" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I19" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J19" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K19" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L19" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M19" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N19" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O19" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C20" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D20" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E20" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H20" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I20" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J20" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K20" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L20" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M20" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N20" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O20" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2239,7 +2225,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2249,222 +2235,228 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C21" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D21" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E21" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H21" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J21" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K21" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L21" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M21" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N21" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O21" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C22" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D22" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E22" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F22" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H22" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I22" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J22" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K22" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L22" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M22" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N22" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O22" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C23" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D23" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E23" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F23" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H23" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I23" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J23" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K23" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L23" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M23" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N23" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O23" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2475,82 +2467,80 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C24" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D24" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E24" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F24" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H24" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I24" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J24" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K24" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L24" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M24" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N24" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O24" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2561,27 +2551,23 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2591,69 +2577,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C25" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D25" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E25" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F25" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H25" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I25" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J25" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K25" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L25" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M25" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N25" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O25" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>60.65</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2663,7 +2653,7 @@
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2671,7 +2661,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2681,210 +2671,210 @@
         <v>58.66</v>
       </c>
       <c r="D26" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E26" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H26" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J26" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K26" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L26" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M26" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N26" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O26" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F27" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J27" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K27" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L27" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M27" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N27" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O27" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>58.66</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O28" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -2901,7 +2891,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2915,7 +2905,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2925,83 +2915,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O29" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -3009,63 +3001,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D30" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E30" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I30" t="n">
         <v>57.86</v>
       </c>
-      <c r="C30" t="n">
+      <c r="J30" t="n">
         <v>57.86</v>
       </c>
-      <c r="D30" t="n">
+      <c r="K30" t="n">
         <v>57.86</v>
       </c>
-      <c r="E30" t="n">
+      <c r="L30" t="n">
         <v>57.86</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J30" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O30" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3085,154 +3081,148 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C31" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D31" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E31" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F31" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H31" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I31" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J31" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K31" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L31" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M31" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N31" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O31" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C32" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D32" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E32" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H32" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I32" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J32" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K32" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L32" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M32" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N32" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O32" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3240,14 +3230,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3259,65 +3247,65 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C33" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D33" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E33" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F33" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H33" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I33" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J33" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K33" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L33" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N33" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O33" t="n">
         <v>57.93</v>
       </c>
-      <c r="M33" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N33" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O33" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
@@ -3329,76 +3317,78 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C34" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D34" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E34" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F34" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H34" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I34" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J34" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K34" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L34" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M34" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N34" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O34" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3409,7 +3399,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3419,17 +3409,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3439,81 +3427,83 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C35" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D35" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E35" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F35" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H35" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I35" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J35" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K35" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L35" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M35" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N35" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O35" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+        <v>62.8</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3521,83 +3511,83 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C36" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D36" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E36" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H36" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I36" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J36" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K36" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L36" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M36" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N36" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O36" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3605,50 +3595,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C37" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D37" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E37" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F37" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H37" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J37" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K37" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L37" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M37" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N37" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O37" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3659,7 +3649,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3671,15 +3661,13 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3689,50 +3677,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C38" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D38" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E38" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F38" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J38" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M38" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O38" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3745,76 +3733,76 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C39" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E39" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I39" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J39" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L39" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O39" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3827,76 +3815,78 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C40" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D40" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E40" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F40" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I40" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K40" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M40" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O40" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3904,83 +3894,83 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W40" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H41" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J41" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K41" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L41" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N41" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3988,86 +3978,88 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C42" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I42" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C42" t="n">
+      <c r="J42" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D42" t="n">
+      <c r="K42" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E42" t="n">
+      <c r="L42" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F42" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J42" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K42" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L42" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M42" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N42" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
@@ -4075,7 +4067,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4087,7 +4079,7 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V42" s="8" t="inlineStr">
@@ -4095,7 +4087,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4105,85 +4097,83 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>65.25</v>
       </c>
       <c r="C43" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D43" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E43" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F43" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H43" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I43" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J43" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N43" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O43" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4191,134 +4181,136 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C44" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E44" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H44" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I44" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J44" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K44" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L44" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O44" t="n">
-        <v>67</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C45" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D45" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D45" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E45" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F45" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H45" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I45" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J45" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K45" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L45" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M45" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O45" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4329,82 +4321,76 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F46" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H46" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I46" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J46" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L46" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N46" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O46" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4415,7 +4401,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4431,7 +4417,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4441,50 +4427,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H47" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J47" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L47" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M47" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N47" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O47" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4492,18 +4478,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4511,60 +4497,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C48" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D48" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E48" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I48" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J48" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K48" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L48" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N48" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4574,81 +4564,85 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C49" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D49" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H49" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I49" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K49" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L49" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M49" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N49" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4658,85 +4652,81 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H50" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J50" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K50" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L50" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O50" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4744,96 +4734,100 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C51" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D51" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E51" t="n">
+        <v>67</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I51" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C51" t="n">
+      <c r="J51" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D51" t="n">
+      <c r="K51" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E51" t="n">
+      <c r="L51" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J51" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K51" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L51" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M51" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4843,173 +4837,169 @@
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H52" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J52" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K52" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L52" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O52" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
+        <v>76.09</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E53" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H53" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I53" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L53" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M53" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N53" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O53" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>68.52</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -5021,7 +5011,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5031,69 +5021,63 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C54" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D54" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E54" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H54" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I54" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J54" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K54" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L54" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O54" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>69.56</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5105,60 +5089,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C55" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D55" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E55" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F55" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H55" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I55" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J55" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K55" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L55" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O55" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5171,76 +5159,78 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C56" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F56" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H56" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I56" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J56" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K56" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M56" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O56" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5248,83 +5238,83 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C57" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D57" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H57" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I57" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J57" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M57" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N57" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O57" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5332,14 +5322,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5351,64 +5339,64 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C58" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D58" t="n">
         <v>66.3</v>
       </c>
-      <c r="D58" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E58" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F58" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H58" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I58" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J58" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K58" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L58" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M58" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O58" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5419,111 +5407,113 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C59" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D59" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E59" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F59" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H59" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I59" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J59" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N59" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O59" t="n">
-        <v>67</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+        <v>69.91</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5531,139 +5521,145 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C60" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D60" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E60" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I60" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J60" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K60" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L60" t="n">
         <v>64.28</v>
       </c>
-      <c r="F60" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I60" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J60" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K60" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L60" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M60" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N60" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O60" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64.14</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>65.81999999999999</v>
+        <v>64.98</v>
       </c>
       <c r="D61" t="n">
-        <v>63.15</v>
+        <v>62.8</v>
       </c>
       <c r="E61" t="n">
-        <v>65.19</v>
+        <v>63.76</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0124</v>
       </c>
       <c r="H61" t="n">
-        <v>2.67</v>
+        <v>2.18</v>
       </c>
       <c r="I61" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J61" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K61" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L61" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M61" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N61" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O61" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
@@ -5672,37 +5668,31 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5713,25 +5703,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>60.48</v>
+        <v>60.62</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>62.87</v>
+        <v>61.51</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>63.85</v>
+        <v>62.66</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>64.84</v>
+        <v>63.82</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>66.52</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>68.20999999999999</v>
+        <v>65.87</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>68.48999999999999</v>
+        <v>67.16</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5617,25 +5617,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64.79000000000001</v>
+        <v>63.76</v>
       </c>
       <c r="C61" t="n">
-        <v>64.98</v>
+        <v>64.08</v>
       </c>
       <c r="D61" t="n">
-        <v>62.8</v>
+        <v>63.39</v>
       </c>
       <c r="E61" t="n">
-        <v>63.76</v>
+        <v>63.85</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0109</v>
       </c>
       <c r="H61" t="n">
-        <v>2.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>61.65</v>
@@ -5703,25 +5703,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>60.62</v>
+        <v>62.7</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>61.51</v>
+        <v>63.22</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>62.66</v>
+        <v>63.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>63.82</v>
+        <v>63.79</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>64.84999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>65.87</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>67.16</v>
+        <v>64.77</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5626,13 +5626,13 @@
         <v>63.39</v>
       </c>
       <c r="E61" t="n">
-        <v>63.85</v>
+        <v>63.92</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0098</v>
       </c>
       <c r="H61" t="n">
         <v>0.6899999999999999</v>
@@ -5706,19 +5706,19 @@
         <v>62.7</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>63.22</v>
+        <v>63.32</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>63.5</v>
+        <v>63.57</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>63.79</v>
+        <v>63.83</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>64.19</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>64.77</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5626,13 +5626,13 @@
         <v>63.39</v>
       </c>
       <c r="E61" t="n">
-        <v>63.92</v>
+        <v>64.03</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.63</v>
+        <v>-0.52</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0081</v>
       </c>
       <c r="H61" t="n">
         <v>0.6899999999999999</v>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5706,19 +5706,19 @@
         <v>62.7</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>63.32</v>
+        <v>63.49</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>63.57</v>
+        <v>63.68</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>63.83</v>
+        <v>63.88</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>64.26000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>64.7</v>
+        <v>64.87</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>64.77</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5617,25 +5617,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.76</v>
+        <v>63.51</v>
       </c>
       <c r="C61" t="n">
-        <v>64.08</v>
+        <v>63.7</v>
       </c>
       <c r="D61" t="n">
-        <v>63.39</v>
+        <v>63.02</v>
       </c>
       <c r="E61" t="n">
-        <v>64.03</v>
+        <v>63.51</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.52</v>
+        <v>-1.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0161</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I61" t="n">
         <v>61.65</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5692,35 +5692,115 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="C62" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="D62" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="E62" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I62" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="J62" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="K62" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="L62" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="M62" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="N62" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="O62" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
+      <c r="I63" s="13" t="n">
         <v>62.7</v>
       </c>
-      <c r="J62" s="13" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>63.88</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>64.87</v>
-      </c>
-      <c r="O62" s="13" t="n">
+      <c r="J63" s="13" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>63.46</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>64.53</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>64.77</v>
       </c>
     </row>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="C2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="D2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="E2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.44</v>
+        <v>-0.73</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>66.56999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="J2" t="n">
-        <v>68.93000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="K2" t="n">
-        <v>69.59999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="L2" t="n">
-        <v>70.28</v>
+        <v>66.25</v>
       </c>
       <c r="M2" t="n">
-        <v>71.79000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="N2" t="n">
-        <v>73.31</v>
+        <v>66.25</v>
       </c>
       <c r="O2" t="n">
-        <v>73.14</v>
+        <v>66.25</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -725,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="C3" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>-0.0535</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I3" t="n">
         <v>65.53</v>
       </c>
-      <c r="C3" t="n">
+      <c r="J3" t="n">
         <v>65.53</v>
       </c>
-      <c r="D3" t="n">
+      <c r="K3" t="n">
         <v>65.53</v>
       </c>
-      <c r="E3" t="n">
+      <c r="L3" t="n">
         <v>65.53</v>
       </c>
-      <c r="F3" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="J3" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="L3" t="n">
-        <v>66.25</v>
-      </c>
       <c r="M3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="N3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="O3" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
@@ -809,50 +809,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.95</v>
+        <v>59.39</v>
       </c>
       <c r="C4" t="n">
-        <v>62.02</v>
+        <v>59.51</v>
       </c>
       <c r="D4" t="n">
-        <v>61.95</v>
+        <v>57.25</v>
       </c>
       <c r="E4" t="n">
-        <v>62.02</v>
+        <v>58.05</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.51</v>
+        <v>-3.97</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>65.53</v>
+        <v>61.88</v>
       </c>
       <c r="J4" t="n">
-        <v>65.53</v>
+        <v>61.97</v>
       </c>
       <c r="K4" t="n">
-        <v>65.53</v>
+        <v>61.99</v>
       </c>
       <c r="L4" t="n">
-        <v>65.53</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>65.53</v>
+        <v>62.06</v>
       </c>
       <c r="N4" t="n">
-        <v>65.53</v>
+        <v>62.11</v>
       </c>
       <c r="O4" t="n">
-        <v>65.53</v>
+        <v>62.09</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
@@ -893,69 +893,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.39</v>
+        <v>58.38</v>
       </c>
       <c r="C5" t="n">
-        <v>59.51</v>
+        <v>58.38</v>
       </c>
       <c r="D5" t="n">
-        <v>57.25</v>
+        <v>58.35</v>
       </c>
       <c r="E5" t="n">
-        <v>58.05</v>
+        <v>58.35</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.97</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.0051</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>61.88</v>
+        <v>54.99</v>
       </c>
       <c r="J5" t="n">
-        <v>61.97</v>
+        <v>55.62</v>
       </c>
       <c r="K5" t="n">
-        <v>61.99</v>
+        <v>56.92</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>58.22</v>
       </c>
       <c r="M5" t="n">
-        <v>62.06</v>
+        <v>59.18</v>
       </c>
       <c r="N5" t="n">
-        <v>62.11</v>
+        <v>60.15</v>
       </c>
       <c r="O5" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>61.78</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -972,55 +966,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C6" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I6" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J6" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M6" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N6" t="n">
         <v>58.38</v>
       </c>
-      <c r="C6" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D6" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E6" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I6" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J6" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K6" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L6" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M6" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N6" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O6" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,109 +1031,111 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C7" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D7" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E7" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F7" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I7" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J7" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K7" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L7" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M7" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N7" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O7" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
+        <v>59.24</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1143,77 +1143,77 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C8" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D8" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E8" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H8" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I8" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J8" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K8" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L8" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M8" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N8" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O8" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1222,55 +1222,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D9" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E9" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H9" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I9" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J9" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K9" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L9" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M9" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N9" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O9" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1285,18 +1289,14 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1308,57 +1308,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C10" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D10" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E10" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F10" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I10" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J10" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K10" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L10" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M10" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N10" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O10" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1366,18 +1366,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1399,50 +1399,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C11" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D11" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E11" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H11" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J11" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K11" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L11" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M11" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N11" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O11" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1483,70 +1483,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C12" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D12" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E12" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F12" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H12" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I12" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J12" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K12" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L12" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M12" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N12" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O12" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1558,68 +1562,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C13" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D13" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E13" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H13" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J13" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K13" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L13" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M13" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N13" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O13" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1651,77 +1651,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C14" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D14" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E14" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H14" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J14" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K14" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L14" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M14" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N14" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O14" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1730,55 +1728,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C15" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D15" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E15" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F15" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J15" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K15" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L15" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M15" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N15" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O15" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1789,20 +1791,16 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1814,70 +1812,76 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C16" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D16" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E16" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H16" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I16" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J16" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K16" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L16" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M16" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N16" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O16" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1894,86 +1898,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C17" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D17" t="n">
         <v>57.51</v>
       </c>
       <c r="E17" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H17" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I17" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J17" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K17" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L17" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M17" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N17" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O17" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1982,80 +1980,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C18" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D18" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E18" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H18" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J18" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K18" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L18" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M18" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N18" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O18" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2064,71 +2066,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C19" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D19" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E19" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H19" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I19" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J19" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K19" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L19" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M19" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N19" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O19" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
@@ -2155,73 +2151,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C20" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D20" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E20" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H20" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J20" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K20" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L20" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M20" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N20" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O20" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2230,70 +2234,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C21" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D21" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E21" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F21" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I21" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J21" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K21" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L21" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M21" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N21" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O21" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
@@ -2302,16 +2304,16 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2320,57 +2322,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C22" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D22" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E22" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F22" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H22" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I22" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J22" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K22" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L22" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M22" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N22" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O22" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2388,75 +2390,73 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C23" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D23" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E23" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F23" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H23" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I23" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J23" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K23" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L23" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M23" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N23" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O23" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2474,18 +2474,14 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
@@ -2497,79 +2493,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C24" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D24" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E24" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H24" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I24" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J24" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K24" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L24" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M24" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N24" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O24" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2587,210 +2587,210 @@
         <v>58.66</v>
       </c>
       <c r="D25" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E25" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H25" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J25" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K25" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L25" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M25" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N25" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O25" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F26" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J26" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K26" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L26" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M26" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N26" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O26" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O27" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -2831,83 +2831,85 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O28" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2915,61 +2917,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D29" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E29" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I29" t="n">
         <v>57.86</v>
       </c>
-      <c r="C29" t="n">
+      <c r="J29" t="n">
         <v>57.86</v>
       </c>
-      <c r="D29" t="n">
+      <c r="K29" t="n">
         <v>57.86</v>
       </c>
-      <c r="E29" t="n">
+      <c r="L29" t="n">
         <v>57.86</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O29" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2996,90 +3002,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C30" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D30" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E30" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F30" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H30" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I30" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J30" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K30" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L30" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M30" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N30" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O30" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
@@ -3088,57 +3088,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C31" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D31" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E31" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H31" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I31" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J31" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K31" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L31" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M31" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N31" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O31" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3146,14 +3146,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3172,58 +3170,58 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C32" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D32" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E32" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F32" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I32" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J32" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K32" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L32" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N32" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O32" t="n">
         <v>57.93</v>
       </c>
-      <c r="M32" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N32" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O32" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
@@ -3233,78 +3231,80 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C33" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D33" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E33" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F33" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H33" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I33" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J33" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K33" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L33" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M33" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N33" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O33" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3325,10 +3325,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
@@ -3345,81 +3343,83 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C34" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D34" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E34" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F34" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H34" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I34" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J34" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K34" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L34" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M34" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N34" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O34" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3427,83 +3427,83 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C35" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D35" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E35" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H35" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I35" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J35" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K35" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L35" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M35" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N35" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O35" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3511,50 +3511,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C36" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D36" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E36" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F36" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H36" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I36" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J36" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K36" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L36" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M36" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N36" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O36" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3577,13 +3577,11 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
@@ -3595,50 +3593,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C37" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D37" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E37" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F37" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I37" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J37" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M37" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O37" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3649,20 +3647,16 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3672,55 +3666,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C38" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E38" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J38" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L38" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O38" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3731,78 +3729,80 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C39" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D39" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E39" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F39" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I39" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K39" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M39" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O39" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3810,83 +3810,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H40" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J40" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K40" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L40" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N40" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3894,86 +3894,88 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C41" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E41" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I41" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C41" t="n">
+      <c r="J41" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D41" t="n">
+      <c r="K41" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E41" t="n">
+      <c r="L41" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J41" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K41" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L41" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M41" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N41" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
@@ -3993,7 +3995,7 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V41" s="8" t="inlineStr">
@@ -4011,85 +4013,83 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>65.25</v>
       </c>
       <c r="C42" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D42" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E42" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F42" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H42" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I42" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J42" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N42" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O42" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4097,134 +4097,136 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C43" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E43" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H43" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I43" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J43" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K43" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L43" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O43" t="n">
-        <v>67</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C44" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D44" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D44" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E44" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F44" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H44" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I44" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J44" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K44" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L44" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M44" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O44" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4242,14 +4244,12 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4258,59 +4258,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F45" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H45" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I45" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J45" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L45" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N45" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O45" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4347,50 +4343,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H46" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J46" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L46" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M46" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N46" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O46" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4398,19 +4394,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4422,55 +4418,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C47" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D47" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E47" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I47" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J47" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K47" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L47" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N47" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4480,19 +4480,23 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4504,57 +4508,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C48" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D48" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H48" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I48" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K48" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L48" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M48" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N48" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4564,23 +4568,19 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4592,57 +4592,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H49" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J49" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K49" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L49" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O49" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4650,22 +4650,24 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4674,72 +4676,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C50" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D50" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E50" t="n">
+        <v>67</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I50" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C50" t="n">
+      <c r="J50" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D50" t="n">
+      <c r="K50" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E50" t="n">
+      <c r="L50" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J50" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K50" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L50" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M50" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4749,173 +4753,169 @@
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H51" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I51" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J51" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K51" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L51" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O51" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E52" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H52" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I52" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L52" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M52" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N52" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O52" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4937,69 +4937,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C53" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D53" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E53" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H53" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I53" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J53" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K53" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L53" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O53" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -5016,55 +5010,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C54" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D54" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E54" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F54" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H54" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I54" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J54" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K54" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L54" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O54" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5075,78 +5073,80 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C55" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F55" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H55" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I55" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J55" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K55" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M55" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O55" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5154,83 +5154,83 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C56" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D56" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H56" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J56" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M56" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N56" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O56" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5238,14 +5238,12 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5264,57 +5262,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C57" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D57" t="n">
         <v>66.3</v>
       </c>
-      <c r="D57" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E57" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F57" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I57" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J57" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K57" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L57" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M57" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O57" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5327,109 +5325,111 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C58" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D58" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E58" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F58" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H58" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I58" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J58" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N58" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O58" t="n">
-        <v>67</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -5437,143 +5437,149 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C59" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D59" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E59" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I59" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J59" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K59" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L59" t="n">
         <v>64.28</v>
       </c>
-      <c r="F59" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I59" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J59" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K59" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L59" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M59" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N59" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O59" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C60" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D60" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E60" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F60" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H60" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J60" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K60" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L60" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M60" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N60" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O60" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5581,20 +5587,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5606,202 +5608,122 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.51</v>
+        <v>63.76</v>
       </c>
       <c r="C61" t="n">
-        <v>63.7</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E61" t="n">
-        <v>63.51</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.04</v>
+        <v>0.67</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0106</v>
       </c>
       <c r="H61" t="n">
-        <v>0.68</v>
+        <v>1.43</v>
       </c>
       <c r="I61" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J61" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K61" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L61" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M61" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N61" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O61" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>63.76</v>
-      </c>
-      <c r="C62" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="D62" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="E62" t="n">
-        <v>63.81</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>62.34</v>
-      </c>
-      <c r="J62" t="n">
-        <v>62.91</v>
-      </c>
-      <c r="K62" t="n">
-        <v>63.17</v>
-      </c>
-      <c r="L62" t="n">
-        <v>63.44</v>
-      </c>
-      <c r="M62" t="n">
-        <v>63.85</v>
-      </c>
-      <c r="N62" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="O62" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>63.46</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>63.77</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>64.53</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>64.77</v>
+      <c r="I62" s="13" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>63.47</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>65.89</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5619,25 +5619,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.76</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>64.45999999999999</v>
+        <v>64.48</v>
       </c>
       <c r="D61" t="n">
-        <v>63.03</v>
+        <v>63.94</v>
       </c>
       <c r="E61" t="n">
-        <v>64.18000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="F61" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0107</v>
       </c>
       <c r="H61" t="n">
-        <v>1.43</v>
+        <v>0.54</v>
       </c>
       <c r="I61" t="n">
         <v>62.34</v>
@@ -5666,10 +5666,8 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
@@ -5705,25 +5703,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>61.61</v>
+        <v>63.4</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>62.97</v>
+        <v>63.64</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>63.47</v>
+        <v>63.92</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>63.97</v>
+        <v>64.2</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>64.90000000000001</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>65.83</v>
+        <v>64.72</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>65.89</v>
+        <v>65.02</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5619,25 +5619,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64.18000000000001</v>
+        <v>63.03</v>
       </c>
       <c r="C61" t="n">
-        <v>64.48</v>
+        <v>63.64</v>
       </c>
       <c r="D61" t="n">
-        <v>63.94</v>
+        <v>63.03</v>
       </c>
       <c r="E61" t="n">
-        <v>64.19</v>
+        <v>63.24</v>
       </c>
       <c r="F61" t="n">
-        <v>0.68</v>
+        <v>-0.28</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0044</v>
       </c>
       <c r="H61" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="I61" t="n">
         <v>62.34</v>
@@ -5666,62 +5666,146 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>65.39</v>
+      </c>
+      <c r="D62" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="E62" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I62" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="J62" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="K62" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="L62" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="M62" t="n">
+        <v>63.54</v>
+      </c>
+      <c r="N62" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="O62" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>63.92</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>64.45999999999999</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>64.72</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>65.02</v>
+      <c r="I63" s="13" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>64.03</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>66.84999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5706,22 +5706,22 @@
         <v>64.18000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>65.39</v>
+        <v>65.42</v>
       </c>
       <c r="D62" t="n">
         <v>63.94</v>
       </c>
       <c r="E62" t="n">
-        <v>65.20999999999999</v>
+        <v>65.36</v>
       </c>
       <c r="F62" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0313</v>
+        <v>0.0335</v>
       </c>
       <c r="H62" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="I62" t="n">
         <v>62.42</v>
@@ -5787,25 +5787,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>62.49</v>
+        <v>62.46</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>64.03</v>
+        <v>64.22</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>64.48999999999999</v>
+        <v>64.62</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>64.94</v>
+        <v>65.02</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>65.94</v>
+        <v>66.09</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>66.94</v>
+        <v>67.17</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>66.84999999999999</v>
+        <v>66.89</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5706,22 +5706,22 @@
         <v>64.18000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>65.42</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="D62" t="n">
         <v>63.94</v>
       </c>
       <c r="E62" t="n">
-        <v>65.36</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="H62" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="I62" t="n">
         <v>62.42</v>
@@ -5787,25 +5787,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>62.46</v>
+        <v>62.42</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>64.22</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>64.62</v>
+        <v>64.59</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>65.02</v>
+        <v>65.03</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>66.09</v>
+        <v>66.11</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>67.17</v>
+        <v>67.2</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>66.89</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5712,13 +5712,13 @@
         <v>63.94</v>
       </c>
       <c r="E62" t="n">
-        <v>65.34999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0334</v>
+        <v>0.032</v>
       </c>
       <c r="H62" t="n">
         <v>1.52</v>
@@ -5790,19 +5790,19 @@
         <v>62.42</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>64.15000000000001</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>64.59</v>
+        <v>64.5</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>65.03</v>
+        <v>64.98</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>66.11</v>
+        <v>66.02</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>67.2</v>
+        <v>67.06</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>66.98999999999999</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="C2" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="D2" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-0.0535</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I2" t="n">
         <v>65.53</v>
       </c>
-      <c r="C2" t="n">
+      <c r="J2" t="n">
         <v>65.53</v>
       </c>
-      <c r="D2" t="n">
+      <c r="K2" t="n">
         <v>65.53</v>
       </c>
-      <c r="E2" t="n">
+      <c r="L2" t="n">
         <v>65.53</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="J2" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="K2" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>66.25</v>
-      </c>
       <c r="M2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="N2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="O2" t="n">
-        <v>66.25</v>
+        <v>65.53</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -725,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.95</v>
+        <v>59.39</v>
       </c>
       <c r="C3" t="n">
-        <v>62.02</v>
+        <v>59.51</v>
       </c>
       <c r="D3" t="n">
-        <v>61.95</v>
+        <v>57.25</v>
       </c>
       <c r="E3" t="n">
-        <v>62.02</v>
+        <v>58.05</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.51</v>
+        <v>-3.97</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>65.53</v>
+        <v>61.88</v>
       </c>
       <c r="J3" t="n">
-        <v>65.53</v>
+        <v>61.97</v>
       </c>
       <c r="K3" t="n">
-        <v>65.53</v>
+        <v>61.99</v>
       </c>
       <c r="L3" t="n">
-        <v>65.53</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>65.53</v>
+        <v>62.06</v>
       </c>
       <c r="N3" t="n">
-        <v>65.53</v>
+        <v>62.11</v>
       </c>
       <c r="O3" t="n">
-        <v>65.53</v>
+        <v>62.09</v>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
@@ -809,69 +809,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.39</v>
+        <v>58.38</v>
       </c>
       <c r="C4" t="n">
-        <v>59.51</v>
+        <v>58.38</v>
       </c>
       <c r="D4" t="n">
-        <v>57.25</v>
+        <v>58.35</v>
       </c>
       <c r="E4" t="n">
-        <v>58.05</v>
+        <v>58.35</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.97</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.0051</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>61.88</v>
+        <v>54.99</v>
       </c>
       <c r="J4" t="n">
-        <v>61.97</v>
+        <v>55.62</v>
       </c>
       <c r="K4" t="n">
-        <v>61.99</v>
+        <v>56.92</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>58.22</v>
       </c>
       <c r="M4" t="n">
-        <v>62.06</v>
+        <v>59.18</v>
       </c>
       <c r="N4" t="n">
-        <v>62.11</v>
+        <v>60.15</v>
       </c>
       <c r="O4" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>61.78</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -888,55 +882,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I5" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J5" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N5" t="n">
         <v>58.38</v>
       </c>
-      <c r="C5" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D5" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E5" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I5" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J5" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K5" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L5" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N5" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O5" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -949,109 +947,111 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C6" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D6" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E6" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F6" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I6" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J6" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K6" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L6" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M6" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N6" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O6" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+        <v>59.24</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1059,77 +1059,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C7" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D7" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E7" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H7" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I7" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J7" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K7" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L7" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M7" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N7" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O7" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1138,55 +1138,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C8" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D8" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E8" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H8" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I8" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J8" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K8" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L8" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M8" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N8" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O8" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1201,18 +1205,14 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1224,57 +1224,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C9" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D9" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E9" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F9" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I9" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J9" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K9" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L9" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M9" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N9" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O9" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,18 +1282,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1315,50 +1315,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C10" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D10" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E10" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H10" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I10" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J10" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K10" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L10" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M10" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N10" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O10" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1399,70 +1399,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C11" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D11" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E11" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H11" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I11" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J11" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K11" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L11" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M11" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N11" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O11" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1474,68 +1478,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C12" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D12" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E12" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H12" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J12" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K12" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L12" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M12" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N12" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O12" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -1567,77 +1567,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C13" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D13" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E13" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J13" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K13" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L13" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M13" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N13" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O13" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1646,55 +1644,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C14" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D14" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E14" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F14" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I14" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J14" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K14" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L14" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M14" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N14" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O14" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,20 +1707,16 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1730,70 +1728,76 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C15" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D15" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E15" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H15" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I15" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J15" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K15" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L15" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M15" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N15" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O15" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1810,86 +1814,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C16" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D16" t="n">
         <v>57.51</v>
       </c>
       <c r="E16" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H16" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I16" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J16" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K16" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L16" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M16" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N16" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O16" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1898,80 +1896,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C17" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D17" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E17" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H17" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I17" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J17" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K17" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L17" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M17" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N17" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O17" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1980,71 +1982,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C18" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D18" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E18" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H18" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I18" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J18" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K18" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L18" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M18" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N18" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O18" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
@@ -2071,73 +2067,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C19" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D19" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E19" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H19" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J19" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K19" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L19" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M19" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N19" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O19" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2146,70 +2150,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C20" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D20" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E20" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H20" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I20" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J20" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K20" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L20" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M20" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N20" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O20" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
@@ -2218,16 +2220,16 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2236,57 +2238,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C21" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D21" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E21" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F21" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H21" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I21" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J21" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K21" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L21" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M21" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N21" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O21" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2304,75 +2306,73 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C22" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D22" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E22" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F22" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H22" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I22" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J22" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K22" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L22" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M22" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N22" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O22" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2390,18 +2390,14 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
@@ -2413,79 +2409,83 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C23" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D23" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E23" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F23" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H23" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I23" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J23" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K23" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L23" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M23" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N23" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O23" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2503,210 +2503,210 @@
         <v>58.66</v>
       </c>
       <c r="D24" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E24" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H24" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J24" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K24" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L24" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M24" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N24" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O24" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J25" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K25" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L25" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M25" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N25" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O25" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O26" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -2747,83 +2747,85 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O27" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2831,61 +2833,65 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C28" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D28" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E28" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I28" t="n">
         <v>57.86</v>
       </c>
-      <c r="C28" t="n">
+      <c r="J28" t="n">
         <v>57.86</v>
       </c>
-      <c r="D28" t="n">
+      <c r="K28" t="n">
         <v>57.86</v>
       </c>
-      <c r="E28" t="n">
+      <c r="L28" t="n">
         <v>57.86</v>
       </c>
-      <c r="F28" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O28" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2912,90 +2918,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C29" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D29" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E29" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H29" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I29" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J29" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K29" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L29" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M29" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N29" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O29" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C30" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D30" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E30" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H30" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I30" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J30" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K30" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L30" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M30" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N30" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O30" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3062,14 +3062,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3088,58 +3086,58 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C31" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D31" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E31" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F31" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H31" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I31" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J31" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K31" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L31" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M31" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N31" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O31" t="n">
         <v>57.93</v>
       </c>
-      <c r="M31" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N31" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O31" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
@@ -3149,78 +3147,80 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C32" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D32" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E32" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F32" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H32" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I32" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J32" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K32" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L32" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M32" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N32" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O32" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3241,10 +3241,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
@@ -3261,81 +3259,83 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C33" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D33" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E33" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F33" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H33" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I33" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J33" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K33" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L33" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M33" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N33" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O33" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3343,83 +3343,83 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C34" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D34" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E34" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H34" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I34" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J34" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K34" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L34" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M34" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N34" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O34" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3427,50 +3427,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C35" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D35" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E35" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F35" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H35" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J35" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K35" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L35" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M35" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N35" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O35" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3493,13 +3493,11 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
@@ -3511,50 +3509,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C36" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D36" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E36" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F36" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H36" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J36" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M36" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O36" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3565,20 +3563,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3588,55 +3582,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C37" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E37" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J37" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L37" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O37" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3647,78 +3645,80 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C38" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D38" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E38" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F38" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I38" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K38" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M38" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O38" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3726,83 +3726,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J39" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K39" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L39" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N39" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3810,86 +3810,88 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C40" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E40" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I40" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C40" t="n">
+      <c r="J40" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D40" t="n">
+      <c r="K40" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E40" t="n">
+      <c r="L40" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F40" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J40" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K40" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L40" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M40" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
@@ -3909,7 +3911,7 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V40" s="8" t="inlineStr">
@@ -3927,85 +3929,83 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>65.25</v>
       </c>
       <c r="C41" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D41" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E41" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F41" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H41" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I41" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J41" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N41" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O41" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -4013,134 +4013,136 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C42" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E42" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H42" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I42" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J42" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K42" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L42" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O42" t="n">
-        <v>67</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C43" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D43" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D43" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E43" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F43" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H43" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I43" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J43" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K43" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L43" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M43" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O43" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4158,14 +4160,12 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4174,59 +4174,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F44" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H44" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I44" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J44" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L44" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N44" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O44" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4263,50 +4259,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H45" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J45" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L45" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M45" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N45" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O45" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4314,19 +4310,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4338,55 +4334,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C46" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D46" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E46" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I46" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J46" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K46" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L46" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N46" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4396,19 +4396,23 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4420,57 +4424,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C47" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D47" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H47" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I47" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K47" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L47" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M47" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N47" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4480,23 +4484,19 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4508,57 +4508,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H48" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J48" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K48" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L48" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O48" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4566,22 +4566,24 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4590,72 +4592,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C49" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D49" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E49" t="n">
+        <v>67</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I49" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C49" t="n">
+      <c r="J49" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D49" t="n">
+      <c r="K49" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E49" t="n">
+      <c r="L49" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J49" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K49" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L49" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M49" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4665,173 +4669,169 @@
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H50" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I50" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J50" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K50" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L50" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O50" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E51" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H51" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I51" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L51" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M51" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N51" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O51" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4853,69 +4853,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C52" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D52" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E52" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H52" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I52" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J52" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K52" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L52" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O52" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4932,55 +4926,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C53" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D53" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E53" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F53" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H53" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I53" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J53" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K53" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L53" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O53" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4991,78 +4989,80 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C54" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F54" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H54" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I54" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J54" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K54" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M54" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O54" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5070,83 +5070,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C55" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D55" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H55" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I55" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J55" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M55" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N55" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O55" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5154,14 +5154,12 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5180,57 +5178,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C56" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D56" t="n">
         <v>66.3</v>
       </c>
-      <c r="D56" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E56" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F56" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I56" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J56" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K56" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L56" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M56" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O56" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5243,109 +5241,111 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C57" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D57" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E57" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F57" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H57" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I57" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J57" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N57" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O57" t="n">
-        <v>67</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -5353,143 +5353,149 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C58" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D58" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E58" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I58" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J58" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K58" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L58" t="n">
         <v>64.28</v>
       </c>
-      <c r="F58" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I58" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K58" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M58" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N58" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O58" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C59" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D59" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E59" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F59" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H59" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I59" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J59" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K59" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L59" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M59" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N59" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O59" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -5497,20 +5503,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5522,71 +5524,69 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C60" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D60" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E60" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H60" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I60" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J60" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K60" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L60" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M60" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N60" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O60" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5608,204 +5608,118 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.03</v>
+        <v>63.42</v>
       </c>
       <c r="C61" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="D61" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="E61" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I61" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="J61" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="K61" t="n">
+        <v>62.93</v>
+      </c>
+      <c r="L61" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="M61" t="n">
+        <v>63.54</v>
+      </c>
+      <c r="N61" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="O61" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>明日預測</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="O62" s="13" t="n">
         <v>63.64</v>
-      </c>
-      <c r="D61" t="n">
-        <v>63.03</v>
-      </c>
-      <c r="E61" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.0044</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I61" t="n">
-        <v>62.34</v>
-      </c>
-      <c r="J61" t="n">
-        <v>62.91</v>
-      </c>
-      <c r="K61" t="n">
-        <v>63.17</v>
-      </c>
-      <c r="L61" t="n">
-        <v>63.44</v>
-      </c>
-      <c r="M61" t="n">
-        <v>63.85</v>
-      </c>
-      <c r="N61" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="O61" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="C62" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="D62" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="E62" t="n">
-        <v>65.26000000000001</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I62" t="n">
-        <v>62.42</v>
-      </c>
-      <c r="J62" t="n">
-        <v>62.58</v>
-      </c>
-      <c r="K62" t="n">
-        <v>62.93</v>
-      </c>
-      <c r="L62" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="M62" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="N62" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="O62" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>62.42</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>64.98</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>67.06</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>66.98999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5622,22 +5622,22 @@
         <v>63.42</v>
       </c>
       <c r="C61" t="n">
-        <v>63.49</v>
+        <v>63.94</v>
       </c>
       <c r="D61" t="n">
-        <v>63.35</v>
+        <v>63.28</v>
       </c>
       <c r="E61" t="n">
-        <v>63.37</v>
+        <v>63.66</v>
       </c>
       <c r="F61" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0067</v>
       </c>
       <c r="H61" t="n">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
       <c r="I61" t="n">
         <v>62.42</v>
@@ -5671,14 +5671,18 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5688,11 +5692,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5701,25 +5701,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>63.2</v>
+        <v>62.61</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>63.19</v>
+        <v>63.02</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>63.29</v>
+        <v>63.33</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>63.39</v>
+        <v>63.64</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>63.44</v>
+        <v>63.99</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>63.48</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>63.64</v>
+        <v>64.61</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5619,25 +5619,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.42</v>
+        <v>64.42</v>
       </c>
       <c r="C61" t="n">
-        <v>63.94</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>63.28</v>
+        <v>63.7</v>
       </c>
       <c r="E61" t="n">
-        <v>63.66</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0067</v>
+        <v>0.0166</v>
       </c>
       <c r="H61" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="I61" t="n">
         <v>62.42</v>
@@ -5676,17 +5676,19 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
@@ -5695,31 +5697,115 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="D62" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="E62" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I62" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="J62" t="n">
+        <v>63.54</v>
+      </c>
+      <c r="K62" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="L62" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="N62" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="O62" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>62.61</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>63.02</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>63.33</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>64.61</v>
+      <c r="I63" s="13" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>65.58</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>65.89</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>65.95999999999999</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>66.12</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5712,13 +5712,13 @@
         <v>65.73999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>65.79000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="F62" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0245</v>
       </c>
       <c r="H62" t="n">
         <v>0.19</v>
@@ -5790,19 +5790,19 @@
         <v>65.55</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>65.58</v>
+        <v>65.69</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>65.69</v>
+        <v>65.77</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>65.81</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>65.89</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>65.95999999999999</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>66.12</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5706,22 +5699,22 @@
         <v>65.76000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>65.93000000000001</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="D62" t="n">
         <v>65.73999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>65.86</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0245</v>
+        <v>0.0273</v>
       </c>
       <c r="H62" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="I62" t="n">
         <v>62.86</v>
@@ -5779,34 +5772,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>65.55</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>65.69</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>65.84999999999999</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>65.95999999999999</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>66.12</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5699,22 +5699,22 @@
         <v>65.76000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>66.20999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="D62" t="n">
         <v>65.73999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>66.04000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F62" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0297</v>
       </c>
       <c r="H62" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="I62" t="n">
         <v>62.86</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61.95</v>
+        <v>59.39</v>
       </c>
       <c r="C2" t="n">
-        <v>62.02</v>
+        <v>59.51</v>
       </c>
       <c r="D2" t="n">
-        <v>61.95</v>
+        <v>57.25</v>
       </c>
       <c r="E2" t="n">
-        <v>62.02</v>
+        <v>58.05</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.51</v>
+        <v>-3.97</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.064</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>65.53</v>
+        <v>61.88</v>
       </c>
       <c r="J2" t="n">
-        <v>65.53</v>
+        <v>61.97</v>
       </c>
       <c r="K2" t="n">
-        <v>65.53</v>
+        <v>61.99</v>
       </c>
       <c r="L2" t="n">
-        <v>65.53</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
-        <v>65.53</v>
+        <v>62.06</v>
       </c>
       <c r="N2" t="n">
-        <v>65.53</v>
+        <v>62.11</v>
       </c>
       <c r="O2" t="n">
-        <v>65.53</v>
+        <v>62.09</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -718,69 +718,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.39</v>
+        <v>58.38</v>
       </c>
       <c r="C3" t="n">
-        <v>59.51</v>
+        <v>58.38</v>
       </c>
       <c r="D3" t="n">
-        <v>57.25</v>
+        <v>58.35</v>
       </c>
       <c r="E3" t="n">
-        <v>58.05</v>
+        <v>58.35</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.97</v>
+        <v>0.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.0051</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>0.04</v>
       </c>
       <c r="I3" t="n">
-        <v>61.88</v>
+        <v>54.99</v>
       </c>
       <c r="J3" t="n">
-        <v>61.97</v>
+        <v>55.62</v>
       </c>
       <c r="K3" t="n">
-        <v>61.99</v>
+        <v>56.92</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>58.22</v>
       </c>
       <c r="M3" t="n">
-        <v>62.06</v>
+        <v>59.18</v>
       </c>
       <c r="N3" t="n">
-        <v>62.11</v>
+        <v>60.15</v>
       </c>
       <c r="O3" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>61.78</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -797,55 +791,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I4" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J4" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M4" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N4" t="n">
         <v>58.38</v>
       </c>
-      <c r="C4" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D4" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E4" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I4" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J4" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K4" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L4" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M4" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N4" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O4" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,109 +856,111 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C5" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D5" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E5" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I5" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J5" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K5" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L5" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M5" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N5" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O5" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+        <v>59.24</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -968,77 +968,77 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C6" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D6" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E6" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H6" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I6" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J6" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K6" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L6" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M6" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N6" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O6" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1047,55 +1047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C7" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D7" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E7" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H7" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I7" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J7" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K7" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L7" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M7" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N7" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O7" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1110,18 +1114,14 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1133,57 +1133,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C8" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D8" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E8" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F8" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I8" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J8" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K8" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L8" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M8" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N8" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O8" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,18 +1191,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1224,50 +1224,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C9" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D9" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E9" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H9" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I9" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J9" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K9" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L9" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M9" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N9" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O9" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1308,70 +1308,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C10" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D10" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E10" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F10" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H10" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J10" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K10" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L10" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M10" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N10" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O10" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1383,68 +1387,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C11" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D11" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E11" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H11" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J11" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K11" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L11" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M11" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N11" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O11" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1476,77 +1476,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C12" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D12" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E12" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J12" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K12" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L12" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M12" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N12" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O12" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1555,55 +1553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C13" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D13" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E13" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F13" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I13" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J13" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K13" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L13" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M13" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N13" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O13" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,20 +1616,16 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1639,70 +1637,76 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C14" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D14" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E14" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H14" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I14" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J14" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K14" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L14" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M14" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N14" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O14" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1719,86 +1723,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C15" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D15" t="n">
         <v>57.51</v>
       </c>
       <c r="E15" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H15" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I15" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J15" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K15" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L15" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M15" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N15" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O15" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1807,80 +1805,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C16" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D16" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E16" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F16" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H16" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I16" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J16" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K16" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L16" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M16" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N16" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O16" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1889,71 +1891,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C17" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D17" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E17" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I17" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J17" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K17" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L17" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M17" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N17" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O17" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
@@ -1980,73 +1976,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C18" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D18" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E18" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H18" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J18" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K18" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L18" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M18" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N18" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O18" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2055,70 +2059,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C19" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D19" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E19" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H19" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I19" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J19" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K19" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L19" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M19" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N19" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O19" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
@@ -2127,16 +2129,16 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2145,57 +2147,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C20" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D20" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E20" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F20" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H20" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I20" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J20" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K20" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L20" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M20" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N20" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O20" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2213,75 +2215,73 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C21" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D21" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E21" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F21" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H21" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J21" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K21" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L21" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M21" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N21" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O21" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2299,18 +2299,14 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
@@ -2322,79 +2318,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C22" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D22" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E22" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H22" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I22" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J22" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K22" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L22" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M22" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N22" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O22" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2412,210 +2412,210 @@
         <v>58.66</v>
       </c>
       <c r="D23" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E23" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H23" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J23" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K23" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L23" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M23" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N23" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O23" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F24" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J24" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K24" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L24" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M24" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N24" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O24" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O25" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -2656,83 +2656,85 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O26" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2740,61 +2742,65 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C27" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E27" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I27" t="n">
         <v>57.86</v>
       </c>
-      <c r="C27" t="n">
+      <c r="J27" t="n">
         <v>57.86</v>
       </c>
-      <c r="D27" t="n">
+      <c r="K27" t="n">
         <v>57.86</v>
       </c>
-      <c r="E27" t="n">
+      <c r="L27" t="n">
         <v>57.86</v>
       </c>
-      <c r="F27" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O27" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
@@ -2821,90 +2827,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C28" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D28" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E28" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F28" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H28" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I28" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J28" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K28" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L28" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M28" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N28" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O28" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
@@ -2913,57 +2913,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C29" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D29" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E29" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H29" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I29" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J29" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K29" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L29" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M29" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N29" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O29" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2971,14 +2971,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2997,58 +2995,58 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C30" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D30" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E30" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H30" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I30" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J30" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K30" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L30" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M30" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N30" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O30" t="n">
         <v>57.93</v>
       </c>
-      <c r="M30" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N30" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O30" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
@@ -3058,78 +3056,80 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C31" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D31" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E31" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F31" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H31" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I31" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J31" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K31" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L31" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M31" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N31" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O31" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3150,10 +3150,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
@@ -3170,81 +3168,83 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C32" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D32" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E32" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F32" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H32" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I32" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J32" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K32" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L32" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M32" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N32" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O32" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3252,83 +3252,83 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C33" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D33" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E33" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H33" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I33" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J33" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K33" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L33" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M33" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N33" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O33" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3336,50 +3336,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C34" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D34" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E34" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F34" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H34" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J34" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K34" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L34" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M34" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N34" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O34" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3402,13 +3402,11 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
@@ -3420,50 +3418,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C35" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D35" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E35" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F35" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J35" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M35" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O35" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3474,20 +3472,16 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3497,55 +3491,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C36" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E36" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I36" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J36" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L36" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O36" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3556,78 +3554,80 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C37" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D37" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E37" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F37" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I37" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K37" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M37" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O37" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3635,83 +3635,83 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H38" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J38" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K38" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L38" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N38" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3719,86 +3719,88 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C39" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I39" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C39" t="n">
+      <c r="J39" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D39" t="n">
+      <c r="K39" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E39" t="n">
+      <c r="L39" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F39" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J39" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L39" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M39" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
@@ -3818,7 +3820,7 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V39" s="8" t="inlineStr">
@@ -3836,85 +3838,83 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>65.25</v>
       </c>
       <c r="C40" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D40" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E40" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F40" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H40" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I40" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J40" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N40" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O40" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3922,134 +3922,136 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C41" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E41" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H41" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I41" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J41" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K41" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L41" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O41" t="n">
-        <v>67</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C42" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D42" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D42" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E42" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F42" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H42" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I42" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J42" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K42" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L42" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M42" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O42" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4067,14 +4069,12 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4083,59 +4083,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F43" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H43" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I43" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J43" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L43" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N43" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O43" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4172,50 +4168,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H44" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J44" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L44" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M44" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N44" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O44" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4223,19 +4219,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4247,55 +4243,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C45" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D45" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E45" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I45" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J45" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K45" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L45" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N45" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4305,19 +4305,23 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4329,57 +4333,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C46" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D46" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H46" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I46" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K46" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L46" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M46" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N46" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4389,23 +4393,19 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4417,57 +4417,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J47" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K47" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L47" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O47" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4475,22 +4475,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4499,72 +4501,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D48" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E48" t="n">
+        <v>67</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I48" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C48" t="n">
+      <c r="J48" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D48" t="n">
+      <c r="K48" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E48" t="n">
+      <c r="L48" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J48" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K48" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L48" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M48" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4574,173 +4578,169 @@
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H49" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I49" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J49" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K49" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L49" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O49" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E50" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H50" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I50" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L50" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M50" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N50" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O50" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4762,69 +4762,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C51" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D51" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E51" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H51" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I51" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J51" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K51" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L51" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O51" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4841,55 +4835,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C52" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D52" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E52" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F52" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H52" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I52" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J52" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K52" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L52" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O52" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4900,78 +4898,80 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C53" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F53" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H53" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I53" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J53" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K53" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M53" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O53" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4979,83 +4979,83 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C54" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D54" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H54" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I54" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J54" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M54" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N54" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O54" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5063,14 +5063,12 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5089,57 +5087,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C55" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D55" t="n">
         <v>66.3</v>
       </c>
-      <c r="D55" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E55" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F55" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I55" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J55" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K55" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L55" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M55" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O55" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5152,109 +5150,111 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C56" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D56" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E56" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F56" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H56" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I56" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J56" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N56" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O56" t="n">
-        <v>67</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -5262,143 +5262,149 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C57" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D57" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E57" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I57" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J57" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K57" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L57" t="n">
         <v>64.28</v>
       </c>
-      <c r="F57" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I57" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J57" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K57" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L57" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M57" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N57" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O57" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D58" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F58" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H58" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I58" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J58" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K58" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L58" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M58" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N58" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O58" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5406,20 +5412,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5431,71 +5433,69 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C59" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D59" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E59" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H59" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I59" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J59" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K59" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L59" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M59" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N59" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O59" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5517,57 +5517,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C60" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E60" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H60" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I60" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J60" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K60" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L60" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M60" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N60" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O60" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5575,83 +5575,83 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C61" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D61" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E61" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F61" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H61" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J61" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K61" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L61" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M61" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O61" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5692,53 +5692,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>65.76000000000001</v>
+        <v>66.94</v>
       </c>
       <c r="C62" t="n">
-        <v>66.22</v>
+        <v>66.94</v>
       </c>
       <c r="D62" t="n">
-        <v>65.73999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="E62" t="n">
-        <v>66.2</v>
+        <v>66.56</v>
       </c>
       <c r="F62" t="n">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0297</v>
+        <v>0.0166</v>
       </c>
       <c r="H62" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="I62" t="n">
-        <v>62.86</v>
+        <v>65.47</v>
       </c>
       <c r="J62" t="n">
-        <v>63.54</v>
+        <v>65.47</v>
       </c>
       <c r="K62" t="n">
-        <v>63.87</v>
+        <v>65.47</v>
       </c>
       <c r="L62" t="n">
-        <v>64.2</v>
+        <v>65.47</v>
       </c>
       <c r="M62" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N62" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O62" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q62" s="6" t="n">
         <v/>
@@ -5763,15 +5765,103 @@
       </c>
       <c r="V62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>67</v>
+      </c>
+      <c r="D63" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="E63" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I63" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="J63" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="K63" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="L63" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="M63" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="N63" t="n">
+        <v>66.84</v>
+      </c>
+      <c r="O63" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.39</v>
+        <v>58.38</v>
       </c>
       <c r="C2" t="n">
-        <v>59.51</v>
+        <v>58.38</v>
       </c>
       <c r="D2" t="n">
-        <v>57.25</v>
+        <v>58.35</v>
       </c>
       <c r="E2" t="n">
-        <v>58.05</v>
+        <v>58.35</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.97</v>
+        <v>0.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.0051</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>0.04</v>
       </c>
       <c r="I2" t="n">
-        <v>61.88</v>
+        <v>54.99</v>
       </c>
       <c r="J2" t="n">
-        <v>61.97</v>
+        <v>55.62</v>
       </c>
       <c r="K2" t="n">
-        <v>61.99</v>
+        <v>56.92</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>58.22</v>
       </c>
       <c r="M2" t="n">
-        <v>62.06</v>
+        <v>59.18</v>
       </c>
       <c r="N2" t="n">
-        <v>62.11</v>
+        <v>60.15</v>
       </c>
       <c r="O2" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>61.78</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +704,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C3" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I3" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L3" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M3" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N3" t="n">
         <v>58.38</v>
       </c>
-      <c r="C3" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D3" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E3" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I3" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J3" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K3" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L3" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M3" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N3" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O3" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,111 +770,113 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C4" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D4" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E4" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I4" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J4" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K4" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L4" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M4" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N4" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O4" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+        <v>59.24</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -884,134 +884,138 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C5" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D5" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E5" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H5" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I5" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J5" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K5" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L5" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M5" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N5" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O5" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C6" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D6" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E6" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H6" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I6" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J6" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K6" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L6" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M6" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N6" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O6" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,82 +1028,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C7" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D7" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E7" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F7" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I7" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J7" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K7" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L7" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M7" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N7" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O7" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,18 +1107,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1126,7 +1126,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1140,50 +1140,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C8" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D8" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E8" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H8" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J8" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K8" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L8" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M8" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N8" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O8" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,7 +1194,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1210,7 +1210,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1224,69 +1224,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C9" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D9" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E9" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F9" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H9" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J9" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K9" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L9" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M9" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N9" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O9" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>63.6</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1294,73 +1298,69 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C10" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D10" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E10" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H10" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J10" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K10" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L10" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M10" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N10" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O10" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -1368,7 +1368,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1382,7 +1382,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1392,134 +1392,136 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C11" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D11" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E11" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I11" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J11" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K11" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L11" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M11" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N11" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O11" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C12" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D12" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E12" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F12" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I12" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J12" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K12" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L12" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M12" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N12" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O12" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1532,93 +1534,95 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C13" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D13" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E13" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H13" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J13" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K13" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L13" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M13" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N13" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O13" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>60.97</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1630,249 +1634,241 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C14" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D14" t="n">
         <v>57.51</v>
       </c>
       <c r="E14" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H14" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I14" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J14" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K14" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L14" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M14" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N14" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O14" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C15" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D15" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E15" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H15" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I15" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J15" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K15" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L15" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M15" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N15" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O15" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C16" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D16" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E16" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H16" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I16" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J16" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K16" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L16" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M16" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N16" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O16" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1886,7 +1882,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1896,222 +1892,228 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C17" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D17" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E17" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J17" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K17" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L17" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M17" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N17" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O17" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C18" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D18" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E18" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H18" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J18" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K18" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L18" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M18" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N18" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O18" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C19" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D19" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E19" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F19" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H19" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I19" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J19" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K19" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L19" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M19" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N19" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O19" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2122,82 +2124,80 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C20" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D20" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E20" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F20" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H20" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I20" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J20" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K20" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L20" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M20" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N20" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O20" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2208,27 +2208,23 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2238,69 +2234,73 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C21" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D21" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E21" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F21" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H21" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I21" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J21" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K21" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L21" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M21" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N21" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O21" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>60.65</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2328,210 +2328,210 @@
         <v>58.66</v>
       </c>
       <c r="D22" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E22" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H22" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J22" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K22" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L22" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M22" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N22" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O22" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F23" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J23" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K23" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L23" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M23" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N23" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O23" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>58.66</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O24" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2562,7 +2562,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2572,83 +2572,85 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O25" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2656,63 +2658,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C26" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I26" t="n">
         <v>57.86</v>
       </c>
-      <c r="C26" t="n">
+      <c r="J26" t="n">
         <v>57.86</v>
       </c>
-      <c r="D26" t="n">
+      <c r="K26" t="n">
         <v>57.86</v>
       </c>
-      <c r="E26" t="n">
+      <c r="L26" t="n">
         <v>57.86</v>
       </c>
-      <c r="F26" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O26" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2732,154 +2738,148 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C27" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D27" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E27" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H27" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J27" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K27" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L27" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M27" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N27" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O27" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C28" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D28" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E28" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H28" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I28" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J28" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K28" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L28" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M28" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N28" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O28" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2887,14 +2887,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2906,65 +2904,65 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C29" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D29" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E29" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H29" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I29" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J29" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K29" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L29" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N29" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O29" t="n">
         <v>57.93</v>
       </c>
-      <c r="M29" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N29" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O29" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
@@ -2976,76 +2974,78 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C30" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D30" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E30" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F30" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H30" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I30" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J30" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K30" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L30" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M30" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N30" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O30" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3056,7 +3056,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3066,17 +3066,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3086,81 +3084,83 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C31" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D31" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E31" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F31" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H31" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I31" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J31" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K31" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L31" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M31" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N31" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O31" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+        <v>62.8</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3168,83 +3168,83 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C32" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D32" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E32" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H32" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I32" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J32" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K32" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L32" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M32" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N32" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O32" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3252,50 +3252,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C33" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D33" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E33" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F33" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H33" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I33" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J33" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K33" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L33" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M33" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N33" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O33" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3306,7 +3306,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3318,15 +3318,13 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3336,50 +3334,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C34" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D34" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E34" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F34" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I34" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J34" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M34" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O34" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3392,76 +3390,76 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C35" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E35" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J35" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L35" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O35" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3474,76 +3472,78 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C36" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D36" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E36" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F36" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I36" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K36" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M36" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O36" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3551,83 +3551,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J37" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K37" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L37" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N37" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3635,86 +3635,88 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C38" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E38" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I38" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C38" t="n">
+      <c r="J38" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D38" t="n">
+      <c r="K38" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E38" t="n">
+      <c r="L38" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J38" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L38" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M38" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
@@ -3722,7 +3724,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3734,7 +3736,7 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
@@ -3742,7 +3744,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3752,85 +3754,83 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>65.25</v>
       </c>
       <c r="C39" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D39" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E39" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F39" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H39" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I39" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J39" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N39" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O39" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3838,134 +3838,136 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C40" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E40" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H40" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I40" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J40" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K40" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L40" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O40" t="n">
-        <v>67</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C41" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D41" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D41" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E41" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F41" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H41" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I41" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J41" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K41" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L41" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M41" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O41" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3976,82 +3978,76 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F42" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H42" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I42" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J42" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L42" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N42" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O42" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4062,7 +4058,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4078,7 +4074,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4088,50 +4084,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H43" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J43" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L43" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M43" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N43" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O43" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4139,18 +4135,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4158,60 +4154,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C44" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D44" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E44" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I44" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J44" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K44" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L44" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N44" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4221,81 +4221,85 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C45" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D45" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H45" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I45" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K45" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L45" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M45" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N45" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4305,85 +4309,81 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J46" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K46" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L46" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O46" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4391,96 +4391,100 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D47" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E47" t="n">
+        <v>67</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I47" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C47" t="n">
+      <c r="J47" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D47" t="n">
+      <c r="K47" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E47" t="n">
+      <c r="L47" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J47" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K47" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L47" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M47" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4490,173 +4494,169 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H48" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I48" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J48" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K48" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L48" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O48" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W48" s="9" t="inlineStr">
+        <v>76.09</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E49" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H49" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I49" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L49" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M49" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N49" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O49" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>68.52</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4668,7 +4668,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4678,69 +4678,63 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C50" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D50" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E50" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H50" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I50" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J50" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K50" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L50" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O50" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>69.56</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4752,60 +4746,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C51" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D51" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E51" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F51" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H51" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I51" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J51" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K51" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L51" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O51" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4818,76 +4816,78 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C52" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F52" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H52" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I52" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J52" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K52" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M52" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O52" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4895,83 +4895,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C53" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D53" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H53" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I53" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J53" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M53" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N53" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O53" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4979,14 +4979,12 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4998,64 +4996,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C54" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D54" t="n">
         <v>66.3</v>
       </c>
-      <c r="D54" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E54" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F54" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I54" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J54" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K54" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L54" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M54" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O54" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5066,111 +5064,113 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C55" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D55" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E55" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F55" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H55" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I55" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J55" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N55" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O55" t="n">
-        <v>67</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>69.91</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5178,143 +5178,149 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C56" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D56" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E56" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I56" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J56" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K56" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L56" t="n">
         <v>64.28</v>
       </c>
-      <c r="F56" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I56" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J56" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K56" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L56" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M56" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N56" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O56" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C57" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D57" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E57" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F57" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H57" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I57" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J57" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K57" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L57" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M57" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N57" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O57" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -5324,95 +5330,89 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C58" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D58" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E58" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I58" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J58" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K58" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L58" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M58" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N58" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O58" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5426,64 +5426,64 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C59" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E59" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H59" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J59" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K59" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L59" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M59" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N59" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O59" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5491,83 +5491,83 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C60" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D60" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E60" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F60" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H60" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J60" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K60" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L60" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M60" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5578,7 +5578,7 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5598,7 +5598,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5608,53 +5608,55 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C61" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D61" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E61" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I61" t="n">
         <v>65.47</v>
       </c>
-      <c r="C61" t="n">
+      <c r="J61" t="n">
         <v>65.47</v>
       </c>
-      <c r="D61" t="n">
+      <c r="K61" t="n">
         <v>65.47</v>
       </c>
-      <c r="E61" t="n">
+      <c r="L61" t="n">
         <v>65.47</v>
       </c>
-      <c r="F61" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J61" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K61" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L61" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M61" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N61" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O61" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q61" s="6" t="n">
         <v/>
@@ -5662,7 +5664,7 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5679,10 +5681,10 @@
       </c>
       <c r="V61" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5692,65 +5694,65 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>66.94</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>66.94</v>
+        <v>67.56</v>
       </c>
       <c r="D62" t="n">
-        <v>66.56</v>
+        <v>66.2</v>
       </c>
       <c r="E62" t="n">
-        <v>66.56</v>
+        <v>66.53</v>
       </c>
       <c r="F62" t="n">
-        <v>1.09</v>
+        <v>-0.03</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0004</v>
       </c>
       <c r="H62" t="n">
-        <v>0.38</v>
+        <v>1.36</v>
       </c>
       <c r="I62" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J62" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K62" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L62" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N62" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O62" t="n">
-        <v>65.47</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.31999999999999</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
       </c>
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5768,98 +5770,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>66.68000000000001</v>
-      </c>
-      <c r="C63" t="n">
-        <v>67</v>
-      </c>
-      <c r="D63" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="E63" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0089</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I63" t="n">
-        <v>66.17</v>
-      </c>
-      <c r="J63" t="n">
-        <v>66.08</v>
-      </c>
-      <c r="K63" t="n">
-        <v>66.36</v>
-      </c>
-      <c r="L63" t="n">
-        <v>66.65000000000001</v>
-      </c>
-      <c r="M63" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="N63" t="n">
-        <v>66.84</v>
-      </c>
-      <c r="O63" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5698,25 +5698,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>66.68000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="C62" t="n">
-        <v>67.56</v>
+        <v>66.67</v>
       </c>
       <c r="D62" t="n">
-        <v>66.2</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>66.53</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.03</v>
+        <v>-0.73</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.011</v>
       </c>
       <c r="H62" t="n">
-        <v>1.36</v>
+        <v>0.84</v>
       </c>
       <c r="I62" t="n">
         <v>66.17</v>
@@ -5739,11 +5739,15 @@
       <c r="O62" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
@@ -5752,32 +5756,110 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="D63" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I63" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="J63" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="K63" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L63" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="M63" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="N63" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="O63" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5791,13 +5791,13 @@
         <v>65.04000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>66.47</v>
+        <v>66.14</v>
       </c>
       <c r="F63" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0047</v>
       </c>
       <c r="H63" t="n">
         <v>2.28</v>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
@@ -5846,20 +5846,20 @@
       </c>
       <c r="U63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="C2" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I2" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="J2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="L2" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M2" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="N2" t="n">
         <v>58.38</v>
       </c>
-      <c r="C2" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="D2" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E2" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I2" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="J2" t="n">
-        <v>55.62</v>
-      </c>
-      <c r="K2" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="L2" t="n">
-        <v>58.22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="N2" t="n">
-        <v>60.15</v>
-      </c>
       <c r="O2" t="n">
-        <v>61.78</v>
+        <v>58.42</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,109 +690,111 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C3" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D3" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E3" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F3" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I3" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J3" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K3" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L3" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M3" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N3" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O3" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
+        <v>59.24</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -800,77 +802,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C4" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D4" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E4" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H4" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I4" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J4" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K4" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L4" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M4" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N4" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O4" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -879,55 +881,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C5" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D5" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E5" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H5" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I5" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J5" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K5" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L5" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M5" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N5" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O5" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,18 +948,14 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -965,57 +967,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C6" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D6" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E6" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I6" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J6" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K6" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L6" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M6" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N6" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O6" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,18 +1025,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1056,50 +1058,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C7" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D7" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E7" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H7" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I7" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J7" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K7" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L7" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M7" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N7" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O7" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1140,70 +1142,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C8" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D8" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E8" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F8" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H8" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J8" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K8" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L8" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M8" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N8" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O8" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1215,68 +1221,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C9" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D9" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E9" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H9" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J9" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K9" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L9" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M9" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N9" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O9" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -1308,77 +1310,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C10" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D10" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E10" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I10" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J10" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K10" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L10" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M10" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N10" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O10" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1387,55 +1387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C11" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D11" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E11" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F11" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J11" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K11" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L11" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M11" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N11" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O11" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,20 +1450,16 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1471,70 +1471,76 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C12" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D12" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E12" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H12" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I12" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J12" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K12" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L12" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M12" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N12" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O12" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1551,86 +1557,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C13" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D13" t="n">
         <v>57.51</v>
       </c>
       <c r="E13" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H13" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I13" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J13" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K13" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L13" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M13" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N13" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O13" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1639,80 +1639,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C14" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D14" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E14" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H14" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I14" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J14" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K14" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L14" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M14" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N14" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O14" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1721,71 +1725,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C15" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D15" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E15" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H15" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I15" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J15" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K15" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L15" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M15" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N15" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O15" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
@@ -1812,73 +1810,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C16" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D16" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E16" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H16" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J16" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K16" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L16" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M16" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N16" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O16" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1887,70 +1893,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C17" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D17" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E17" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F17" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I17" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J17" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K17" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L17" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M17" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N17" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O17" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1959,16 +1963,16 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
@@ -1977,57 +1981,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C18" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D18" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E18" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F18" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H18" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I18" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J18" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K18" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L18" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M18" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N18" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O18" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2045,75 +2049,73 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C19" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D19" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E19" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F19" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H19" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I19" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J19" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K19" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L19" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M19" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N19" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O19" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2131,18 +2133,14 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2154,79 +2152,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C20" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D20" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E20" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F20" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H20" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I20" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J20" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K20" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L20" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M20" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N20" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O20" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2234,7 +2236,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2244,210 +2246,210 @@
         <v>58.66</v>
       </c>
       <c r="D21" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E21" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H21" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J21" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K21" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L21" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M21" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N21" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O21" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F22" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J22" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K22" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L22" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M22" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N22" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O22" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O23" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -2488,83 +2490,85 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O24" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2572,61 +2576,65 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C25" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I25" t="n">
         <v>57.86</v>
       </c>
-      <c r="C25" t="n">
+      <c r="J25" t="n">
         <v>57.86</v>
       </c>
-      <c r="D25" t="n">
+      <c r="K25" t="n">
         <v>57.86</v>
       </c>
-      <c r="E25" t="n">
+      <c r="L25" t="n">
         <v>57.86</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O25" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2653,90 +2661,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C26" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D26" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E26" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F26" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H26" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I26" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J26" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K26" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L26" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M26" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N26" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O26" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2745,57 +2747,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C27" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D27" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E27" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H27" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I27" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J27" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K27" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L27" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M27" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N27" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O27" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2803,14 +2805,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2829,58 +2829,58 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C28" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D28" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E28" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H28" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I28" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J28" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K28" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L28" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M28" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N28" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O28" t="n">
         <v>57.93</v>
       </c>
-      <c r="M28" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N28" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O28" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
@@ -2890,78 +2890,80 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C29" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D29" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E29" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F29" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H29" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I29" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J29" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K29" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L29" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M29" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N29" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O29" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2982,10 +2984,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
@@ -3002,81 +3002,83 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C30" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D30" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E30" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F30" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H30" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I30" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J30" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K30" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L30" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M30" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N30" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O30" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3084,83 +3086,83 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C31" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D31" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E31" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H31" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I31" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J31" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K31" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L31" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M31" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N31" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O31" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3168,50 +3170,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C32" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D32" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E32" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H32" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J32" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K32" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L32" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M32" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N32" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O32" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3234,13 +3236,11 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3252,50 +3252,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C33" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D33" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E33" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F33" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J33" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M33" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O33" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3306,20 +3306,16 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3329,55 +3325,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C34" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E34" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I34" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J34" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L34" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O34" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3388,78 +3388,80 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C35" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D35" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E35" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F35" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I35" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K35" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M35" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O35" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3467,83 +3469,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J36" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K36" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L36" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N36" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3551,86 +3553,88 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C37" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D37" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I37" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C37" t="n">
+      <c r="J37" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D37" t="n">
+      <c r="K37" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E37" t="n">
+      <c r="L37" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J37" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K37" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L37" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M37" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q37" s="6" t="n">
         <v/>
@@ -3650,7 +3654,7 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V37" s="8" t="inlineStr">
@@ -3668,85 +3672,83 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>65.25</v>
       </c>
       <c r="C38" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D38" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E38" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F38" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H38" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I38" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J38" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N38" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O38" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3754,134 +3756,136 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C39" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E39" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H39" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I39" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J39" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K39" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L39" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O39" t="n">
-        <v>67</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C40" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D40" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D40" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E40" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F40" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H40" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I40" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J40" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K40" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L40" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M40" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O40" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3899,14 +3903,12 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3915,59 +3917,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F41" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H41" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I41" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J41" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L41" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N41" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O41" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -4004,50 +4002,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H42" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J42" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L42" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M42" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N42" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O42" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4055,19 +4053,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4079,55 +4077,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C43" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D43" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E43" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J43" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K43" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L43" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N43" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4137,19 +4139,23 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4161,57 +4167,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C44" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D44" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H44" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I44" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K44" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L44" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M44" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N44" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4221,23 +4227,19 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4249,57 +4251,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H45" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J45" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K45" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L45" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O45" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4307,22 +4309,24 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4331,72 +4335,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D46" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E46" t="n">
+        <v>67</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I46" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C46" t="n">
+      <c r="J46" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D46" t="n">
+      <c r="K46" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E46" t="n">
+      <c r="L46" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J46" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K46" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L46" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M46" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4406,173 +4412,169 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H47" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I47" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J47" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K47" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L47" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O47" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E48" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H48" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I48" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L48" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M48" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N48" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O48" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4594,69 +4596,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C49" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D49" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E49" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H49" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I49" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J49" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K49" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L49" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O49" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4673,55 +4669,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C50" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D50" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E50" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F50" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H50" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I50" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J50" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K50" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L50" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O50" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4732,78 +4732,80 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C51" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F51" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H51" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I51" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J51" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K51" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M51" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O51" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4811,83 +4813,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C52" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D52" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H52" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I52" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J52" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M52" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N52" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O52" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4895,14 +4897,12 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4921,57 +4921,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C53" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D53" t="n">
         <v>66.3</v>
       </c>
-      <c r="D53" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E53" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F53" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H53" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I53" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J53" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K53" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L53" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M53" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O53" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4984,109 +4984,111 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C54" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D54" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E54" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F54" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H54" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I54" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J54" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N54" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O54" t="n">
-        <v>67</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr"/>
@@ -5094,143 +5096,149 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C55" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D55" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E55" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I55" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J55" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K55" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L55" t="n">
         <v>64.28</v>
       </c>
-      <c r="F55" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I55" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J55" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K55" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L55" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M55" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N55" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O55" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C56" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D56" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E56" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F56" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H56" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J56" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K56" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L56" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M56" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N56" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O56" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -5238,20 +5246,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5263,71 +5267,69 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C57" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D57" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E57" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H57" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I57" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J57" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K57" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L57" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M57" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N57" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O57" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5349,57 +5351,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C58" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E58" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H58" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I58" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J58" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K58" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L58" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M58" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N58" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O58" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5407,83 +5409,83 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C59" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D59" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E59" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F59" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H59" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J59" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K59" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L59" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M59" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5524,53 +5526,55 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C60" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D60" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E60" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I60" t="n">
         <v>65.47</v>
       </c>
-      <c r="C60" t="n">
+      <c r="J60" t="n">
         <v>65.47</v>
       </c>
-      <c r="D60" t="n">
+      <c r="K60" t="n">
         <v>65.47</v>
       </c>
-      <c r="E60" t="n">
+      <c r="L60" t="n">
         <v>65.47</v>
       </c>
-      <c r="F60" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J60" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K60" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L60" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M60" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N60" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O60" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q60" s="6" t="n">
         <v/>
@@ -5595,7 +5599,7 @@
       </c>
       <c r="V60" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W60" s="9" t="inlineStr">
@@ -5608,85 +5612,83 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C61" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D61" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H61" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J61" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K61" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L61" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N61" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O61" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5694,174 +5696,86 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>66.44</v>
+        <v>67.61</v>
       </c>
       <c r="C62" t="n">
-        <v>66.67</v>
+        <v>67.75</v>
       </c>
       <c r="D62" t="n">
-        <v>65.81999999999999</v>
+        <v>67.61</v>
       </c>
       <c r="E62" t="n">
-        <v>65.81999999999999</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.73</v>
+        <v>1.89</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0286</v>
       </c>
       <c r="H62" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="I62" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J62" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K62" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M62" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O62" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>66.68000000000001</v>
-      </c>
-      <c r="C63" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="D63" t="n">
-        <v>65.04000000000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I63" t="n">
-        <v>64.98</v>
-      </c>
-      <c r="J63" t="n">
-        <v>64.77</v>
-      </c>
-      <c r="K63" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="L63" t="n">
-        <v>66.03</v>
-      </c>
-      <c r="M63" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="N63" t="n">
-        <v>66.45</v>
-      </c>
-      <c r="O63" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5703,22 +5703,22 @@
         <v>67.61</v>
       </c>
       <c r="C62" t="n">
-        <v>67.75</v>
+        <v>68.06</v>
       </c>
       <c r="D62" t="n">
-        <v>67.61</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>67.70999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="F62" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0286</v>
+        <v>0.0232</v>
       </c>
       <c r="H62" t="n">
-        <v>0.14</v>
+        <v>0.74</v>
       </c>
       <c r="I62" t="n">
         <v>64.98</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5706,19 +5706,19 @@
         <v>68.06</v>
       </c>
       <c r="D62" t="n">
-        <v>67.31999999999999</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>67.36</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0223</v>
       </c>
       <c r="H62" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="I62" t="n">
         <v>64.98</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5706,19 +5706,19 @@
         <v>68.06</v>
       </c>
       <c r="D62" t="n">
-        <v>67.23999999999999</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>67.29000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="F62" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0223</v>
+        <v>0.0175</v>
       </c>
       <c r="H62" t="n">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="I62" t="n">
         <v>64.98</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -5706,19 +5706,19 @@
         <v>68.06</v>
       </c>
       <c r="D62" t="n">
-        <v>66.93000000000001</v>
+        <v>66.86</v>
       </c>
       <c r="E62" t="n">
-        <v>66.98</v>
+        <v>67</v>
       </c>
       <c r="F62" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0179</v>
       </c>
       <c r="H62" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="I62" t="n">
         <v>64.98</v>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5700,25 +5700,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>67.61</v>
+        <v>65.39</v>
       </c>
       <c r="C62" t="n">
-        <v>68.06</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>66.86</v>
+        <v>65.39</v>
       </c>
       <c r="E62" t="n">
-        <v>67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>1.18</v>
+        <v>0.11</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0016</v>
       </c>
       <c r="H62" t="n">
-        <v>1.2</v>
+        <v>0.54</v>
       </c>
       <c r="I62" t="n">
         <v>64.98</v>
@@ -5747,35 +5747,127 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="C63" t="n">
+        <v>68.06</v>
+      </c>
+      <c r="D63" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I63" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="J63" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="K63" t="n">
+        <v>65.66</v>
+      </c>
+      <c r="L63" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>66.61</v>
+      </c>
+      <c r="O63" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,83 +634,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.19</v>
+        <v>58.68</v>
       </c>
       <c r="C2" t="n">
-        <v>59.22</v>
+        <v>59.12</v>
       </c>
       <c r="D2" t="n">
-        <v>59.19</v>
+        <v>57.54</v>
       </c>
       <c r="E2" t="n">
-        <v>59.22</v>
+        <v>58.17</v>
       </c>
       <c r="F2" t="n">
-        <v>0.87</v>
+        <v>-1.04</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0176</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03</v>
+        <v>1.58</v>
       </c>
       <c r="I2" t="n">
-        <v>58.31</v>
+        <v>59.16</v>
       </c>
       <c r="J2" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="K2" t="n">
-        <v>58.33</v>
+        <v>59.2</v>
       </c>
       <c r="L2" t="n">
-        <v>58.36</v>
+        <v>59.21</v>
       </c>
       <c r="M2" t="n">
-        <v>58.37</v>
+        <v>59.23</v>
       </c>
       <c r="N2" t="n">
-        <v>58.38</v>
+        <v>59.25</v>
       </c>
       <c r="O2" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>59.24</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -718,134 +718,138 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C3" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D3" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E3" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H3" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I3" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J3" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K3" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L3" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M3" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N3" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O3" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C4" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D4" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E4" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H4" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I4" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J4" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K4" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L4" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M4" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N4" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O4" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,82 +862,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C5" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D5" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E5" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F5" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I5" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J5" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K5" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L5" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M5" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N5" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O5" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,18 +941,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -960,7 +960,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -974,50 +974,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C6" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D6" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E6" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H6" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J6" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K6" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L6" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M6" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N6" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O6" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,7 +1028,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1044,7 +1044,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1058,69 +1058,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C7" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D7" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E7" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H7" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I7" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J7" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K7" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L7" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M7" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N7" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O7" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>63.6</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1128,73 +1132,69 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C8" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D8" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E8" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H8" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J8" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K8" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L8" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M8" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N8" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O8" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -1202,7 +1202,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1216,7 +1216,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1226,134 +1226,136 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C9" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D9" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E9" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J9" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K9" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L9" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M9" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N9" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O9" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C10" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D10" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E10" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F10" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I10" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J10" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K10" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L10" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M10" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N10" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O10" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1366,93 +1368,95 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C11" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D11" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E11" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H11" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I11" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J11" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K11" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L11" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M11" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N11" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O11" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>60.97</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1464,249 +1468,241 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C12" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D12" t="n">
         <v>57.51</v>
       </c>
       <c r="E12" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H12" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I12" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J12" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K12" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L12" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M12" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N12" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O12" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C13" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D13" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E13" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H13" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I13" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J13" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K13" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L13" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M13" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N13" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O13" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C14" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D14" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E14" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H14" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I14" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J14" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K14" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L14" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M14" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N14" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O14" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1720,7 +1716,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1730,222 +1726,228 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C15" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D15" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E15" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H15" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J15" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K15" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L15" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M15" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N15" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O15" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C16" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D16" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E16" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F16" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J16" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K16" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L16" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M16" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N16" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O16" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C17" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D17" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E17" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F17" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H17" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I17" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J17" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K17" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L17" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M17" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N17" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O17" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1956,82 +1958,80 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C18" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D18" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E18" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F18" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H18" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I18" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J18" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K18" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L18" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M18" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N18" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O18" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2042,27 +2042,23 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2072,69 +2068,73 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C19" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D19" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E19" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F19" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H19" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I19" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J19" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K19" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L19" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M19" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N19" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O19" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>60.65</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2152,7 +2152,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2162,210 +2162,210 @@
         <v>58.66</v>
       </c>
       <c r="D20" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E20" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H20" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J20" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K20" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L20" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M20" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N20" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O20" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F21" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J21" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K21" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L21" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M21" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N21" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O21" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>58.66</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O22" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2396,7 +2396,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2406,83 +2406,85 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O23" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2490,63 +2492,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C24" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E24" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I24" t="n">
         <v>57.86</v>
       </c>
-      <c r="C24" t="n">
+      <c r="J24" t="n">
         <v>57.86</v>
       </c>
-      <c r="D24" t="n">
+      <c r="K24" t="n">
         <v>57.86</v>
       </c>
-      <c r="E24" t="n">
+      <c r="L24" t="n">
         <v>57.86</v>
       </c>
-      <c r="F24" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O24" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2566,154 +2572,148 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C25" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D25" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E25" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F25" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H25" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I25" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J25" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K25" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L25" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M25" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N25" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O25" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C26" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D26" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E26" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H26" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I26" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J26" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K26" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L26" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M26" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N26" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O26" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2721,14 +2721,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2740,65 +2738,65 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C27" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D27" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E27" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H27" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I27" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J27" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K27" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L27" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N27" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O27" t="n">
         <v>57.93</v>
       </c>
-      <c r="M27" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N27" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O27" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
@@ -2810,76 +2808,78 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C28" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D28" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E28" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F28" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H28" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I28" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J28" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K28" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L28" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M28" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N28" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O28" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2890,7 +2890,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2900,17 +2900,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2920,81 +2918,83 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C29" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D29" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E29" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F29" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H29" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J29" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K29" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L29" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M29" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N29" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O29" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>62.8</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -3002,83 +3002,83 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C30" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D30" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E30" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H30" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I30" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J30" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K30" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L30" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M30" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N30" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O30" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3086,50 +3086,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C31" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D31" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E31" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F31" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H31" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I31" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J31" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K31" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L31" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M31" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N31" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O31" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3140,7 +3140,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3152,15 +3152,13 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3170,50 +3168,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C32" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D32" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E32" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F32" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J32" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M32" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O32" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3226,76 +3224,76 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C33" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E33" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J33" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L33" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O33" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3308,76 +3306,78 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C34" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D34" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E34" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F34" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I34" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K34" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M34" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O34" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3385,83 +3385,83 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J35" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K35" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L35" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N35" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3469,86 +3469,88 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C36" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I36" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C36" t="n">
+      <c r="J36" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D36" t="n">
+      <c r="K36" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E36" t="n">
+      <c r="L36" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F36" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J36" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K36" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L36" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M36" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q36" s="6" t="n">
         <v/>
@@ -3556,7 +3558,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3568,7 +3570,7 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V36" s="8" t="inlineStr">
@@ -3576,7 +3578,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3586,85 +3588,83 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>65.25</v>
       </c>
       <c r="C37" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D37" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E37" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F37" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H37" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I37" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J37" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N37" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O37" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3672,134 +3672,136 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C38" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E38" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H38" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I38" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J38" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K38" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L38" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O38" t="n">
-        <v>67</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C39" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D39" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D39" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E39" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F39" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H39" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I39" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J39" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K39" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L39" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M39" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O39" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3810,82 +3812,76 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F40" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H40" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I40" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J40" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L40" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N40" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O40" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3896,7 +3892,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3912,7 +3908,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3922,50 +3918,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H41" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J41" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L41" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M41" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N41" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O41" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3973,18 +3969,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3992,60 +3988,64 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C42" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D42" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E42" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I42" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J42" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K42" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L42" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N42" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4055,81 +4055,85 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C43" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D43" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H43" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K43" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L43" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M43" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N43" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4139,85 +4143,81 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J44" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K44" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L44" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O44" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4225,96 +4225,100 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C45" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D45" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E45" t="n">
+        <v>67</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I45" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C45" t="n">
+      <c r="J45" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D45" t="n">
+      <c r="K45" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E45" t="n">
+      <c r="L45" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J45" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K45" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L45" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M45" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4324,173 +4328,169 @@
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H46" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I46" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J46" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K46" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L46" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O46" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+        <v>76.09</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E47" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H47" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I47" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L47" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M47" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N47" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O47" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>68.52</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4502,7 +4502,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4512,69 +4512,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C48" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D48" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E48" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H48" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I48" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J48" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K48" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L48" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O48" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>69.56</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4586,60 +4580,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C49" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D49" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E49" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F49" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H49" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I49" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J49" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K49" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L49" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O49" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4652,76 +4650,78 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C50" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F50" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H50" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J50" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K50" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M50" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O50" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4729,83 +4729,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W50" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C51" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D51" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H51" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J51" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M51" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N51" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O51" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4813,14 +4813,12 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4832,64 +4830,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C52" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D52" t="n">
         <v>66.3</v>
       </c>
-      <c r="D52" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E52" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F52" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I52" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J52" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K52" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L52" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M52" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O52" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4900,111 +4898,113 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C53" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D53" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E53" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F53" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H53" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I53" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J53" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N53" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O53" t="n">
-        <v>67</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>69.91</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
@@ -5012,143 +5012,149 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C54" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D54" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E54" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I54" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J54" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K54" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L54" t="n">
         <v>64.28</v>
       </c>
-      <c r="F54" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I54" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J54" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K54" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L54" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M54" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N54" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O54" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C55" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D55" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E55" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F55" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H55" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J55" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K55" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L55" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M55" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N55" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O55" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -5158,95 +5164,89 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C56" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D56" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E56" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H56" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I56" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J56" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K56" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L56" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M56" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N56" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O56" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5260,64 +5260,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C57" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E57" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H57" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I57" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J57" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K57" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L57" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M57" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N57" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O57" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5325,83 +5325,83 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C58" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D58" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E58" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F58" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H58" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J58" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K58" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L58" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M58" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5412,7 +5412,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5432,7 +5432,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5442,53 +5442,55 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C59" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D59" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E59" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I59" t="n">
         <v>65.47</v>
       </c>
-      <c r="C59" t="n">
+      <c r="J59" t="n">
         <v>65.47</v>
       </c>
-      <c r="D59" t="n">
+      <c r="K59" t="n">
         <v>65.47</v>
       </c>
-      <c r="E59" t="n">
+      <c r="L59" t="n">
         <v>65.47</v>
       </c>
-      <c r="F59" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J59" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K59" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L59" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M59" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N59" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O59" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q59" s="6" t="n">
         <v/>
@@ -5496,7 +5498,7 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5513,10 +5515,10 @@
       </c>
       <c r="V59" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W59" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5526,85 +5528,83 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C60" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D60" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H60" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I60" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J60" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K60" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L60" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N60" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O60" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5612,69 +5612,65 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>66.44</v>
+        <v>65.39</v>
       </c>
       <c r="C61" t="n">
-        <v>66.67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>65.81999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="E61" t="n">
-        <v>65.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.73</v>
+        <v>0.11</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0016</v>
       </c>
       <c r="H61" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J61" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K61" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M61" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O61" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5686,75 +5682,83 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>65.39</v>
+        <v>64.92</v>
       </c>
       <c r="C62" t="n">
-        <v>65.93000000000001</v>
+        <v>65</v>
       </c>
       <c r="D62" t="n">
-        <v>65.39</v>
+        <v>64.89</v>
       </c>
       <c r="E62" t="n">
-        <v>65.93000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F62" t="n">
-        <v>0.11</v>
+        <v>-0.98</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0149</v>
       </c>
       <c r="H62" t="n">
-        <v>0.54</v>
+        <v>0.1</v>
       </c>
       <c r="I62" t="n">
-        <v>64.98</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>64.77</v>
+        <v>65.53</v>
       </c>
       <c r="K62" t="n">
-        <v>65.40000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="L62" t="n">
-        <v>66.03</v>
+        <v>65.8</v>
       </c>
       <c r="M62" t="n">
-        <v>66.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N62" t="n">
-        <v>66.45</v>
+        <v>66.61</v>
       </c>
       <c r="O62" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+        <v>66.47</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5766,108 +5770,12 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>67.61</v>
-      </c>
-      <c r="C63" t="n">
-        <v>68.06</v>
-      </c>
-      <c r="D63" t="n">
-        <v>65.29000000000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0066</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I63" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="J63" t="n">
-        <v>65.53</v>
-      </c>
-      <c r="K63" t="n">
-        <v>65.66</v>
-      </c>
-      <c r="L63" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="M63" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="N63" t="n">
-        <v>66.61</v>
-      </c>
-      <c r="O63" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,134 +634,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58.68</v>
+        <v>58.34</v>
       </c>
       <c r="C2" t="n">
-        <v>59.12</v>
+        <v>60.4</v>
       </c>
       <c r="D2" t="n">
-        <v>57.54</v>
+        <v>57.03</v>
       </c>
       <c r="E2" t="n">
-        <v>58.17</v>
+        <v>59.48</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0224</v>
       </c>
       <c r="H2" t="n">
-        <v>1.58</v>
+        <v>3.37</v>
       </c>
       <c r="I2" t="n">
-        <v>59.16</v>
+        <v>55.96</v>
       </c>
       <c r="J2" t="n">
-        <v>59.2</v>
+        <v>56.51</v>
       </c>
       <c r="K2" t="n">
-        <v>59.2</v>
+        <v>57.38</v>
       </c>
       <c r="L2" t="n">
-        <v>59.21</v>
+        <v>58.25</v>
       </c>
       <c r="M2" t="n">
-        <v>59.23</v>
+        <v>58.97</v>
       </c>
       <c r="N2" t="n">
-        <v>59.25</v>
+        <v>59.68</v>
       </c>
       <c r="O2" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>60.71</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C3" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D3" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E3" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H3" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I3" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J3" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K3" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L3" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M3" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N3" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O3" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,82 +778,74 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C4" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D4" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E4" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I4" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J4" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K4" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L4" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M4" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N4" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O4" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,18 +853,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -878,62 +874,58 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C5" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D5" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E5" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H5" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I5" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J5" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K5" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L5" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M5" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N5" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O5" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,7 +936,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -962,81 +954,81 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C6" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D6" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E6" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F6" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I6" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J6" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K6" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L6" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M6" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N6" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O6" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>63.6</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1046,7 +1038,7 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1058,59 +1050,59 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C7" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D7" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E7" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H7" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J7" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K7" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L7" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M7" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N7" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O7" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -1118,7 +1110,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1132,7 +1124,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1142,134 +1134,136 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C8" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D8" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E8" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I8" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J8" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K8" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L8" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M8" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N8" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O8" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C9" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D9" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E9" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F9" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I9" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J9" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K9" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L9" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M9" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N9" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O9" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,93 +1276,95 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C10" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D10" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E10" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H10" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I10" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J10" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K10" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L10" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M10" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N10" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O10" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>60.97</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1380,249 +1376,241 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C11" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D11" t="n">
         <v>57.51</v>
       </c>
       <c r="E11" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H11" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I11" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J11" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K11" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L11" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M11" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N11" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O11" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C12" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D12" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E12" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H12" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I12" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J12" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K12" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L12" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M12" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N12" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O12" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C13" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D13" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E13" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H13" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I13" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J13" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K13" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L13" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M13" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N13" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O13" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1636,7 +1624,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1646,222 +1634,228 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C14" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D14" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E14" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J14" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K14" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L14" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M14" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N14" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O14" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C15" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D15" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E15" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I15" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J15" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K15" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L15" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M15" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N15" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O15" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C16" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D16" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E16" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F16" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H16" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I16" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J16" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K16" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L16" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M16" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N16" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O16" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1872,82 +1866,80 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C17" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D17" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E17" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F17" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H17" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I17" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J17" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K17" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L17" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M17" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N17" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O17" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1958,27 +1950,23 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1988,69 +1976,73 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C18" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D18" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E18" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F18" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H18" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I18" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J18" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K18" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L18" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M18" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N18" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O18" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>60.65</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2060,7 +2052,7 @@
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2068,7 +2060,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2078,210 +2070,210 @@
         <v>58.66</v>
       </c>
       <c r="D19" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E19" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H19" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J19" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K19" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L19" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M19" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N19" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O19" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F20" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J20" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K20" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L20" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M20" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N20" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O20" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>58.66</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O21" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -2298,7 +2290,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2312,7 +2304,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2322,83 +2314,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O22" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2406,63 +2400,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C23" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E23" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I23" t="n">
         <v>57.86</v>
       </c>
-      <c r="C23" t="n">
+      <c r="J23" t="n">
         <v>57.86</v>
       </c>
-      <c r="D23" t="n">
+      <c r="K23" t="n">
         <v>57.86</v>
       </c>
-      <c r="E23" t="n">
+      <c r="L23" t="n">
         <v>57.86</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O23" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2482,154 +2480,148 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C24" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D24" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E24" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H24" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I24" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J24" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K24" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L24" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M24" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N24" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O24" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C25" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D25" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E25" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H25" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I25" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J25" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K25" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L25" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M25" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N25" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O25" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2637,14 +2629,12 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2656,65 +2646,65 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C26" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D26" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E26" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H26" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I26" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J26" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K26" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L26" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M26" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N26" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O26" t="n">
         <v>57.93</v>
       </c>
-      <c r="M26" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N26" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O26" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
@@ -2726,76 +2716,78 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C27" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D27" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E27" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F27" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H27" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I27" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J27" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K27" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L27" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M27" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N27" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O27" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2806,7 +2798,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2816,17 +2808,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2836,81 +2826,83 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C28" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D28" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E28" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F28" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H28" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I28" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J28" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K28" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L28" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M28" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N28" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O28" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>62.8</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2918,83 +2910,83 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C29" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D29" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E29" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H29" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I29" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J29" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K29" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L29" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M29" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N29" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O29" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -3002,50 +2994,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C30" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D30" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E30" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F30" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H30" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J30" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K30" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L30" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M30" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N30" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O30" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3056,7 +3048,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3068,15 +3060,13 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3086,50 +3076,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C31" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D31" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E31" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F31" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J31" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M31" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O31" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3142,76 +3132,76 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C32" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E32" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I32" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J32" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L32" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O32" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3224,76 +3214,78 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C33" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D33" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E33" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F33" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I33" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K33" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M33" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O33" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3301,83 +3293,83 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J34" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K34" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L34" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N34" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3385,86 +3377,88 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C35" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D35" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I35" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C35" t="n">
+      <c r="J35" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D35" t="n">
+      <c r="K35" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E35" t="n">
+      <c r="L35" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J35" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K35" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L35" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M35" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q35" s="6" t="n">
         <v/>
@@ -3472,7 +3466,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3484,7 +3478,7 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V35" s="8" t="inlineStr">
@@ -3492,7 +3486,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3502,85 +3496,83 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>65.25</v>
       </c>
       <c r="C36" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D36" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E36" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F36" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H36" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I36" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J36" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N36" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O36" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3588,134 +3580,136 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C37" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E37" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H37" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I37" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J37" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K37" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L37" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O37" t="n">
-        <v>67</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C38" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D38" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D38" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E38" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F38" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H38" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I38" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J38" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K38" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L38" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M38" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O38" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3726,82 +3720,76 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F39" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H39" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I39" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J39" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L39" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N39" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O39" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3812,7 +3800,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3828,7 +3816,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3838,50 +3826,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H40" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J40" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L40" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M40" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N40" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O40" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3889,18 +3877,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3908,60 +3896,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C41" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D41" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E41" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I41" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J41" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K41" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L41" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N41" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3971,81 +3963,85 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C42" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D42" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H42" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I42" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K42" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L42" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M42" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N42" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4055,85 +4051,81 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J43" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K43" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L43" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O43" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4141,96 +4133,100 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D44" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E44" t="n">
+        <v>67</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I44" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C44" t="n">
+      <c r="J44" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D44" t="n">
+      <c r="K44" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E44" t="n">
+      <c r="L44" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J44" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K44" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L44" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M44" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4240,173 +4236,169 @@
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H45" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I45" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J45" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K45" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L45" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O45" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="9" t="inlineStr">
+        <v>76.09</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E46" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H46" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I46" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L46" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M46" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N46" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O46" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>68.52</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4418,7 +4410,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4428,69 +4420,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C47" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D47" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E47" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H47" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I47" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J47" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K47" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L47" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O47" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>69.56</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4502,60 +4488,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C48" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D48" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E48" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F48" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H48" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I48" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J48" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K48" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L48" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O48" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4568,76 +4558,78 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C49" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F49" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H49" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J49" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K49" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M49" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O49" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4645,83 +4637,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C50" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D50" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H50" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I50" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J50" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M50" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N50" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O50" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4729,14 +4721,12 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4748,64 +4738,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C51" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D51" t="n">
         <v>66.3</v>
       </c>
-      <c r="D51" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E51" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F51" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I51" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J51" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K51" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L51" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M51" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O51" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4816,111 +4806,113 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C52" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D52" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E52" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F52" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H52" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I52" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J52" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N52" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O52" t="n">
-        <v>67</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+        <v>69.91</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
@@ -4928,143 +4920,149 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C53" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D53" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E53" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I53" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J53" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K53" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L53" t="n">
         <v>64.28</v>
       </c>
-      <c r="F53" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I53" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J53" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K53" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L53" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M53" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N53" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O53" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C54" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D54" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E54" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F54" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H54" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I54" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J54" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K54" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L54" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M54" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N54" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O54" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5074,95 +5072,89 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C55" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D55" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E55" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I55" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J55" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K55" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L55" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M55" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N55" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O55" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5176,64 +5168,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C56" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E56" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H56" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I56" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J56" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K56" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L56" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M56" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N56" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O56" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5241,83 +5233,83 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C57" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D57" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E57" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F57" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H57" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J57" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K57" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L57" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M57" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5328,7 +5320,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5348,7 +5340,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5358,53 +5350,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C58" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D58" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E58" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I58" t="n">
         <v>65.47</v>
       </c>
-      <c r="C58" t="n">
+      <c r="J58" t="n">
         <v>65.47</v>
       </c>
-      <c r="D58" t="n">
+      <c r="K58" t="n">
         <v>65.47</v>
       </c>
-      <c r="E58" t="n">
+      <c r="L58" t="n">
         <v>65.47</v>
       </c>
-      <c r="F58" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J58" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K58" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L58" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M58" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N58" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O58" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5412,7 +5406,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5429,10 +5423,10 @@
       </c>
       <c r="V58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5442,85 +5436,83 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C59" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D59" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H59" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I59" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J59" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K59" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L59" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N59" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O59" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5528,69 +5520,65 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66.44</v>
+        <v>65.39</v>
       </c>
       <c r="C60" t="n">
-        <v>66.67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>65.81999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="E60" t="n">
-        <v>65.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.73</v>
+        <v>0.11</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0016</v>
       </c>
       <c r="H60" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="I60" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J60" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K60" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M60" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O60" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5602,79 +5590,89 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>65.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C61" t="n">
-        <v>65.93000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="D61" t="n">
-        <v>65.39</v>
+        <v>64.38</v>
       </c>
       <c r="E61" t="n">
-        <v>65.93000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="F61" t="n">
-        <v>0.11</v>
+        <v>-1.55</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0235</v>
       </c>
       <c r="H61" t="n">
-        <v>0.54</v>
+        <v>1.84</v>
       </c>
       <c r="I61" t="n">
-        <v>64.98</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>64.77</v>
+        <v>65.53</v>
       </c>
       <c r="K61" t="n">
-        <v>65.40000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="L61" t="n">
-        <v>66.03</v>
+        <v>65.8</v>
       </c>
       <c r="M61" t="n">
-        <v>66.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N61" t="n">
-        <v>66.45</v>
+        <v>66.61</v>
       </c>
       <c r="O61" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>66.47</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5682,7 +5680,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5696,69 +5694,63 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64.92</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>64.28</v>
       </c>
       <c r="D62" t="n">
-        <v>64.89</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>64.95</v>
+        <v>64.19</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0029</v>
       </c>
       <c r="H62" t="n">
         <v>0.1</v>
       </c>
       <c r="I62" t="n">
-        <v>64.84999999999999</v>
+        <v>62.54</v>
       </c>
       <c r="J62" t="n">
-        <v>65.53</v>
+        <v>62.08</v>
       </c>
       <c r="K62" t="n">
-        <v>65.66</v>
+        <v>63.46</v>
       </c>
       <c r="L62" t="n">
-        <v>65.8</v>
+        <v>64.84</v>
       </c>
       <c r="M62" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="N62" t="n">
-        <v>66.61</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>68.06</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5770,7 +5762,7 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58.34</v>
+        <v>58.87</v>
       </c>
       <c r="C2" t="n">
-        <v>60.4</v>
+        <v>60.42</v>
       </c>
       <c r="D2" t="n">
-        <v>57.03</v>
+        <v>57.33</v>
       </c>
       <c r="E2" t="n">
-        <v>59.48</v>
+        <v>60.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0224</v>
+        <v>0.0102</v>
       </c>
       <c r="H2" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="I2" t="n">
-        <v>55.96</v>
+        <v>53.67</v>
       </c>
       <c r="J2" t="n">
-        <v>56.51</v>
+        <v>56.49</v>
       </c>
       <c r="K2" t="n">
-        <v>57.38</v>
+        <v>57.79</v>
       </c>
       <c r="L2" t="n">
-        <v>58.25</v>
+        <v>59.1</v>
       </c>
       <c r="M2" t="n">
-        <v>58.97</v>
+        <v>61.16</v>
       </c>
       <c r="N2" t="n">
-        <v>59.68</v>
+        <v>63.22</v>
       </c>
       <c r="O2" t="n">
-        <v>60.71</v>
+        <v>63.77</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,18 +692,14 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -713,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C3" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D3" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E3" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F3" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I3" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J3" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K3" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L3" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M3" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N3" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O3" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -802,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C4" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D4" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E4" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H4" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J4" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K4" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L4" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M4" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N4" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O4" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -882,70 +874,74 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C5" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D5" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E5" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F5" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H5" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J5" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K5" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L5" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M5" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N5" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O5" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -957,64 +953,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C6" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D6" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E6" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H6" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J6" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K6" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L6" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M6" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N6" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O6" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -1036,91 +1036,85 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C7" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D7" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E7" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J7" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K7" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L7" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M7" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N7" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O7" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1129,55 +1123,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C8" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D8" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E8" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F8" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I8" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J8" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K8" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L8" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M8" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N8" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O8" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,20 +1186,16 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1213,70 +1207,76 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C9" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D9" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E9" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H9" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I9" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J9" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K9" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L9" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M9" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N9" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O9" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1293,86 +1293,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C10" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D10" t="n">
         <v>57.51</v>
       </c>
       <c r="E10" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H10" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I10" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J10" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K10" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L10" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M10" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N10" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O10" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1381,80 +1375,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C11" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D11" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E11" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H11" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I11" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J11" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K11" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L11" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M11" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N11" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O11" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1463,71 +1461,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C12" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D12" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E12" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H12" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I12" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J12" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K12" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L12" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M12" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N12" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O12" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1554,73 +1546,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C13" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D13" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E13" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H13" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J13" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K13" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L13" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M13" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N13" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O13" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1629,70 +1629,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C14" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D14" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E14" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J14" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K14" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L14" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M14" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N14" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O14" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1701,16 +1699,16 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
@@ -1719,57 +1717,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C15" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D15" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E15" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F15" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H15" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I15" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J15" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K15" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L15" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M15" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N15" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O15" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,75 +1785,73 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C16" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D16" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E16" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F16" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H16" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J16" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K16" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L16" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M16" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N16" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O16" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1873,18 +1869,14 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1896,79 +1888,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C17" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D17" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E17" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F17" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H17" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I17" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J17" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K17" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L17" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M17" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N17" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O17" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1976,7 +1972,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1986,210 +1982,210 @@
         <v>58.66</v>
       </c>
       <c r="D18" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E18" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H18" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J18" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K18" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L18" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M18" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N18" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O18" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F19" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J19" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K19" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L19" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M19" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N19" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O19" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O20" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -2230,83 +2226,85 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O21" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2314,61 +2312,65 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C22" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E22" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I22" t="n">
         <v>57.86</v>
       </c>
-      <c r="C22" t="n">
+      <c r="J22" t="n">
         <v>57.86</v>
       </c>
-      <c r="D22" t="n">
+      <c r="K22" t="n">
         <v>57.86</v>
       </c>
-      <c r="E22" t="n">
+      <c r="L22" t="n">
         <v>57.86</v>
       </c>
-      <c r="F22" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O22" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
@@ -2395,90 +2397,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C23" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D23" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E23" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F23" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H23" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I23" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J23" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K23" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L23" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M23" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N23" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O23" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2487,57 +2483,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C24" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D24" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E24" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H24" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I24" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J24" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K24" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L24" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M24" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N24" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O24" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2545,14 +2541,12 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2571,58 +2565,58 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C25" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D25" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E25" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H25" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I25" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J25" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K25" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L25" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N25" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O25" t="n">
         <v>57.93</v>
       </c>
-      <c r="M25" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N25" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O25" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
@@ -2632,78 +2626,80 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C26" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D26" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E26" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F26" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H26" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I26" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J26" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K26" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L26" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M26" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N26" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O26" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2724,10 +2720,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="inlineStr">
         <is>
@@ -2744,81 +2738,83 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C27" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D27" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E27" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F27" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H27" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I27" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J27" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K27" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L27" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M27" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N27" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O27" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2826,83 +2822,83 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C28" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D28" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E28" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H28" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I28" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J28" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K28" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L28" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M28" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N28" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O28" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2910,50 +2906,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C29" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D29" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E29" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F29" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H29" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I29" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J29" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K29" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L29" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M29" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N29" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O29" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2976,13 +2972,11 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2994,50 +2988,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C30" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D30" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E30" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F30" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I30" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J30" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M30" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O30" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3048,20 +3042,16 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3071,55 +3061,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C31" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E31" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I31" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J31" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L31" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O31" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3130,78 +3124,80 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C32" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D32" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E32" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F32" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I32" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K32" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M32" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O32" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,83 +3205,83 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J33" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K33" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L33" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N33" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3293,86 +3289,88 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C34" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D34" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E34" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I34" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C34" t="n">
+      <c r="J34" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D34" t="n">
+      <c r="K34" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E34" t="n">
+      <c r="L34" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F34" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J34" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K34" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L34" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M34" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q34" s="6" t="n">
         <v/>
@@ -3392,7 +3390,7 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
@@ -3410,85 +3408,83 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>65.25</v>
       </c>
       <c r="C35" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D35" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E35" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F35" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H35" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I35" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J35" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N35" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O35" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3496,134 +3492,136 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C36" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E36" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H36" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I36" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J36" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K36" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L36" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O36" t="n">
-        <v>67</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C37" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D37" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D37" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E37" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F37" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H37" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I37" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J37" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K37" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L37" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M37" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O37" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3641,14 +3639,12 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3657,59 +3653,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F38" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H38" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I38" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J38" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L38" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N38" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O38" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3746,50 +3738,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H39" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J39" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L39" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M39" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N39" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O39" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3797,19 +3789,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3821,55 +3813,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C40" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D40" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E40" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I40" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J40" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K40" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L40" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N40" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3879,19 +3875,23 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3903,57 +3903,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C41" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D41" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H41" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I41" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K41" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L41" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M41" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N41" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3963,23 +3963,19 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3991,57 +3987,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J42" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K42" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L42" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O42" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4049,22 +4045,24 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4073,72 +4071,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D43" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E43" t="n">
+        <v>67</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I43" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C43" t="n">
+      <c r="J43" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D43" t="n">
+      <c r="K43" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E43" t="n">
+      <c r="L43" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J43" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K43" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L43" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M43" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4148,173 +4148,169 @@
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H44" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J44" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K44" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L44" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O44" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E45" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H45" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I45" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L45" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M45" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N45" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O45" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4336,69 +4332,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C46" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D46" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E46" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I46" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J46" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K46" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L46" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O46" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4415,55 +4405,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C47" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D47" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E47" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F47" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H47" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I47" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J47" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K47" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L47" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O47" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4474,78 +4468,80 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C48" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F48" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H48" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J48" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K48" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M48" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O48" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,83 +4549,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C49" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D49" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H49" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I49" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J49" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M49" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N49" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O49" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4637,14 +4633,12 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4663,57 +4657,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C50" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D50" t="n">
         <v>66.3</v>
       </c>
-      <c r="D50" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E50" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F50" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I50" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J50" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K50" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L50" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M50" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O50" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4726,109 +4720,111 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C51" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D51" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E51" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F51" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H51" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I51" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J51" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N51" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O51" t="n">
-        <v>67</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr"/>
@@ -4836,143 +4832,149 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C52" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D52" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E52" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I52" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J52" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K52" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L52" t="n">
         <v>64.28</v>
       </c>
-      <c r="F52" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I52" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J52" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K52" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L52" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M52" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N52" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O52" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C53" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D53" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E53" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F53" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H53" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I53" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J53" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K53" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L53" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M53" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N53" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O53" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4980,20 +4982,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -5005,71 +5003,69 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C54" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D54" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E54" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H54" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I54" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J54" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K54" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L54" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M54" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N54" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O54" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5091,57 +5087,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C55" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E55" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H55" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I55" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J55" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K55" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L55" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M55" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N55" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O55" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5149,83 +5145,83 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C56" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D56" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E56" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F56" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H56" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J56" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K56" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L56" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M56" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5266,53 +5262,55 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C57" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D57" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E57" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I57" t="n">
         <v>65.47</v>
       </c>
-      <c r="C57" t="n">
+      <c r="J57" t="n">
         <v>65.47</v>
       </c>
-      <c r="D57" t="n">
+      <c r="K57" t="n">
         <v>65.47</v>
       </c>
-      <c r="E57" t="n">
+      <c r="L57" t="n">
         <v>65.47</v>
       </c>
-      <c r="F57" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J57" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K57" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L57" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M57" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N57" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O57" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q57" s="6" t="n">
         <v/>
@@ -5337,7 +5335,7 @@
       </c>
       <c r="V57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
@@ -5350,85 +5348,83 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C58" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D58" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H58" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I58" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J58" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K58" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L58" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N58" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O58" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -5436,60 +5432,56 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66.44</v>
+        <v>65.39</v>
       </c>
       <c r="C59" t="n">
-        <v>66.67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>65.81999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="E59" t="n">
-        <v>65.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.73</v>
+        <v>0.11</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0016</v>
       </c>
       <c r="H59" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="I59" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J59" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K59" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M59" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O59" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5498,7 +5490,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5515,61 +5507,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>65.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>65.93000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="D60" t="n">
-        <v>65.39</v>
+        <v>64.38</v>
       </c>
       <c r="E60" t="n">
-        <v>65.93000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="F60" t="n">
-        <v>0.11</v>
+        <v>-1.55</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0235</v>
       </c>
       <c r="H60" t="n">
-        <v>0.54</v>
+        <v>1.84</v>
       </c>
       <c r="I60" t="n">
-        <v>64.98</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>64.77</v>
+        <v>65.53</v>
       </c>
       <c r="K60" t="n">
-        <v>65.40000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="L60" t="n">
-        <v>66.03</v>
+        <v>65.8</v>
       </c>
       <c r="M60" t="n">
-        <v>66.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N60" t="n">
-        <v>66.45</v>
+        <v>66.61</v>
       </c>
       <c r="O60" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>66.47</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5578,11 +5578,13 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5604,75 +5606,69 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>66.20999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="C61" t="n">
-        <v>66.22</v>
+        <v>63.63</v>
       </c>
       <c r="D61" t="n">
-        <v>64.38</v>
+        <v>63</v>
       </c>
       <c r="E61" t="n">
-        <v>64.38</v>
+        <v>63.46</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.55</v>
+        <v>-0.93</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0144</v>
       </c>
       <c r="H61" t="n">
-        <v>1.84</v>
+        <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>64.84999999999999</v>
+        <v>62.54</v>
       </c>
       <c r="J61" t="n">
-        <v>65.53</v>
+        <v>62.08</v>
       </c>
       <c r="K61" t="n">
-        <v>65.66</v>
+        <v>63.46</v>
       </c>
       <c r="L61" t="n">
-        <v>65.8</v>
+        <v>64.84</v>
       </c>
       <c r="M61" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="N61" t="n">
-        <v>66.61</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>68.06</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5685,59 +5681,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64.26000000000001</v>
+        <v>63.63</v>
       </c>
       <c r="C62" t="n">
-        <v>64.28</v>
+        <v>64.25</v>
       </c>
       <c r="D62" t="n">
-        <v>64.18000000000001</v>
+        <v>63.62</v>
       </c>
       <c r="E62" t="n">
-        <v>64.19</v>
+        <v>64.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.19</v>
+        <v>0.79</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0029</v>
+        <v>0.0124</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="I62" t="n">
-        <v>62.54</v>
+        <v>62.37</v>
       </c>
       <c r="J62" t="n">
-        <v>62.08</v>
+        <v>62.89</v>
       </c>
       <c r="K62" t="n">
-        <v>63.46</v>
+        <v>63.14</v>
       </c>
       <c r="L62" t="n">
-        <v>64.84</v>
+        <v>63.39</v>
       </c>
       <c r="M62" t="n">
-        <v>65.3</v>
+        <v>63.77</v>
       </c>
       <c r="N62" t="n">
-        <v>65.76000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="O62" t="n">
-        <v>68.06</v>
+        <v>64.27</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5748,26 +5740,114 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="C63" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="D63" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="E63" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I63" t="n">
+        <v>63</v>
+      </c>
+      <c r="J63" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="K63" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="L63" t="n">
+        <v>64.09</v>
+      </c>
+      <c r="M63" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="N63" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="O63" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58.87</v>
+        <v>59.47</v>
       </c>
       <c r="C2" t="n">
-        <v>60.42</v>
+        <v>61.6</v>
       </c>
       <c r="D2" t="n">
-        <v>57.33</v>
+        <v>59.47</v>
       </c>
       <c r="E2" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="F2" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>3.09</v>
+        <v>2.13</v>
       </c>
       <c r="I2" t="n">
-        <v>53.67</v>
+        <v>54.23</v>
       </c>
       <c r="J2" t="n">
-        <v>56.49</v>
+        <v>57.6</v>
       </c>
       <c r="K2" t="n">
-        <v>57.79</v>
+        <v>58.54</v>
       </c>
       <c r="L2" t="n">
-        <v>59.1</v>
+        <v>59.48</v>
       </c>
       <c r="M2" t="n">
-        <v>61.16</v>
+        <v>61.63</v>
       </c>
       <c r="N2" t="n">
-        <v>63.22</v>
+        <v>63.79</v>
       </c>
       <c r="O2" t="n">
-        <v>63.77</v>
+        <v>63.51</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -714,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C3" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D3" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E3" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H3" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I3" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J3" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K3" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L3" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M3" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N3" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O3" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -794,70 +794,74 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C4" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D4" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E4" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F4" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H4" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J4" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K4" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L4" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M4" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N4" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O4" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -869,64 +873,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C5" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D5" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E5" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H5" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J5" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K5" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L5" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M5" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N5" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O5" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -948,91 +956,85 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C6" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D6" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E6" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J6" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K6" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L6" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M6" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N6" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O6" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1041,55 +1043,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C7" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D7" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E7" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F7" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I7" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J7" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K7" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L7" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M7" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N7" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O7" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,20 +1106,16 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1125,70 +1127,76 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C8" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D8" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E8" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H8" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I8" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J8" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K8" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L8" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M8" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N8" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O8" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1205,86 +1213,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C9" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D9" t="n">
         <v>57.51</v>
       </c>
       <c r="E9" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H9" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I9" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J9" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K9" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L9" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M9" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N9" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O9" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1293,80 +1295,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C10" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D10" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E10" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H10" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I10" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J10" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K10" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L10" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M10" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N10" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O10" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1375,71 +1381,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C11" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D11" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E11" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H11" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I11" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J11" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K11" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L11" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M11" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N11" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O11" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1466,73 +1466,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C12" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D12" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E12" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H12" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J12" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K12" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L12" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M12" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N12" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O12" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1541,70 +1549,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C13" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D13" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E13" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F13" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I13" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J13" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K13" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L13" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M13" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N13" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O13" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
@@ -1613,16 +1619,16 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
@@ -1631,57 +1637,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C14" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D14" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E14" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F14" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H14" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I14" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J14" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K14" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L14" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M14" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N14" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O14" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,75 +1705,73 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C15" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D15" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E15" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F15" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H15" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J15" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K15" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L15" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M15" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N15" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O15" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,18 +1789,14 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1808,79 +1808,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C16" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D16" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E16" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H16" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I16" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J16" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K16" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L16" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M16" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N16" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O16" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1888,7 +1892,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1898,210 +1902,210 @@
         <v>58.66</v>
       </c>
       <c r="D17" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E17" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H17" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J17" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K17" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L17" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M17" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N17" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O17" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F18" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J18" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K18" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L18" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M18" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N18" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O18" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O19" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -2142,83 +2146,85 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O20" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2226,61 +2232,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C21" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E21" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I21" t="n">
         <v>57.86</v>
       </c>
-      <c r="C21" t="n">
+      <c r="J21" t="n">
         <v>57.86</v>
       </c>
-      <c r="D21" t="n">
+      <c r="K21" t="n">
         <v>57.86</v>
       </c>
-      <c r="E21" t="n">
+      <c r="L21" t="n">
         <v>57.86</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O21" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
@@ -2307,90 +2317,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C22" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D22" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E22" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H22" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I22" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J22" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K22" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L22" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M22" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N22" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O22" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2399,57 +2403,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C23" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D23" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E23" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H23" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I23" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J23" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K23" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L23" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M23" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N23" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O23" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2457,14 +2461,12 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2483,58 +2485,58 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C24" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D24" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E24" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H24" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I24" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J24" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K24" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L24" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N24" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O24" t="n">
         <v>57.93</v>
       </c>
-      <c r="M24" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N24" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O24" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
@@ -2544,78 +2546,80 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C25" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D25" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E25" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F25" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H25" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I25" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J25" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K25" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L25" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M25" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N25" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O25" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2636,10 +2640,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
@@ -2656,81 +2658,83 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C26" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D26" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E26" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F26" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H26" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I26" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J26" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K26" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L26" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M26" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N26" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O26" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2738,83 +2742,83 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C27" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D27" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E27" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H27" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I27" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J27" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K27" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L27" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M27" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N27" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O27" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2822,50 +2826,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C28" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D28" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E28" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F28" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H28" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J28" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K28" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L28" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M28" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N28" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O28" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2888,13 +2892,11 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2906,50 +2908,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C29" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D29" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E29" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F29" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J29" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M29" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O29" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2960,20 +2962,16 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2983,55 +2981,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C30" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E30" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I30" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J30" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L30" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O30" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3042,78 +3044,80 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C31" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D31" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E31" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F31" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I31" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K31" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M31" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O31" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,83 +3125,83 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J32" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K32" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L32" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N32" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,86 +3209,88 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C33" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D33" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E33" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I33" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C33" t="n">
+      <c r="J33" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="K33" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E33" t="n">
+      <c r="L33" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J33" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K33" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L33" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M33" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q33" s="6" t="n">
         <v/>
@@ -3304,7 +3310,7 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V33" s="8" t="inlineStr">
@@ -3322,85 +3328,83 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>65.25</v>
       </c>
       <c r="C34" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D34" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E34" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F34" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H34" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I34" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J34" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N34" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O34" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3408,134 +3412,136 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C35" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E35" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H35" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I35" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J35" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K35" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L35" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O35" t="n">
-        <v>67</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C36" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D36" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D36" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E36" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F36" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H36" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I36" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J36" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K36" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L36" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M36" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O36" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3553,14 +3559,12 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3569,59 +3573,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F37" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H37" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I37" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J37" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L37" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N37" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O37" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3658,50 +3658,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H38" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J38" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L38" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M38" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N38" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O38" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3709,19 +3709,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3733,55 +3733,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C39" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D39" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E39" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I39" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J39" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K39" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L39" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N39" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3791,19 +3795,23 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3815,57 +3823,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C40" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D40" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H40" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I40" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K40" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L40" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M40" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N40" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3875,23 +3883,19 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3903,57 +3907,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J41" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K41" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L41" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O41" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3961,22 +3965,24 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3985,72 +3991,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D42" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E42" t="n">
+        <v>67</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I42" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C42" t="n">
+      <c r="J42" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D42" t="n">
+      <c r="K42" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E42" t="n">
+      <c r="L42" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J42" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K42" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L42" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M42" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4060,173 +4068,169 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H43" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I43" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J43" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K43" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L43" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O43" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E44" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H44" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I44" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L44" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M44" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N44" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O44" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4248,69 +4252,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C45" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D45" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E45" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H45" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I45" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J45" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K45" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L45" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O45" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4327,55 +4325,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C46" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D46" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E46" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F46" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H46" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I46" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J46" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K46" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L46" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O46" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4386,78 +4388,80 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C47" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F47" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H47" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J47" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K47" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M47" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O47" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,83 +4469,83 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C48" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D48" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H48" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I48" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J48" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M48" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N48" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O48" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4549,14 +4553,12 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4575,57 +4577,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C49" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D49" t="n">
         <v>66.3</v>
       </c>
-      <c r="D49" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E49" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F49" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I49" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J49" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K49" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L49" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M49" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O49" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4638,109 +4640,111 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C50" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D50" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E50" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F50" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H50" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I50" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J50" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N50" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O50" t="n">
-        <v>67</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -4748,143 +4752,149 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C51" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D51" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E51" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I51" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J51" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K51" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L51" t="n">
         <v>64.28</v>
       </c>
-      <c r="F51" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I51" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J51" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K51" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L51" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M51" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N51" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O51" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C52" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D52" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E52" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F52" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H52" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I52" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J52" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K52" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L52" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M52" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N52" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O52" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4892,20 +4902,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4917,71 +4923,69 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C53" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D53" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E53" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H53" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I53" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J53" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K53" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L53" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M53" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N53" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O53" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5003,57 +5007,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C54" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E54" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H54" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I54" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J54" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K54" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L54" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M54" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N54" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O54" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5061,83 +5065,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C55" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D55" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E55" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F55" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H55" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J55" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K55" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L55" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M55" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5178,53 +5182,55 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C56" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D56" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E56" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I56" t="n">
         <v>65.47</v>
       </c>
-      <c r="C56" t="n">
+      <c r="J56" t="n">
         <v>65.47</v>
       </c>
-      <c r="D56" t="n">
+      <c r="K56" t="n">
         <v>65.47</v>
       </c>
-      <c r="E56" t="n">
+      <c r="L56" t="n">
         <v>65.47</v>
       </c>
-      <c r="F56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J56" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K56" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L56" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M56" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N56" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O56" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q56" s="6" t="n">
         <v/>
@@ -5249,7 +5255,7 @@
       </c>
       <c r="V56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W56" s="9" t="inlineStr">
@@ -5262,85 +5268,83 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C57" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D57" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H57" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I57" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J57" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K57" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L57" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N57" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O57" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -5348,60 +5352,56 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66.44</v>
+        <v>65.39</v>
       </c>
       <c r="C58" t="n">
-        <v>66.67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>65.81999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="E58" t="n">
-        <v>65.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.73</v>
+        <v>0.11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0016</v>
       </c>
       <c r="H58" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="I58" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J58" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K58" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M58" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O58" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5427,61 +5427,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>65.93000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="D59" t="n">
-        <v>65.39</v>
+        <v>64.38</v>
       </c>
       <c r="E59" t="n">
-        <v>65.93000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="F59" t="n">
-        <v>0.11</v>
+        <v>-1.55</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0235</v>
       </c>
       <c r="H59" t="n">
-        <v>0.54</v>
+        <v>1.84</v>
       </c>
       <c r="I59" t="n">
-        <v>64.98</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>64.77</v>
+        <v>65.53</v>
       </c>
       <c r="K59" t="n">
-        <v>65.40000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="L59" t="n">
-        <v>66.03</v>
+        <v>65.8</v>
       </c>
       <c r="M59" t="n">
-        <v>66.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N59" t="n">
-        <v>66.45</v>
+        <v>66.61</v>
       </c>
       <c r="O59" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>66.47</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5490,11 +5498,13 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5516,75 +5526,69 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66.20999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="C60" t="n">
-        <v>66.22</v>
+        <v>63.63</v>
       </c>
       <c r="D60" t="n">
-        <v>64.38</v>
+        <v>63</v>
       </c>
       <c r="E60" t="n">
-        <v>64.38</v>
+        <v>63.46</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.55</v>
+        <v>-0.93</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0144</v>
       </c>
       <c r="H60" t="n">
-        <v>1.84</v>
+        <v>0.63</v>
       </c>
       <c r="I60" t="n">
-        <v>64.84999999999999</v>
+        <v>62.54</v>
       </c>
       <c r="J60" t="n">
-        <v>65.53</v>
+        <v>62.08</v>
       </c>
       <c r="K60" t="n">
-        <v>65.66</v>
+        <v>63.46</v>
       </c>
       <c r="L60" t="n">
-        <v>65.8</v>
+        <v>64.84</v>
       </c>
       <c r="M60" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="N60" t="n">
-        <v>66.61</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>68.06</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5597,59 +5601,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.4</v>
+        <v>63.63</v>
       </c>
       <c r="C61" t="n">
-        <v>63.63</v>
+        <v>64.25</v>
       </c>
       <c r="D61" t="n">
-        <v>63</v>
+        <v>63.62</v>
       </c>
       <c r="E61" t="n">
-        <v>63.46</v>
+        <v>64.25</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0124</v>
       </c>
       <c r="H61" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I61" t="n">
-        <v>62.54</v>
+        <v>62.37</v>
       </c>
       <c r="J61" t="n">
-        <v>62.08</v>
+        <v>62.89</v>
       </c>
       <c r="K61" t="n">
-        <v>63.46</v>
+        <v>63.14</v>
       </c>
       <c r="L61" t="n">
-        <v>64.84</v>
+        <v>63.39</v>
       </c>
       <c r="M61" t="n">
-        <v>65.3</v>
+        <v>63.77</v>
       </c>
       <c r="N61" t="n">
-        <v>65.76000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="O61" t="n">
-        <v>68.06</v>
+        <v>64.27</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5657,28 +5657,32 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5686,168 +5690,86 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63.63</v>
+        <v>61.03</v>
       </c>
       <c r="C62" t="n">
-        <v>64.25</v>
+        <v>61.13</v>
       </c>
       <c r="D62" t="n">
-        <v>63.62</v>
+        <v>61.01</v>
       </c>
       <c r="E62" t="n">
-        <v>64.25</v>
+        <v>61.12</v>
       </c>
       <c r="F62" t="n">
-        <v>0.79</v>
+        <v>-3.12</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0486</v>
       </c>
       <c r="H62" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="I62" t="n">
-        <v>62.37</v>
+        <v>63</v>
       </c>
       <c r="J62" t="n">
-        <v>62.89</v>
+        <v>63.78</v>
       </c>
       <c r="K62" t="n">
-        <v>63.14</v>
+        <v>63.94</v>
       </c>
       <c r="L62" t="n">
-        <v>63.39</v>
+        <v>64.09</v>
       </c>
       <c r="M62" t="n">
-        <v>63.77</v>
+        <v>64.56</v>
       </c>
       <c r="N62" t="n">
-        <v>64.16</v>
+        <v>65.02</v>
       </c>
       <c r="O62" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
+        <v>64.87</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="C63" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="D63" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="E63" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.008699999999999999</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I63" t="n">
-        <v>63</v>
-      </c>
-      <c r="J63" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="K63" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="L63" t="n">
-        <v>64.09</v>
-      </c>
-      <c r="M63" t="n">
-        <v>64.56</v>
-      </c>
-      <c r="N63" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="O63" t="n">
-        <v>64.87</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.47</v>
+        <v>62.62</v>
       </c>
       <c r="C2" t="n">
-        <v>61.6</v>
+        <v>62.62</v>
       </c>
       <c r="D2" t="n">
-        <v>59.47</v>
+        <v>61.63</v>
       </c>
       <c r="E2" t="n">
-        <v>60.64</v>
+        <v>61.92</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0211</v>
       </c>
       <c r="H2" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I2" t="n">
-        <v>54.23</v>
+        <v>57.33</v>
       </c>
       <c r="J2" t="n">
-        <v>57.6</v>
+        <v>58.57</v>
       </c>
       <c r="K2" t="n">
-        <v>58.54</v>
+        <v>59.58</v>
       </c>
       <c r="L2" t="n">
-        <v>59.48</v>
+        <v>60.59</v>
       </c>
       <c r="M2" t="n">
-        <v>61.63</v>
+        <v>61.71</v>
       </c>
       <c r="N2" t="n">
-        <v>63.79</v>
+        <v>62.83</v>
       </c>
       <c r="O2" t="n">
-        <v>63.51</v>
+        <v>63.73</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -714,70 +714,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C3" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D3" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E3" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F3" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H3" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J3" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K3" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L3" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M3" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N3" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O3" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>63.6</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -789,64 +793,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C4" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D4" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E4" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H4" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J4" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K4" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L4" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M4" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N4" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O4" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -868,91 +876,85 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C5" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D5" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E5" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I5" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J5" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K5" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L5" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M5" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N5" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O5" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -961,55 +963,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C6" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D6" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E6" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F6" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J6" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K6" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L6" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M6" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N6" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O6" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,20 +1026,16 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1045,70 +1047,76 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C7" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D7" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E7" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H7" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J7" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K7" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L7" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M7" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N7" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O7" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1125,86 +1133,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C8" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D8" t="n">
         <v>57.51</v>
       </c>
       <c r="E8" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H8" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I8" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J8" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K8" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L8" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M8" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N8" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O8" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1213,80 +1215,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C9" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D9" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E9" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H9" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J9" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K9" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L9" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M9" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N9" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O9" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1295,71 +1301,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C10" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D10" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E10" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I10" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J10" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K10" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L10" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M10" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N10" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O10" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
@@ -1386,73 +1386,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C11" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D11" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E11" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J11" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K11" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L11" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M11" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N11" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O11" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1461,70 +1469,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C12" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D12" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E12" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F12" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I12" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J12" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K12" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L12" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M12" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N12" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O12" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>57.06</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1533,16 +1539,16 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
@@ -1551,57 +1557,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C13" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D13" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E13" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F13" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H13" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I13" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J13" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K13" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L13" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M13" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N13" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O13" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1619,75 +1625,73 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C14" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D14" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E14" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F14" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H14" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I14" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J14" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K14" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L14" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M14" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N14" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O14" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,18 +1709,14 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1728,79 +1728,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C15" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D15" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E15" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F15" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H15" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I15" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J15" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K15" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L15" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M15" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N15" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O15" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1808,7 +1812,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1818,210 +1822,210 @@
         <v>58.66</v>
       </c>
       <c r="D16" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E16" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H16" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J16" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K16" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L16" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M16" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N16" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O16" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F17" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J17" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K17" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L17" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M17" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N17" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O17" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O18" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -2062,83 +2066,85 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O19" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2146,61 +2152,65 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C20" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E20" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I20" t="n">
         <v>57.86</v>
       </c>
-      <c r="C20" t="n">
+      <c r="J20" t="n">
         <v>57.86</v>
       </c>
-      <c r="D20" t="n">
+      <c r="K20" t="n">
         <v>57.86</v>
       </c>
-      <c r="E20" t="n">
+      <c r="L20" t="n">
         <v>57.86</v>
       </c>
-      <c r="F20" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O20" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
@@ -2227,90 +2237,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C21" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D21" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E21" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F21" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H21" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I21" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J21" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K21" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L21" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M21" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N21" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O21" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2319,57 +2323,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C22" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D22" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E22" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H22" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I22" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J22" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K22" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L22" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M22" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N22" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O22" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2377,14 +2381,12 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2403,58 +2405,58 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C23" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D23" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E23" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H23" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I23" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J23" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K23" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L23" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N23" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O23" t="n">
         <v>57.93</v>
       </c>
-      <c r="M23" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N23" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O23" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
@@ -2464,78 +2466,80 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C24" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D24" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E24" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F24" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H24" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I24" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J24" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K24" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L24" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M24" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N24" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O24" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2556,10 +2560,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
@@ -2576,81 +2578,83 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C25" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D25" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E25" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F25" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H25" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I25" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J25" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K25" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L25" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M25" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N25" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O25" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2658,83 +2662,83 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C26" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D26" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E26" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H26" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I26" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J26" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K26" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L26" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M26" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N26" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O26" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2742,50 +2746,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C27" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D27" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E27" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F27" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H27" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I27" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J27" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K27" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L27" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M27" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N27" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O27" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2808,13 +2812,11 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2826,50 +2828,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C28" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D28" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E28" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F28" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J28" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M28" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O28" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2880,20 +2882,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2903,55 +2901,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C29" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E29" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J29" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L29" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O29" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2962,78 +2964,80 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C30" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D30" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E30" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F30" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I30" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K30" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M30" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O30" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,83 +3045,83 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J31" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K31" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L31" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N31" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,86 +3129,88 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C32" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D32" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I32" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C32" t="n">
+      <c r="J32" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D32" t="n">
+      <c r="K32" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E32" t="n">
+      <c r="L32" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F32" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J32" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K32" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L32" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M32" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q32" s="6" t="n">
         <v/>
@@ -3224,7 +3230,7 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
@@ -3242,85 +3248,83 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>65.25</v>
       </c>
       <c r="C33" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D33" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E33" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F33" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H33" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I33" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J33" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N33" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O33" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3328,134 +3332,136 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C34" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E34" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H34" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I34" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J34" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K34" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L34" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O34" t="n">
-        <v>67</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C35" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D35" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D35" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E35" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F35" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H35" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I35" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J35" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K35" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L35" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M35" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O35" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3473,14 +3479,12 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3489,59 +3493,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F36" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H36" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I36" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J36" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L36" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N36" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O36" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3578,50 +3578,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H37" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J37" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L37" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M37" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N37" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O37" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,19 +3629,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3653,55 +3653,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C38" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D38" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E38" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I38" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J38" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K38" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L38" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N38" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3711,19 +3715,23 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3735,57 +3743,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C39" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D39" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H39" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I39" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K39" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L39" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M39" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N39" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3795,23 +3803,19 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3823,57 +3827,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J40" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K40" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L40" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O40" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3881,22 +3885,24 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3905,72 +3911,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D41" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>67</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I41" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C41" t="n">
+      <c r="J41" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D41" t="n">
+      <c r="K41" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E41" t="n">
+      <c r="L41" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J41" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K41" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L41" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M41" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3980,173 +3988,169 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H42" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I42" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J42" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K42" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L42" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O42" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E43" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H43" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I43" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L43" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M43" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N43" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O43" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4168,69 +4172,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C44" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D44" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E44" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H44" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I44" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J44" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K44" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L44" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O44" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4247,55 +4245,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C45" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D45" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E45" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F45" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H45" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I45" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J45" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K45" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L45" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O45" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4306,78 +4308,80 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C46" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F46" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H46" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I46" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J46" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K46" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M46" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O46" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4385,83 +4389,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C47" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D47" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H47" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I47" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J47" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M47" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N47" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O47" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4469,14 +4473,12 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4495,57 +4497,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C48" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D48" t="n">
         <v>66.3</v>
       </c>
-      <c r="D48" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E48" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F48" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I48" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J48" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K48" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L48" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M48" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O48" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4558,109 +4560,111 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C49" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D49" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E49" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F49" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H49" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I49" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J49" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N49" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O49" t="n">
-        <v>67</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -4668,143 +4672,149 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C50" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D50" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E50" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I50" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J50" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K50" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L50" t="n">
         <v>64.28</v>
       </c>
-      <c r="F50" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I50" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J50" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K50" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L50" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M50" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N50" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O50" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C51" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D51" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E51" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F51" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H51" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J51" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K51" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L51" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M51" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N51" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O51" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4812,20 +4822,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4837,71 +4843,69 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C52" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D52" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E52" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H52" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I52" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J52" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K52" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L52" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M52" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N52" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O52" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4923,57 +4927,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C53" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E53" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H53" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I53" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J53" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K53" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L53" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M53" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N53" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O53" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4981,83 +4985,83 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C54" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D54" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E54" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F54" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H54" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J54" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K54" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L54" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M54" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5098,53 +5102,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C55" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D55" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E55" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I55" t="n">
         <v>65.47</v>
       </c>
-      <c r="C55" t="n">
+      <c r="J55" t="n">
         <v>65.47</v>
       </c>
-      <c r="D55" t="n">
+      <c r="K55" t="n">
         <v>65.47</v>
       </c>
-      <c r="E55" t="n">
+      <c r="L55" t="n">
         <v>65.47</v>
       </c>
-      <c r="F55" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J55" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K55" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L55" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M55" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N55" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O55" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q55" s="6" t="n">
         <v/>
@@ -5169,7 +5175,7 @@
       </c>
       <c r="V55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W55" s="9" t="inlineStr">
@@ -5182,85 +5188,83 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C56" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D56" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H56" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I56" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J56" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K56" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L56" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N56" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O56" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -5268,60 +5272,56 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>66.44</v>
+        <v>65.39</v>
       </c>
       <c r="C57" t="n">
-        <v>66.67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>65.81999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="E57" t="n">
-        <v>65.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.73</v>
+        <v>0.11</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0016</v>
       </c>
       <c r="H57" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="I57" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J57" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K57" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M57" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O57" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5347,61 +5347,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>65.93000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="D58" t="n">
-        <v>65.39</v>
+        <v>64.38</v>
       </c>
       <c r="E58" t="n">
-        <v>65.93000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="F58" t="n">
-        <v>0.11</v>
+        <v>-1.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0235</v>
       </c>
       <c r="H58" t="n">
-        <v>0.54</v>
+        <v>1.84</v>
       </c>
       <c r="I58" t="n">
-        <v>64.98</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>64.77</v>
+        <v>65.53</v>
       </c>
       <c r="K58" t="n">
-        <v>65.40000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="L58" t="n">
-        <v>66.03</v>
+        <v>65.8</v>
       </c>
       <c r="M58" t="n">
-        <v>66.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N58" t="n">
-        <v>66.45</v>
+        <v>66.61</v>
       </c>
       <c r="O58" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+        <v>66.47</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5410,11 +5418,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5436,75 +5446,69 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66.20999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="C59" t="n">
-        <v>66.22</v>
+        <v>63.63</v>
       </c>
       <c r="D59" t="n">
-        <v>64.38</v>
+        <v>63</v>
       </c>
       <c r="E59" t="n">
-        <v>64.38</v>
+        <v>63.46</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.55</v>
+        <v>-0.93</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0144</v>
       </c>
       <c r="H59" t="n">
-        <v>1.84</v>
+        <v>0.63</v>
       </c>
       <c r="I59" t="n">
-        <v>64.84999999999999</v>
+        <v>62.54</v>
       </c>
       <c r="J59" t="n">
-        <v>65.53</v>
+        <v>62.08</v>
       </c>
       <c r="K59" t="n">
-        <v>65.66</v>
+        <v>63.46</v>
       </c>
       <c r="L59" t="n">
-        <v>65.8</v>
+        <v>64.84</v>
       </c>
       <c r="M59" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="N59" t="n">
-        <v>66.61</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>68.06</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5517,59 +5521,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63.4</v>
+        <v>63.63</v>
       </c>
       <c r="C60" t="n">
-        <v>63.63</v>
+        <v>64.25</v>
       </c>
       <c r="D60" t="n">
-        <v>63</v>
+        <v>63.62</v>
       </c>
       <c r="E60" t="n">
-        <v>63.46</v>
+        <v>64.25</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0124</v>
       </c>
       <c r="H60" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I60" t="n">
-        <v>62.54</v>
+        <v>62.37</v>
       </c>
       <c r="J60" t="n">
-        <v>62.08</v>
+        <v>62.89</v>
       </c>
       <c r="K60" t="n">
-        <v>63.46</v>
+        <v>63.14</v>
       </c>
       <c r="L60" t="n">
-        <v>64.84</v>
+        <v>63.39</v>
       </c>
       <c r="M60" t="n">
-        <v>65.3</v>
+        <v>63.77</v>
       </c>
       <c r="N60" t="n">
-        <v>65.76000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="O60" t="n">
-        <v>68.06</v>
+        <v>64.27</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5577,28 +5577,32 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5606,83 +5610,83 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63.63</v>
+        <v>61.38</v>
       </c>
       <c r="C61" t="n">
-        <v>64.25</v>
+        <v>61.38</v>
       </c>
       <c r="D61" t="n">
-        <v>63.62</v>
+        <v>61.22</v>
       </c>
       <c r="E61" t="n">
-        <v>64.25</v>
+        <v>61.22</v>
       </c>
       <c r="F61" t="n">
-        <v>0.79</v>
+        <v>-3.03</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0471</v>
       </c>
       <c r="H61" t="n">
-        <v>0.62</v>
+        <v>0.16</v>
       </c>
       <c r="I61" t="n">
-        <v>62.37</v>
+        <v>63</v>
       </c>
       <c r="J61" t="n">
-        <v>62.89</v>
+        <v>63.78</v>
       </c>
       <c r="K61" t="n">
-        <v>63.14</v>
+        <v>63.94</v>
       </c>
       <c r="L61" t="n">
-        <v>63.39</v>
+        <v>64.09</v>
       </c>
       <c r="M61" t="n">
-        <v>63.77</v>
+        <v>64.56</v>
       </c>
       <c r="N61" t="n">
-        <v>64.16</v>
+        <v>65.02</v>
       </c>
       <c r="O61" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
+        <v>64.87</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5690,83 +5694,83 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>61.03</v>
+        <v>61.83</v>
       </c>
       <c r="C62" t="n">
-        <v>61.13</v>
+        <v>61.97</v>
       </c>
       <c r="D62" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="E62" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I62" t="n">
+        <v>61.06</v>
+      </c>
+      <c r="J62" t="n">
         <v>61.01</v>
       </c>
-      <c r="E62" t="n">
-        <v>61.12</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0486</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I62" t="n">
-        <v>63</v>
-      </c>
-      <c r="J62" t="n">
-        <v>63.78</v>
-      </c>
       <c r="K62" t="n">
-        <v>63.94</v>
+        <v>61.14</v>
       </c>
       <c r="L62" t="n">
-        <v>64.09</v>
+        <v>61.26</v>
       </c>
       <c r="M62" t="n">
-        <v>64.56</v>
+        <v>61.3</v>
       </c>
       <c r="N62" t="n">
-        <v>65.02</v>
+        <v>61.34</v>
       </c>
       <c r="O62" t="n">
-        <v>64.87</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>61.55</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,69 +634,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.62</v>
+        <v>61.21</v>
       </c>
       <c r="C2" t="n">
-        <v>62.62</v>
+        <v>61.37</v>
       </c>
       <c r="D2" t="n">
-        <v>61.63</v>
+        <v>60.21</v>
       </c>
       <c r="E2" t="n">
-        <v>61.92</v>
+        <v>60.93</v>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0211</v>
+        <v>-0.016</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="I2" t="n">
-        <v>57.33</v>
+        <v>60.65</v>
       </c>
       <c r="J2" t="n">
-        <v>58.57</v>
+        <v>60.83</v>
       </c>
       <c r="K2" t="n">
-        <v>59.58</v>
+        <v>61.43</v>
       </c>
       <c r="L2" t="n">
-        <v>60.59</v>
+        <v>62.02</v>
       </c>
       <c r="M2" t="n">
-        <v>61.71</v>
+        <v>62.41</v>
       </c>
       <c r="N2" t="n">
-        <v>62.83</v>
+        <v>62.8</v>
       </c>
       <c r="O2" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>63.6</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,64 +713,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C3" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D3" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E3" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J3" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K3" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L3" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M3" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N3" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O3" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -774,7 +782,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -788,148 +796,146 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C4" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D4" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E4" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J4" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K4" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L4" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M4" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N4" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O4" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C5" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D5" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E5" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F5" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J5" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K5" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L5" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M5" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N5" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O5" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,93 +948,95 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C6" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D6" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E6" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I6" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J6" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K6" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L6" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M6" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N6" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O6" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>60.97</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1040,249 +1048,241 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C7" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D7" t="n">
         <v>57.51</v>
       </c>
       <c r="E7" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H7" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I7" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J7" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K7" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L7" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M7" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N7" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O7" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C8" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D8" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E8" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F8" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H8" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I8" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J8" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K8" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L8" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M8" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N8" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O8" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C9" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D9" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E9" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I9" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J9" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K9" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L9" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M9" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N9" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O9" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1296,7 +1296,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1306,222 +1306,228 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C10" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D10" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E10" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H10" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J10" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K10" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L10" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M10" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N10" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O10" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C11" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D11" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E11" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I11" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J11" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K11" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L11" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M11" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N11" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O11" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C12" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D12" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E12" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F12" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H12" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J12" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K12" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L12" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M12" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N12" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O12" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1532,82 +1538,80 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W12" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C13" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D13" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E13" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F13" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H13" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I13" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J13" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K13" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L13" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M13" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N13" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O13" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1618,25 +1622,21 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1648,69 +1648,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C14" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D14" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E14" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F14" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H14" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I14" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J14" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K14" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L14" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M14" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N14" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O14" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>60.65</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1718,9 +1722,9 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1728,7 +1732,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1738,210 +1742,210 @@
         <v>58.66</v>
       </c>
       <c r="D15" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E15" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H15" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J15" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K15" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L15" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M15" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N15" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O15" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F16" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J16" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K16" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L16" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M16" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N16" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O16" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>58.66</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O17" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1958,7 +1962,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1972,7 +1976,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1982,83 +1986,85 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O18" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2066,63 +2072,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C19" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E19" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I19" t="n">
         <v>57.86</v>
       </c>
-      <c r="C19" t="n">
+      <c r="J19" t="n">
         <v>57.86</v>
       </c>
-      <c r="D19" t="n">
+      <c r="K19" t="n">
         <v>57.86</v>
       </c>
-      <c r="E19" t="n">
+      <c r="L19" t="n">
         <v>57.86</v>
       </c>
-      <c r="F19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O19" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2147,90 +2157,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C20" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D20" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E20" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F20" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H20" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I20" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J20" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K20" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L20" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M20" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N20" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O20" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2239,57 +2243,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C21" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D21" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E21" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H21" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I21" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J21" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K21" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L21" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M21" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N21" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O21" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2297,14 +2301,12 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2323,58 +2325,58 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C22" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D22" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E22" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H22" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I22" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J22" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K22" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L22" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N22" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O22" t="n">
         <v>57.93</v>
       </c>
-      <c r="M22" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N22" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O22" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
@@ -2384,78 +2386,80 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C23" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D23" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E23" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F23" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H23" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I23" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J23" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K23" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L23" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M23" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N23" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O23" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2466,7 +2470,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2476,10 +2480,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="inlineStr">
         <is>
@@ -2496,81 +2498,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C24" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D24" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E24" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F24" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H24" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I24" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J24" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K24" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L24" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M24" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N24" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O24" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>62.8</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2578,83 +2582,83 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C25" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D25" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E25" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H25" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I25" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J25" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K25" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L25" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M25" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N25" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O25" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2662,50 +2666,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C26" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D26" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E26" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F26" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H26" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I26" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J26" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K26" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L26" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M26" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N26" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O26" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2716,7 +2720,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2728,13 +2732,11 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2746,50 +2748,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C27" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D27" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E27" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F27" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J27" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M27" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O27" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2802,18 +2804,14 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2823,55 +2821,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C28" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E28" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J28" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L28" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O28" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2882,78 +2884,80 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C29" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D29" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E29" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F29" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I29" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K29" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M29" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O29" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2961,83 +2965,83 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J30" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K30" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L30" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N30" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,86 +3049,88 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C31" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I31" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C31" t="n">
+      <c r="J31" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D31" t="n">
+      <c r="K31" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E31" t="n">
+      <c r="L31" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F31" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J31" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K31" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L31" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M31" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q31" s="6" t="n">
         <v/>
@@ -3132,7 +3138,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3144,7 +3150,7 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
@@ -3162,85 +3168,83 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>65.25</v>
       </c>
       <c r="C32" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D32" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E32" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F32" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H32" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J32" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N32" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O32" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3248,134 +3252,136 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C33" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E33" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H33" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I33" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J33" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K33" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L33" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O33" t="n">
-        <v>67</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C34" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D34" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D34" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E34" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F34" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H34" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I34" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J34" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K34" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L34" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M34" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O34" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3386,21 +3392,19 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3409,59 +3413,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F35" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H35" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I35" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J35" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L35" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N35" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O35" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3472,7 +3472,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3498,50 +3498,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H36" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J36" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L36" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M36" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N36" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O36" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3549,18 +3549,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3573,55 +3573,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C37" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D37" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E37" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I37" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J37" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K37" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L37" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N37" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3631,19 +3635,23 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3655,57 +3663,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C38" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D38" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H38" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I38" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K38" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L38" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M38" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N38" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3715,23 +3723,19 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3743,57 +3747,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J39" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K39" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L39" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O39" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3801,22 +3805,24 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3825,72 +3831,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D40" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E40" t="n">
+        <v>67</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I40" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C40" t="n">
+      <c r="J40" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D40" t="n">
+      <c r="K40" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E40" t="n">
+      <c r="L40" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J40" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K40" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L40" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M40" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3900,173 +3908,169 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W40" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H41" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I41" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J41" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K41" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L41" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O41" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
+        <v>76.09</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E42" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H42" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I42" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L42" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M42" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N42" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O42" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>68.52</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4078,7 +4082,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4088,69 +4092,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C43" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D43" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E43" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H43" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I43" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J43" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K43" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L43" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O43" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>69.56</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4162,60 +4160,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C44" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D44" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E44" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F44" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <c r="H44" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="I44" t="n">
-        <v>61.03</v>
+        <v>61.67</v>
       </c>
       <c r="J44" t="n">
-        <v>61.44</v>
+        <v>63.29</v>
       </c>
       <c r="K44" t="n">
-        <v>63.2</v>
+        <v>63.88</v>
       </c>
       <c r="L44" t="n">
-        <v>64.95999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>66.04000000000001</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>67.13</v>
+        <v>66.67</v>
       </c>
       <c r="O44" t="n">
-        <v>69.56</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4226,78 +4228,80 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65.56</v>
+        <v>66.53</v>
       </c>
       <c r="C45" t="n">
-        <v>67.3</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>65.44</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>66.97</v>
+        <v>66.05</v>
       </c>
       <c r="F45" t="n">
-        <v>2.25</v>
+        <v>-0.93</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0348</v>
+        <v>-0.0138</v>
       </c>
       <c r="H45" t="n">
-        <v>1.86</v>
+        <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>61.67</v>
+        <v>63.58</v>
       </c>
       <c r="J45" t="n">
-        <v>63.29</v>
+        <v>65.41</v>
       </c>
       <c r="K45" t="n">
-        <v>63.88</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>64.45999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="M45" t="n">
-        <v>65.56999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>66.67</v>
+        <v>69.13</v>
       </c>
       <c r="O45" t="n">
-        <v>66.73999999999999</v>
+        <v>69.16</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4305,83 +4309,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66.53</v>
+        <v>65.97</v>
       </c>
       <c r="C46" t="n">
-        <v>66.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D46" t="n">
-        <v>65.45999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.93</v>
+        <v>0.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0038</v>
       </c>
       <c r="H46" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>63.58</v>
+        <v>64.39</v>
       </c>
       <c r="J46" t="n">
-        <v>65.41</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>66.04000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>66.67</v>
+        <v>66.02</v>
       </c>
       <c r="M46" t="n">
-        <v>67.90000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="N46" t="n">
-        <v>69.13</v>
+        <v>67.14</v>
       </c>
       <c r="O46" t="n">
-        <v>69.16</v>
+        <v>67.62</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4389,14 +4393,12 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4415,57 +4417,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65.97</v>
+        <v>66.3</v>
       </c>
       <c r="C47" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="D47" t="n">
         <v>66.3</v>
       </c>
-      <c r="D47" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="E47" t="n">
-        <v>66.3</v>
+        <v>67.94</v>
       </c>
       <c r="F47" t="n">
-        <v>0.25</v>
+        <v>1.65</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0248</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7</v>
+        <v>1.81</v>
       </c>
       <c r="I47" t="n">
-        <v>64.39</v>
+        <v>64.89</v>
       </c>
       <c r="J47" t="n">
-        <v>64.98999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="K47" t="n">
-        <v>65.51000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="L47" t="n">
-        <v>66.02</v>
+        <v>66.12</v>
       </c>
       <c r="M47" t="n">
-        <v>66.58</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>67.14</v>
+        <v>67.17</v>
       </c>
       <c r="O47" t="n">
-        <v>67.62</v>
+        <v>67</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4476,111 +4478,113 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+      <c r="S47" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66.3</v>
+        <v>64.19</v>
       </c>
       <c r="C48" t="n">
-        <v>68.11</v>
+        <v>64.41</v>
       </c>
       <c r="D48" t="n">
-        <v>66.3</v>
+        <v>64.14</v>
       </c>
       <c r="E48" t="n">
-        <v>67.94</v>
+        <v>64.28</v>
       </c>
       <c r="F48" t="n">
-        <v>1.65</v>
+        <v>-3.66</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0248</v>
+        <v>-0.0538</v>
       </c>
       <c r="H48" t="n">
-        <v>1.81</v>
+        <v>0.27</v>
       </c>
       <c r="I48" t="n">
-        <v>64.89</v>
+        <v>64.5</v>
       </c>
       <c r="J48" t="n">
-        <v>65.77</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>65.95</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>66.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>66.65000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="N48" t="n">
-        <v>67.17</v>
+        <v>70.12</v>
       </c>
       <c r="O48" t="n">
-        <v>67</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>69.91</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -4588,143 +4592,149 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="C49" t="n">
-        <v>64.41</v>
+        <v>64.55</v>
       </c>
       <c r="D49" t="n">
-        <v>64.14</v>
+        <v>63.1</v>
       </c>
       <c r="E49" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I49" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J49" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="K49" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="L49" t="n">
         <v>64.28</v>
       </c>
-      <c r="F49" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I49" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="K49" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="L49" t="n">
-        <v>67.56999999999999</v>
-      </c>
       <c r="M49" t="n">
-        <v>68.84</v>
+        <v>64.42</v>
       </c>
       <c r="N49" t="n">
-        <v>70.12</v>
+        <v>64.55</v>
       </c>
       <c r="O49" t="n">
-        <v>69.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63.29</v>
+        <v>63.51</v>
       </c>
       <c r="C50" t="n">
-        <v>64.55</v>
+        <v>63.7</v>
       </c>
       <c r="D50" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E50" t="n">
-        <v>64.55</v>
+        <v>63.51</v>
       </c>
       <c r="F50" t="n">
-        <v>0.27</v>
+        <v>-1.04</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0161</v>
       </c>
       <c r="H50" t="n">
-        <v>1.45</v>
+        <v>0.68</v>
       </c>
       <c r="I50" t="n">
-        <v>63.88</v>
+        <v>61.65</v>
       </c>
       <c r="J50" t="n">
-        <v>64.02</v>
+        <v>63.46</v>
       </c>
       <c r="K50" t="n">
-        <v>64.15000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="L50" t="n">
-        <v>64.28</v>
+        <v>64.19</v>
       </c>
       <c r="M50" t="n">
-        <v>64.42</v>
+        <v>65.28</v>
       </c>
       <c r="N50" t="n">
-        <v>64.55</v>
+        <v>66.37</v>
       </c>
       <c r="O50" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66.01000000000001</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4734,18 +4744,14 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4757,72 +4763,70 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63.51</v>
+        <v>63.03</v>
       </c>
       <c r="C51" t="n">
-        <v>63.7</v>
+        <v>63.64</v>
       </c>
       <c r="D51" t="n">
-        <v>63.02</v>
+        <v>63.03</v>
       </c>
       <c r="E51" t="n">
-        <v>63.51</v>
+        <v>63.24</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.04</v>
+        <v>-0.28</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0044</v>
       </c>
       <c r="H51" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="I51" t="n">
-        <v>61.65</v>
+        <v>62.34</v>
       </c>
       <c r="J51" t="n">
-        <v>63.46</v>
+        <v>62.91</v>
       </c>
       <c r="K51" t="n">
-        <v>63.83</v>
+        <v>63.17</v>
       </c>
       <c r="L51" t="n">
-        <v>64.19</v>
+        <v>63.44</v>
       </c>
       <c r="M51" t="n">
-        <v>65.28</v>
+        <v>63.85</v>
       </c>
       <c r="N51" t="n">
-        <v>66.37</v>
+        <v>64.27</v>
       </c>
       <c r="O51" t="n">
-        <v>66.01000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4843,57 +4847,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.03</v>
+        <v>64.42</v>
       </c>
       <c r="C52" t="n">
-        <v>63.64</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>63.03</v>
+        <v>63.7</v>
       </c>
       <c r="E52" t="n">
-        <v>63.24</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.28</v>
+        <v>1.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0166</v>
       </c>
       <c r="H52" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="I52" t="n">
-        <v>62.34</v>
+        <v>62.42</v>
       </c>
       <c r="J52" t="n">
-        <v>62.91</v>
+        <v>62.58</v>
       </c>
       <c r="K52" t="n">
-        <v>63.17</v>
+        <v>62.93</v>
       </c>
       <c r="L52" t="n">
-        <v>63.44</v>
+        <v>63.29</v>
       </c>
       <c r="M52" t="n">
-        <v>63.85</v>
+        <v>63.54</v>
       </c>
       <c r="N52" t="n">
-        <v>64.27</v>
+        <v>63.8</v>
       </c>
       <c r="O52" t="n">
-        <v>64.38</v>
+        <v>64.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4901,83 +4905,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64.42</v>
+        <v>65.47</v>
       </c>
       <c r="C53" t="n">
-        <v>64.54000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="D53" t="n">
-        <v>63.7</v>
+        <v>65.47</v>
       </c>
       <c r="E53" t="n">
-        <v>64.29000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="F53" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0184</v>
       </c>
       <c r="H53" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>62.42</v>
+        <v>62.86</v>
       </c>
       <c r="J53" t="n">
-        <v>62.58</v>
+        <v>63.54</v>
       </c>
       <c r="K53" t="n">
-        <v>62.93</v>
+        <v>63.87</v>
       </c>
       <c r="L53" t="n">
-        <v>63.29</v>
+        <v>64.2</v>
       </c>
       <c r="M53" t="n">
-        <v>63.54</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>63.8</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>64.25</v>
+        <v>65.37</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4988,7 +4992,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5018,53 +5022,55 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="C54" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="D54" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="E54" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I54" t="n">
         <v>65.47</v>
       </c>
-      <c r="C54" t="n">
+      <c r="J54" t="n">
         <v>65.47</v>
       </c>
-      <c r="D54" t="n">
+      <c r="K54" t="n">
         <v>65.47</v>
       </c>
-      <c r="E54" t="n">
+      <c r="L54" t="n">
         <v>65.47</v>
       </c>
-      <c r="F54" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.0184</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="J54" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="K54" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="L54" t="n">
-        <v>64.2</v>
-      </c>
       <c r="M54" t="n">
-        <v>64.70999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="N54" t="n">
-        <v>65.20999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="O54" t="n">
-        <v>65.37</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
+        <v>65.47</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q54" s="6" t="n">
         <v/>
@@ -5072,7 +5078,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5089,7 +5095,7 @@
       </c>
       <c r="V54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W54" s="9" t="inlineStr">
@@ -5102,85 +5108,83 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66.94</v>
+        <v>66.44</v>
       </c>
       <c r="C55" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D55" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>66.56</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.011</v>
       </c>
       <c r="H55" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I55" t="n">
-        <v>65.47</v>
+        <v>66.17</v>
       </c>
       <c r="J55" t="n">
-        <v>65.47</v>
+        <v>66.08</v>
       </c>
       <c r="K55" t="n">
-        <v>65.47</v>
+        <v>66.36</v>
       </c>
       <c r="L55" t="n">
-        <v>65.47</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>65.47</v>
+        <v>66.75</v>
       </c>
       <c r="N55" t="n">
-        <v>65.47</v>
+        <v>66.84</v>
       </c>
       <c r="O55" t="n">
-        <v>65.47</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5188,69 +5192,65 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.44</v>
+        <v>65.39</v>
       </c>
       <c r="C56" t="n">
-        <v>66.67</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>65.81999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="E56" t="n">
-        <v>65.81999999999999</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.73</v>
+        <v>0.11</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0016</v>
       </c>
       <c r="H56" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="I56" t="n">
-        <v>66.17</v>
+        <v>64.98</v>
       </c>
       <c r="J56" t="n">
-        <v>66.08</v>
+        <v>64.77</v>
       </c>
       <c r="K56" t="n">
-        <v>66.36</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>66.65000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="M56" t="n">
-        <v>66.75</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>66.84</v>
+        <v>66.45</v>
       </c>
       <c r="O56" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>67.51000000000001</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5262,79 +5262,89 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65.39</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>65.93000000000001</v>
+        <v>66.22</v>
       </c>
       <c r="D57" t="n">
-        <v>65.39</v>
+        <v>64.38</v>
       </c>
       <c r="E57" t="n">
-        <v>65.93000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="F57" t="n">
-        <v>0.11</v>
+        <v>-1.55</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0235</v>
       </c>
       <c r="H57" t="n">
-        <v>0.54</v>
+        <v>1.84</v>
       </c>
       <c r="I57" t="n">
-        <v>64.98</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>64.77</v>
+        <v>65.53</v>
       </c>
       <c r="K57" t="n">
-        <v>65.40000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="L57" t="n">
-        <v>66.03</v>
+        <v>65.8</v>
       </c>
       <c r="M57" t="n">
-        <v>66.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N57" t="n">
-        <v>66.45</v>
+        <v>66.61</v>
       </c>
       <c r="O57" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>66.47</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5342,7 +5352,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5356,75 +5366,69 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66.20999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="C58" t="n">
-        <v>66.22</v>
+        <v>63.63</v>
       </c>
       <c r="D58" t="n">
-        <v>64.38</v>
+        <v>63</v>
       </c>
       <c r="E58" t="n">
-        <v>64.38</v>
+        <v>63.46</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.55</v>
+        <v>-0.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0144</v>
       </c>
       <c r="H58" t="n">
-        <v>1.84</v>
+        <v>0.63</v>
       </c>
       <c r="I58" t="n">
-        <v>64.84999999999999</v>
+        <v>62.54</v>
       </c>
       <c r="J58" t="n">
-        <v>65.53</v>
+        <v>62.08</v>
       </c>
       <c r="K58" t="n">
-        <v>65.66</v>
+        <v>63.46</v>
       </c>
       <c r="L58" t="n">
-        <v>65.8</v>
+        <v>64.84</v>
       </c>
       <c r="M58" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="N58" t="n">
-        <v>66.61</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>68.06</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5432,64 +5436,60 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63.4</v>
+        <v>63.63</v>
       </c>
       <c r="C59" t="n">
-        <v>63.63</v>
+        <v>64.25</v>
       </c>
       <c r="D59" t="n">
-        <v>63</v>
+        <v>63.62</v>
       </c>
       <c r="E59" t="n">
-        <v>63.46</v>
+        <v>64.25</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0124</v>
       </c>
       <c r="H59" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I59" t="n">
-        <v>62.54</v>
+        <v>62.37</v>
       </c>
       <c r="J59" t="n">
-        <v>62.08</v>
+        <v>62.89</v>
       </c>
       <c r="K59" t="n">
-        <v>63.46</v>
+        <v>63.14</v>
       </c>
       <c r="L59" t="n">
-        <v>64.84</v>
+        <v>63.39</v>
       </c>
       <c r="M59" t="n">
-        <v>65.3</v>
+        <v>63.77</v>
       </c>
       <c r="N59" t="n">
-        <v>65.76000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="O59" t="n">
-        <v>68.06</v>
+        <v>64.27</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5497,28 +5497,32 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5526,83 +5530,83 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63.63</v>
+        <v>61.38</v>
       </c>
       <c r="C60" t="n">
-        <v>64.25</v>
+        <v>61.38</v>
       </c>
       <c r="D60" t="n">
-        <v>63.62</v>
+        <v>61.22</v>
       </c>
       <c r="E60" t="n">
-        <v>64.25</v>
+        <v>61.22</v>
       </c>
       <c r="F60" t="n">
-        <v>0.79</v>
+        <v>-3.03</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0471</v>
       </c>
       <c r="H60" t="n">
-        <v>0.62</v>
+        <v>0.16</v>
       </c>
       <c r="I60" t="n">
-        <v>62.37</v>
+        <v>63</v>
       </c>
       <c r="J60" t="n">
-        <v>62.89</v>
+        <v>63.78</v>
       </c>
       <c r="K60" t="n">
-        <v>63.14</v>
+        <v>63.94</v>
       </c>
       <c r="L60" t="n">
-        <v>63.39</v>
+        <v>64.09</v>
       </c>
       <c r="M60" t="n">
-        <v>63.77</v>
+        <v>64.56</v>
       </c>
       <c r="N60" t="n">
-        <v>64.16</v>
+        <v>65.02</v>
       </c>
       <c r="O60" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>64.87</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W60" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5610,67 +5614,67 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>61.38</v>
+        <v>60.66</v>
       </c>
       <c r="C61" t="n">
-        <v>61.38</v>
+        <v>61.2</v>
       </c>
       <c r="D61" t="n">
-        <v>61.22</v>
+        <v>60.49</v>
       </c>
       <c r="E61" t="n">
-        <v>61.22</v>
+        <v>60.67</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.03</v>
+        <v>-0.55</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0471</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>63</v>
+        <v>61.06</v>
       </c>
       <c r="J61" t="n">
-        <v>63.78</v>
+        <v>61.01</v>
       </c>
       <c r="K61" t="n">
-        <v>63.94</v>
+        <v>61.14</v>
       </c>
       <c r="L61" t="n">
-        <v>64.09</v>
+        <v>61.26</v>
       </c>
       <c r="M61" t="n">
-        <v>64.56</v>
+        <v>61.3</v>
       </c>
       <c r="N61" t="n">
-        <v>65.02</v>
+        <v>61.34</v>
       </c>
       <c r="O61" t="n">
-        <v>64.87</v>
+        <v>61.55</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5684,7 +5688,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5694,50 +5698,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>61.83</v>
+        <v>60.78</v>
       </c>
       <c r="C62" t="n">
-        <v>61.97</v>
+        <v>60.8</v>
       </c>
       <c r="D62" t="n">
-        <v>61.81</v>
+        <v>60.72</v>
       </c>
       <c r="E62" t="n">
-        <v>61.97</v>
+        <v>60.76</v>
       </c>
       <c r="F62" t="n">
-        <v>0.74</v>
+        <v>0.09</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0122</v>
+        <v>0.0014</v>
       </c>
       <c r="H62" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="I62" t="n">
-        <v>61.06</v>
+        <v>59.79</v>
       </c>
       <c r="J62" t="n">
-        <v>61.01</v>
+        <v>59.87</v>
       </c>
       <c r="K62" t="n">
-        <v>61.14</v>
+        <v>60.32</v>
       </c>
       <c r="L62" t="n">
-        <v>61.26</v>
+        <v>60.76</v>
       </c>
       <c r="M62" t="n">
-        <v>61.3</v>
+        <v>61.02</v>
       </c>
       <c r="N62" t="n">
-        <v>61.34</v>
+        <v>61.28</v>
       </c>
       <c r="O62" t="n">
-        <v>61.55</v>
+        <v>61.91</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5750,30 +5754,28 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5702,25 +5702,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>60.78</v>
+        <v>60.82</v>
       </c>
       <c r="C62" t="n">
-        <v>60.8</v>
+        <v>60.82</v>
       </c>
       <c r="D62" t="n">
-        <v>60.72</v>
+        <v>60</v>
       </c>
       <c r="E62" t="n">
-        <v>60.76</v>
+        <v>60.1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.09</v>
+        <v>-0.57</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H62" t="n">
-        <v>0.08</v>
+        <v>0.82</v>
       </c>
       <c r="I62" t="n">
         <v>59.79</v>
@@ -5749,12 +5749,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5771,11 +5773,91 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="C63" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="D63" t="n">
+        <v>61.31</v>
+      </c>
+      <c r="E63" t="n">
+        <v>61.31</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0201</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I63" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="J63" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="K63" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="L63" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="M63" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="N63" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="O63" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_daily.xlsx
+++ b/three_gate/analysis/SI_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,59 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61.21</v>
+        <v>60.9</v>
       </c>
       <c r="C2" t="n">
-        <v>61.37</v>
+        <v>60.9</v>
       </c>
       <c r="D2" t="n">
-        <v>60.21</v>
+        <v>57.76</v>
       </c>
       <c r="E2" t="n">
-        <v>60.93</v>
+        <v>58.16</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.99</v>
+        <v>-2.77</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.0454</v>
       </c>
       <c r="H2" t="n">
-        <v>1.16</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>60.65</v>
+        <v>59.04</v>
       </c>
       <c r="J2" t="n">
-        <v>60.83</v>
+        <v>59.84</v>
       </c>
       <c r="K2" t="n">
-        <v>61.43</v>
+        <v>60.35</v>
       </c>
       <c r="L2" t="n">
-        <v>62.02</v>
+        <v>60.86</v>
       </c>
       <c r="M2" t="n">
-        <v>62.41</v>
+        <v>61.51</v>
       </c>
       <c r="N2" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="O2" t="n">
-        <v>63.6</v>
+        <v>62.53</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -710,146 +710,144 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.9</v>
+        <v>59.22</v>
       </c>
       <c r="C3" t="n">
-        <v>60.9</v>
+        <v>60.5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.76</v>
+        <v>58.9</v>
       </c>
       <c r="E3" t="n">
-        <v>58.16</v>
+        <v>60.38</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.77</v>
+        <v>2.21</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0454</v>
+        <v>0.0381</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>59.04</v>
+        <v>54.61</v>
       </c>
       <c r="J3" t="n">
-        <v>59.84</v>
+        <v>54.43</v>
       </c>
       <c r="K3" t="n">
-        <v>60.35</v>
+        <v>56.59</v>
       </c>
       <c r="L3" t="n">
-        <v>60.86</v>
+        <v>58.75</v>
       </c>
       <c r="M3" t="n">
-        <v>61.51</v>
+        <v>59.74</v>
       </c>
       <c r="N3" t="n">
-        <v>62.17</v>
+        <v>60.72</v>
       </c>
       <c r="O3" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>64.05</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.22</v>
+        <v>59.98</v>
       </c>
       <c r="C4" t="n">
-        <v>60.5</v>
+        <v>60.35</v>
       </c>
       <c r="D4" t="n">
-        <v>58.9</v>
+        <v>59.72</v>
       </c>
       <c r="E4" t="n">
-        <v>60.38</v>
+        <v>59.81</v>
       </c>
       <c r="F4" t="n">
-        <v>2.21</v>
+        <v>-0.57</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0381</v>
+        <v>-0.0094</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6</v>
+        <v>0.62</v>
       </c>
       <c r="I4" t="n">
-        <v>54.61</v>
+        <v>57.3</v>
       </c>
       <c r="J4" t="n">
-        <v>54.43</v>
+        <v>59.12</v>
       </c>
       <c r="K4" t="n">
-        <v>56.59</v>
+        <v>59.58</v>
       </c>
       <c r="L4" t="n">
-        <v>58.75</v>
+        <v>60.04</v>
       </c>
       <c r="M4" t="n">
-        <v>59.74</v>
+        <v>61.18</v>
       </c>
       <c r="N4" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="O4" t="n">
-        <v>64.05</v>
+        <v>62.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,95 +858,97 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.98</v>
+        <v>58.94</v>
       </c>
       <c r="C5" t="n">
-        <v>60.35</v>
+        <v>59.04</v>
       </c>
       <c r="D5" t="n">
-        <v>59.72</v>
+        <v>57.51</v>
       </c>
       <c r="E5" t="n">
-        <v>59.81</v>
+        <v>57.63</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.57</v>
+        <v>-2.17</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>1.53</v>
       </c>
       <c r="I5" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="J5" t="n">
-        <v>59.12</v>
+        <v>59.07</v>
       </c>
       <c r="K5" t="n">
-        <v>59.58</v>
+        <v>59.5</v>
       </c>
       <c r="L5" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="M5" t="n">
-        <v>61.18</v>
+        <v>60.12</v>
       </c>
       <c r="N5" t="n">
-        <v>62.32</v>
+        <v>60.32</v>
       </c>
       <c r="O5" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>60.97</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -960,248 +960,240 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.94</v>
+        <v>57.65</v>
       </c>
       <c r="C6" t="n">
-        <v>59.04</v>
+        <v>59.6</v>
       </c>
       <c r="D6" t="n">
         <v>57.51</v>
       </c>
       <c r="E6" t="n">
-        <v>57.63</v>
+        <v>58.77</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.17</v>
+        <v>1.14</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0364</v>
+        <v>0.0197</v>
       </c>
       <c r="H6" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="I6" t="n">
-        <v>59.1</v>
+        <v>55.97</v>
       </c>
       <c r="J6" t="n">
-        <v>59.07</v>
+        <v>55.78</v>
       </c>
       <c r="K6" t="n">
-        <v>59.5</v>
+        <v>56.87</v>
       </c>
       <c r="L6" t="n">
-        <v>59.92</v>
+        <v>57.96</v>
       </c>
       <c r="M6" t="n">
-        <v>60.12</v>
+        <v>58.4</v>
       </c>
       <c r="N6" t="n">
-        <v>60.32</v>
+        <v>58.85</v>
       </c>
       <c r="O6" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>60.58</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57.65</v>
+        <v>58.69</v>
       </c>
       <c r="C7" t="n">
-        <v>59.6</v>
+        <v>58.69</v>
       </c>
       <c r="D7" t="n">
-        <v>57.51</v>
+        <v>56.9</v>
       </c>
       <c r="E7" t="n">
-        <v>58.77</v>
+        <v>57.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0197</v>
+        <v>-0.0283</v>
       </c>
       <c r="H7" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="J7" t="n">
-        <v>55.78</v>
+        <v>56.79</v>
       </c>
       <c r="K7" t="n">
-        <v>56.87</v>
+        <v>57.73</v>
       </c>
       <c r="L7" t="n">
-        <v>57.96</v>
+        <v>58.67</v>
       </c>
       <c r="M7" t="n">
-        <v>58.4</v>
+        <v>59.82</v>
       </c>
       <c r="N7" t="n">
-        <v>58.85</v>
+        <v>60.97</v>
       </c>
       <c r="O7" t="n">
-        <v>60.58</v>
+        <v>61.69</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.69</v>
+        <v>55.92</v>
       </c>
       <c r="C8" t="n">
-        <v>58.69</v>
+        <v>56.08</v>
       </c>
       <c r="D8" t="n">
-        <v>56.9</v>
+        <v>55.9</v>
       </c>
       <c r="E8" t="n">
-        <v>57.11</v>
+        <v>55.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.66</v>
+        <v>-1.21</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0283</v>
+        <v>-0.0212</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79</v>
+        <v>0.19</v>
       </c>
       <c r="I8" t="n">
-        <v>55.42</v>
+        <v>55.11</v>
       </c>
       <c r="J8" t="n">
-        <v>56.79</v>
+        <v>54.97</v>
       </c>
       <c r="K8" t="n">
-        <v>57.73</v>
+        <v>56.21</v>
       </c>
       <c r="L8" t="n">
-        <v>58.67</v>
+        <v>57.45</v>
       </c>
       <c r="M8" t="n">
-        <v>59.82</v>
+        <v>58.01</v>
       </c>
       <c r="N8" t="n">
-        <v>60.97</v>
+        <v>58.56</v>
       </c>
       <c r="O8" t="n">
-        <v>61.69</v>
+        <v>60.49</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1216,7 +1208,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1226,222 +1218,228 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55.92</v>
+        <v>55.55</v>
       </c>
       <c r="C9" t="n">
-        <v>56.08</v>
+        <v>56.04</v>
       </c>
       <c r="D9" t="n">
-        <v>55.9</v>
+        <v>55.01</v>
       </c>
       <c r="E9" t="n">
-        <v>55.9</v>
+        <v>56.04</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0212</v>
+        <v>0.0025</v>
       </c>
       <c r="H9" t="n">
-        <v>0.19</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>55.11</v>
+        <v>55.71</v>
       </c>
       <c r="J9" t="n">
-        <v>54.97</v>
+        <v>55.66</v>
       </c>
       <c r="K9" t="n">
-        <v>56.21</v>
+        <v>55.8</v>
       </c>
       <c r="L9" t="n">
-        <v>57.45</v>
+        <v>55.94</v>
       </c>
       <c r="M9" t="n">
-        <v>58.01</v>
+        <v>55.99</v>
       </c>
       <c r="N9" t="n">
-        <v>58.56</v>
+        <v>56.04</v>
       </c>
       <c r="O9" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+        <v>56.27</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.55</v>
+        <v>55.65</v>
       </c>
       <c r="C10" t="n">
-        <v>56.04</v>
+        <v>57.1</v>
       </c>
       <c r="D10" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E10" t="n">
-        <v>56.04</v>
+        <v>56.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0136</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="I10" t="n">
-        <v>55.71</v>
+        <v>53.99</v>
       </c>
       <c r="J10" t="n">
-        <v>55.66</v>
+        <v>55.27</v>
       </c>
       <c r="K10" t="n">
-        <v>55.8</v>
+        <v>55.53</v>
       </c>
       <c r="L10" t="n">
-        <v>55.94</v>
+        <v>55.78</v>
       </c>
       <c r="M10" t="n">
-        <v>55.99</v>
+        <v>56.55</v>
       </c>
       <c r="N10" t="n">
-        <v>56.04</v>
+        <v>57.32</v>
       </c>
       <c r="O10" t="n">
-        <v>56.27</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="11" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="C11" t="n">
-        <v>57.1</v>
+        <v>59.03</v>
       </c>
       <c r="D11" t="n">
-        <v>55.65</v>
+        <v>56.33</v>
       </c>
       <c r="E11" t="n">
-        <v>56.8</v>
+        <v>58.83</v>
       </c>
       <c r="F11" t="n">
-        <v>0.76</v>
+        <v>2.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0358</v>
       </c>
       <c r="H11" t="n">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="I11" t="n">
-        <v>53.99</v>
+        <v>54.2</v>
       </c>
       <c r="J11" t="n">
-        <v>55.27</v>
+        <v>55.56</v>
       </c>
       <c r="K11" t="n">
-        <v>55.53</v>
+        <v>56.08</v>
       </c>
       <c r="L11" t="n">
-        <v>55.78</v>
+        <v>56.59</v>
       </c>
       <c r="M11" t="n">
-        <v>56.55</v>
+        <v>57.53</v>
       </c>
       <c r="N11" t="n">
-        <v>57.32</v>
+        <v>58.46</v>
       </c>
       <c r="O11" t="n">
-        <v>57.06</v>
+        <v>58.56</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1452,82 +1450,80 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="C12" t="n">
-        <v>59.03</v>
+        <v>60.02</v>
       </c>
       <c r="D12" t="n">
-        <v>56.33</v>
+        <v>59.38</v>
       </c>
       <c r="E12" t="n">
-        <v>58.83</v>
+        <v>60.02</v>
       </c>
       <c r="F12" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0358</v>
+        <v>0.0201</v>
       </c>
       <c r="H12" t="n">
-        <v>2.69</v>
+        <v>0.63</v>
       </c>
       <c r="I12" t="n">
-        <v>54.2</v>
+        <v>53.64</v>
       </c>
       <c r="J12" t="n">
-        <v>55.56</v>
+        <v>56.72</v>
       </c>
       <c r="K12" t="n">
-        <v>56.08</v>
+        <v>57.49</v>
       </c>
       <c r="L12" t="n">
-        <v>56.59</v>
+        <v>58.26</v>
       </c>
       <c r="M12" t="n">
-        <v>57.53</v>
+        <v>60.18</v>
       </c>
       <c r="N12" t="n">
-        <v>58.46</v>
+        <v>62.1</v>
       </c>
       <c r="O12" t="n">
-        <v>58.56</v>
+        <v>61.72</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1538,27 +1534,23 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1568,70 +1560,74 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59.38</v>
+        <v>58.66</v>
       </c>
       <c r="C13" t="n">
-        <v>60.02</v>
+        <v>58.66</v>
       </c>
       <c r="D13" t="n">
-        <v>59.38</v>
+        <v>57.8</v>
       </c>
       <c r="E13" t="n">
-        <v>60.02</v>
+        <v>57.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1.18</v>
+        <v>-2.22</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0201</v>
+        <v>-0.037</v>
       </c>
       <c r="H13" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="I13" t="n">
-        <v>53.64</v>
+        <v>58.75</v>
       </c>
       <c r="J13" t="n">
-        <v>56.72</v>
+        <v>59.54</v>
       </c>
       <c r="K13" t="n">
-        <v>57.49</v>
+        <v>59.7</v>
       </c>
       <c r="L13" t="n">
-        <v>58.26</v>
+        <v>59.86</v>
       </c>
       <c r="M13" t="n">
-        <v>60.18</v>
+        <v>60.34</v>
       </c>
       <c r="N13" t="n">
-        <v>62.1</v>
+        <v>60.81</v>
       </c>
       <c r="O13" t="n">
-        <v>61.72</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+        <v>60.65</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1640,7 +1636,7 @@
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1648,7 +1644,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1658,210 +1654,210 @@
         <v>58.66</v>
       </c>
       <c r="D14" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="E14" t="n">
-        <v>57.8</v>
+        <v>58.66</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.22</v>
+        <v>0.86</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.037</v>
+        <v>0.0148</v>
       </c>
       <c r="H14" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>58.75</v>
+        <v>56.94</v>
       </c>
       <c r="J14" t="n">
-        <v>59.54</v>
+        <v>56.72</v>
       </c>
       <c r="K14" t="n">
-        <v>59.7</v>
+        <v>57.37</v>
       </c>
       <c r="L14" t="n">
-        <v>59.86</v>
+        <v>58.01</v>
       </c>
       <c r="M14" t="n">
-        <v>60.34</v>
+        <v>58.23</v>
       </c>
       <c r="N14" t="n">
-        <v>60.81</v>
+        <v>58.44</v>
       </c>
       <c r="O14" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="C15" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="D15" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="E15" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="F15" t="n">
-        <v>0.86</v>
+        <v>-0.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0148</v>
+        <v>-0.0031</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>56.94</v>
+        <v>58.66</v>
       </c>
       <c r="J15" t="n">
-        <v>56.72</v>
+        <v>58.66</v>
       </c>
       <c r="K15" t="n">
-        <v>57.37</v>
+        <v>58.66</v>
       </c>
       <c r="L15" t="n">
-        <v>58.01</v>
+        <v>58.66</v>
       </c>
       <c r="M15" t="n">
-        <v>58.23</v>
+        <v>58.66</v>
       </c>
       <c r="N15" t="n">
-        <v>58.44</v>
+        <v>58.66</v>
       </c>
       <c r="O15" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+        <v>58.66</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="C16" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="D16" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="E16" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.18</v>
+        <v>-1.18</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0201</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="J16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="K16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="L16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="M16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="N16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="O16" t="n">
-        <v>58.66</v>
+        <v>58.47</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1888,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1902,83 +1898,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="C17" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="D17" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="E17" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.18</v>
+        <v>0.57</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0201</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="J17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="K17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="L17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="M17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="N17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="O17" t="n">
-        <v>58.47</v>
+        <v>57.3</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1986,63 +1984,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="C18" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I18" t="n">
         <v>57.86</v>
       </c>
-      <c r="C18" t="n">
+      <c r="J18" t="n">
         <v>57.86</v>
       </c>
-      <c r="D18" t="n">
+      <c r="K18" t="n">
         <v>57.86</v>
       </c>
-      <c r="E18" t="n">
+      <c r="L18" t="n">
         <v>57.86</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>57.3</v>
-      </c>
       <c r="M18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="N18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="O18" t="n">
-        <v>57.3</v>
+        <v>57.86</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2062,154 +2064,148 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.28</v>
+        <v>59.2</v>
       </c>
       <c r="C19" t="n">
-        <v>59.25</v>
+        <v>59.2</v>
       </c>
       <c r="D19" t="n">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
       <c r="E19" t="n">
-        <v>58.81</v>
+        <v>57.59</v>
       </c>
       <c r="F19" t="n">
-        <v>0.95</v>
+        <v>-1.22</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.0208</v>
       </c>
       <c r="H19" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="I19" t="n">
-        <v>57.86</v>
+        <v>55.2</v>
       </c>
       <c r="J19" t="n">
-        <v>57.86</v>
+        <v>57.08</v>
       </c>
       <c r="K19" t="n">
-        <v>57.86</v>
+        <v>57.8</v>
       </c>
       <c r="L19" t="n">
-        <v>57.86</v>
+        <v>58.53</v>
       </c>
       <c r="M19" t="n">
-        <v>57.86</v>
+        <v>59.83</v>
       </c>
       <c r="N19" t="n">
-        <v>57.86</v>
+        <v>61.13</v>
       </c>
       <c r="O19" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>61.28</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59.2</v>
+        <v>57.67</v>
       </c>
       <c r="C20" t="n">
-        <v>59.2</v>
+        <v>57.8</v>
       </c>
       <c r="D20" t="n">
-        <v>57.34</v>
+        <v>57.67</v>
       </c>
       <c r="E20" t="n">
-        <v>57.59</v>
+        <v>57.67</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.22</v>
+        <v>0.08</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0013</v>
       </c>
       <c r="H20" t="n">
-        <v>1.86</v>
+        <v>0.13</v>
       </c>
       <c r="I20" t="n">
-        <v>55.2</v>
+        <v>55.48</v>
       </c>
       <c r="J20" t="n">
-        <v>57.08</v>
+        <v>55.39</v>
       </c>
       <c r="K20" t="n">
-        <v>57.8</v>
+        <v>56.66</v>
       </c>
       <c r="L20" t="n">
-        <v>58.53</v>
+        <v>57.93</v>
       </c>
       <c r="M20" t="n">
-        <v>59.83</v>
+        <v>58.52</v>
       </c>
       <c r="N20" t="n">
-        <v>61.13</v>
+        <v>59.11</v>
       </c>
       <c r="O20" t="n">
-        <v>61.28</v>
+        <v>61.06</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2217,14 +2213,12 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2236,65 +2230,65 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="C21" t="n">
-        <v>57.8</v>
+        <v>60.06</v>
       </c>
       <c r="D21" t="n">
-        <v>57.67</v>
+        <v>58.1</v>
       </c>
       <c r="E21" t="n">
-        <v>57.67</v>
+        <v>60.06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0414</v>
       </c>
       <c r="H21" t="n">
-        <v>0.13</v>
+        <v>1.96</v>
       </c>
       <c r="I21" t="n">
-        <v>55.48</v>
+        <v>57.53</v>
       </c>
       <c r="J21" t="n">
-        <v>55.39</v>
+        <v>57.5</v>
       </c>
       <c r="K21" t="n">
-        <v>56.66</v>
+        <v>57.6</v>
       </c>
       <c r="L21" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="N21" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="O21" t="n">
         <v>57.93</v>
       </c>
-      <c r="M21" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="N21" t="n">
-        <v>59.11</v>
-      </c>
-      <c r="O21" t="n">
-        <v>61.06</v>
-      </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
@@ -2304,78 +2298,80 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58.1</v>
+        <v>62.45</v>
       </c>
       <c r="C22" t="n">
-        <v>60.06</v>
+        <v>62.45</v>
       </c>
       <c r="D22" t="n">
-        <v>58.1</v>
+        <v>62.1</v>
       </c>
       <c r="E22" t="n">
-        <v>60.06</v>
+        <v>62.1</v>
       </c>
       <c r="F22" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0414</v>
+        <v>0.034</v>
       </c>
       <c r="H22" t="n">
-        <v>1.96</v>
+        <v>0.35</v>
       </c>
       <c r="I22" t="n">
-        <v>57.53</v>
+        <v>56.14</v>
       </c>
       <c r="J22" t="n">
-        <v>57.5</v>
+        <v>58.59</v>
       </c>
       <c r="K22" t="n">
-        <v>57.6</v>
+        <v>59.08</v>
       </c>
       <c r="L22" t="n">
-        <v>57.7</v>
+        <v>59.57</v>
       </c>
       <c r="M22" t="n">
-        <v>57.73</v>
+        <v>61.03</v>
       </c>
       <c r="N22" t="n">
-        <v>57.77</v>
+        <v>62.5</v>
       </c>
       <c r="O22" t="n">
-        <v>57.93</v>
+        <v>62.01</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2386,7 +2382,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="11" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2396,17 +2392,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2416,81 +2410,83 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="C23" t="n">
-        <v>62.45</v>
+        <v>61.91</v>
       </c>
       <c r="D23" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="E23" t="n">
-        <v>62.1</v>
+        <v>61.44</v>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>-0.66</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.034</v>
+        <v>-0.0106</v>
       </c>
       <c r="H23" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I23" t="n">
-        <v>56.14</v>
+        <v>61.75</v>
       </c>
       <c r="J23" t="n">
-        <v>58.59</v>
+        <v>61.66</v>
       </c>
       <c r="K23" t="n">
-        <v>59.08</v>
+        <v>61.92</v>
       </c>
       <c r="L23" t="n">
-        <v>59.57</v>
+        <v>62.19</v>
       </c>
       <c r="M23" t="n">
-        <v>61.03</v>
+        <v>62.27</v>
       </c>
       <c r="N23" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="O23" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>62.8</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2498,83 +2494,83 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>61.91</v>
+        <v>63.62</v>
       </c>
       <c r="C24" t="n">
-        <v>61.91</v>
+        <v>65.05</v>
       </c>
       <c r="D24" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="E24" t="n">
-        <v>61.44</v>
+        <v>63.33</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.66</v>
+        <v>1.89</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0308</v>
       </c>
       <c r="H24" t="n">
-        <v>0.47</v>
+        <v>1.72</v>
       </c>
       <c r="I24" t="n">
-        <v>61.75</v>
+        <v>60.97</v>
       </c>
       <c r="J24" t="n">
-        <v>61.66</v>
+        <v>60.85</v>
       </c>
       <c r="K24" t="n">
-        <v>61.92</v>
+        <v>61.2</v>
       </c>
       <c r="L24" t="n">
-        <v>62.19</v>
+        <v>61.56</v>
       </c>
       <c r="M24" t="n">
-        <v>62.27</v>
+        <v>61.67</v>
       </c>
       <c r="N24" t="n">
-        <v>62.36</v>
+        <v>61.79</v>
       </c>
       <c r="O24" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
+        <v>62.38</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2582,50 +2578,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63.62</v>
+        <v>63.9</v>
       </c>
       <c r="C25" t="n">
-        <v>65.05</v>
+        <v>65.11</v>
       </c>
       <c r="D25" t="n">
-        <v>63.33</v>
+        <v>63.9</v>
       </c>
       <c r="E25" t="n">
-        <v>63.33</v>
+        <v>65.11</v>
       </c>
       <c r="F25" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.028</v>
       </c>
       <c r="H25" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="I25" t="n">
-        <v>60.97</v>
+        <v>61.61</v>
       </c>
       <c r="J25" t="n">
-        <v>60.85</v>
+        <v>61.18</v>
       </c>
       <c r="K25" t="n">
-        <v>61.2</v>
+        <v>62.47</v>
       </c>
       <c r="L25" t="n">
-        <v>61.56</v>
+        <v>63.76</v>
       </c>
       <c r="M25" t="n">
-        <v>61.67</v>
+        <v>64.19</v>
       </c>
       <c r="N25" t="n">
-        <v>61.79</v>
+        <v>64.62</v>
       </c>
       <c r="O25" t="n">
-        <v>62.38</v>
+        <v>66.77</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2636,7 +2632,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="11" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2648,15 +2644,13 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2666,50 +2660,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63.9</v>
+        <v>64.86</v>
       </c>
       <c r="C26" t="n">
-        <v>65.11</v>
+        <v>64.86</v>
       </c>
       <c r="D26" t="n">
-        <v>63.9</v>
+        <v>64.77</v>
       </c>
       <c r="E26" t="n">
-        <v>65.11</v>
+        <v>64.77</v>
       </c>
       <c r="F26" t="n">
-        <v>1.77</v>
+        <v>-0.34</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.028</v>
+        <v>-0.0052</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>61.61</v>
+        <v>62.7</v>
       </c>
       <c r="J26" t="n">
-        <v>61.18</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>62.47</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>63.76</v>
+        <v>64.81</v>
       </c>
       <c r="M26" t="n">
-        <v>64.19</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>64.62</v>
+        <v>66.61</v>
       </c>
       <c r="O26" t="n">
-        <v>66.77</v>
+        <v>66.31</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2720,78 +2714,78 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.86</v>
+        <v>66.62</v>
       </c>
       <c r="C27" t="n">
-        <v>64.86</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="E27" t="n">
-        <v>64.77</v>
+        <v>65.56</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.34</v>
+        <v>0.79</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0121</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I27" t="n">
-        <v>62.7</v>
+        <v>64.67</v>
       </c>
       <c r="J27" t="n">
-        <v>64.20999999999999</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>64.51000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="L27" t="n">
-        <v>64.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>65.70999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>66.61</v>
+        <v>64.84</v>
       </c>
       <c r="O27" t="n">
-        <v>66.31</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2802,78 +2796,80 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66.62</v>
+        <v>64.87</v>
       </c>
       <c r="C28" t="n">
-        <v>66.65000000000001</v>
+        <v>64.87</v>
       </c>
       <c r="D28" t="n">
-        <v>65.56</v>
+        <v>64.78</v>
       </c>
       <c r="E28" t="n">
-        <v>65.56</v>
+        <v>64.87</v>
       </c>
       <c r="F28" t="n">
-        <v>0.79</v>
+        <v>-0.68</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0104</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1</v>
+        <v>0.09</v>
       </c>
       <c r="I28" t="n">
-        <v>64.67</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>64.65000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="K28" t="n">
-        <v>64.72</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>64.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="M28" t="n">
-        <v>64.81999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>64.84</v>
+        <v>66.38</v>
       </c>
       <c r="O28" t="n">
-        <v>64.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2881,83 +2877,83 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>64.78</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>64.87</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0018</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>64.45999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="J29" t="n">
-        <v>64.19</v>
+        <v>64.8</v>
       </c>
       <c r="K29" t="n">
-        <v>65.01000000000001</v>
+        <v>64.83</v>
       </c>
       <c r="L29" t="n">
-        <v>65.83</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>66.09999999999999</v>
+        <v>64.92</v>
       </c>
       <c r="N29" t="n">
-        <v>66.38</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>67.75</v>
+        <v>64.97</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2965,86 +2961,88 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C30" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I30" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C30" t="n">
+      <c r="J30" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="D30" t="n">
+      <c r="K30" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E30" t="n">
+      <c r="L30" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="J30" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>64.83</v>
-      </c>
-      <c r="L30" t="n">
-        <v>64.84999999999999</v>
-      </c>
       <c r="M30" t="n">
-        <v>64.92</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>64.98999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q30" s="6" t="n">
         <v/>
@@ -3052,7 +3050,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3064,7 +3062,7 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V30" s="8" t="inlineStr">
@@ -3072,7 +3070,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3082,85 +3080,83 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>65.25</v>
       </c>
       <c r="C31" t="n">
-        <v>66.12</v>
+        <v>65.25</v>
       </c>
       <c r="D31" t="n">
-        <v>65.25</v>
+        <v>63.6</v>
       </c>
       <c r="E31" t="n">
-        <v>66.12</v>
+        <v>63.94</v>
       </c>
       <c r="F31" t="n">
-        <v>1.13</v>
+        <v>-2.18</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.033</v>
       </c>
       <c r="H31" t="n">
-        <v>0.88</v>
+        <v>1.65</v>
       </c>
       <c r="I31" t="n">
-        <v>64.98999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="J31" t="n">
-        <v>64.98999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>64.98999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>64.98999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>64.98999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="N31" t="n">
-        <v>64.98999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="O31" t="n">
-        <v>64.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3168,134 +3164,136 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65.25</v>
+        <v>63.21</v>
       </c>
       <c r="C32" t="n">
-        <v>65.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>63.6</v>
+        <v>63.12</v>
       </c>
       <c r="E32" t="n">
-        <v>63.94</v>
+        <v>65.73</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.033</v>
+        <v>0.028</v>
       </c>
       <c r="H32" t="n">
-        <v>1.65</v>
+        <v>3.73</v>
       </c>
       <c r="I32" t="n">
-        <v>64.37</v>
+        <v>61.96</v>
       </c>
       <c r="J32" t="n">
-        <v>65.45999999999999</v>
+        <v>62.05</v>
       </c>
       <c r="K32" t="n">
-        <v>65.68000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="L32" t="n">
-        <v>65.90000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>66.56</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>67.22</v>
+        <v>65.34</v>
       </c>
       <c r="O32" t="n">
-        <v>67</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="C33" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="D33" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="D33" t="n">
-        <v>63.12</v>
-      </c>
       <c r="E33" t="n">
-        <v>65.73</v>
+        <v>68.03</v>
       </c>
       <c r="F33" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0349</v>
       </c>
       <c r="H33" t="n">
-        <v>3.73</v>
+        <v>2.1</v>
       </c>
       <c r="I33" t="n">
-        <v>61.96</v>
+        <v>59.39</v>
       </c>
       <c r="J33" t="n">
-        <v>62.05</v>
+        <v>62.38</v>
       </c>
       <c r="K33" t="n">
-        <v>63.12</v>
+        <v>63.87</v>
       </c>
       <c r="L33" t="n">
-        <v>64.18000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="M33" t="n">
-        <v>64.76000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>65.34</v>
+        <v>69.84</v>
       </c>
       <c r="O33" t="n">
-        <v>66.90000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3306,82 +3304,76 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>68.95</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>66.84999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>68.03</v>
+        <v>69.47</v>
       </c>
       <c r="F34" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0212</v>
       </c>
       <c r="H34" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="I34" t="n">
-        <v>59.39</v>
+        <v>64.75</v>
       </c>
       <c r="J34" t="n">
-        <v>62.38</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>63.87</v>
+        <v>66.98</v>
       </c>
       <c r="L34" t="n">
-        <v>65.36</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>67.59999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N34" t="n">
-        <v>69.84</v>
+        <v>70.19</v>
       </c>
       <c r="O34" t="n">
-        <v>70.58</v>
+        <v>71.05</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3392,7 +3384,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="11" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3408,7 +3400,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3418,50 +3410,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68.09999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>69.84999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>68.09999999999999</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>69.47</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>1.44</v>
+        <v>-0.93</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0133</v>
       </c>
       <c r="H35" t="n">
-        <v>1.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>64.75</v>
+        <v>66.34</v>
       </c>
       <c r="J35" t="n">
-        <v>65.98999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>66.98</v>
+        <v>68.59</v>
       </c>
       <c r="L35" t="n">
-        <v>67.95999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="M35" t="n">
-        <v>69.08</v>
+        <v>70.34</v>
       </c>
       <c r="N35" t="n">
-        <v>70.19</v>
+        <v>71.47</v>
       </c>
       <c r="O35" t="n">
-        <v>71.05</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3469,79 +3461,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C36" t="n">
-        <v>69.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="D36" t="n">
-        <v>68.54000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="E36" t="n">
-        <v>68.54000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.93</v>
+        <v>0.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0133</v>
+        <v>0.0014</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="I36" t="n">
-        <v>66.34</v>
+        <v>67.73</v>
       </c>
       <c r="J36" t="n">
-        <v>67.95999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="K36" t="n">
-        <v>68.59</v>
+        <v>68.14</v>
       </c>
       <c r="L36" t="n">
-        <v>69.22</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>70.34</v>
+        <v>68.95</v>
       </c>
       <c r="N36" t="n">
-        <v>71.47</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>71.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3551,81 +3547,85 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="C37" t="n">
-        <v>69.5</v>
+        <v>69.31</v>
       </c>
       <c r="D37" t="n">
-        <v>68.12</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>68.64</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0094</v>
       </c>
       <c r="H37" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>67.73</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>67.53</v>
+        <v>67.16</v>
       </c>
       <c r="K37" t="n">
-        <v>68.14</v>
+        <v>67.94</v>
       </c>
       <c r="L37" t="n">
-        <v>68.73999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="M37" t="n">
-        <v>68.95</v>
+        <v>69.33</v>
       </c>
       <c r="N37" t="n">
-        <v>69.15000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>70.16</v>
+        <v>70.89</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3635,85 +3635,81 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>69.31</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>67.98999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.65</v>
+        <v>1.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0212</v>
       </c>
       <c r="H38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>66.73999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="J38" t="n">
-        <v>67.16</v>
+        <v>66.34</v>
       </c>
       <c r="K38" t="n">
-        <v>67.94</v>
+        <v>67.33</v>
       </c>
       <c r="L38" t="n">
-        <v>68.72</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>69.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>69.93000000000001</v>
+        <v>68.98</v>
       </c>
       <c r="O38" t="n">
-        <v>70.89</v>
+        <v>70.63</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3721,96 +3717,100 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="C39" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="D39" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="E39" t="n">
+        <v>67</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I39" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="C39" t="n">
+      <c r="J39" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="D39" t="n">
+      <c r="K39" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="E39" t="n">
+      <c r="L39" t="n">
         <v>69.43000000000001</v>
       </c>
-      <c r="F39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="J39" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="K39" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L39" t="n">
-        <v>68.31999999999999</v>
-      </c>
       <c r="M39" t="n">
-        <v>68.65000000000001</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>68.98</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>69.43000000000001</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3820,173 +3820,169 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>71.16</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>66.23</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>67</v>
+        <v>66.22</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.43</v>
+        <v>-0.77</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0351</v>
+        <v>-0.0116</v>
       </c>
       <c r="H40" t="n">
-        <v>4.93</v>
+        <v>1.33</v>
       </c>
       <c r="I40" t="n">
-        <v>69.43000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="J40" t="n">
-        <v>69.43000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="K40" t="n">
-        <v>69.43000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="L40" t="n">
-        <v>69.43000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>69.43000000000001</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>69.43000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="O40" t="n">
-        <v>69.43000000000001</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>76.09</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W40" s="10" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66.01000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>67.18000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>65.84999999999999</v>
+        <v>63.87</v>
       </c>
       <c r="E41" t="n">
-        <v>66.22</v>
+        <v>64.62</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.77</v>
+        <v>-1.6</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0242</v>
       </c>
       <c r="H41" t="n">
-        <v>1.33</v>
+        <v>2.84</v>
       </c>
       <c r="I41" t="n">
-        <v>61.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>61.22</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>64.53</v>
+        <v>65.55</v>
       </c>
       <c r="L41" t="n">
-        <v>67.84999999999999</v>
+        <v>66.37</v>
       </c>
       <c r="M41" t="n">
-        <v>69.45999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="N41" t="n">
-        <v>71.08</v>
+        <v>67.41</v>
       </c>
       <c r="O41" t="n">
-        <v>76.09</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>68.52</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3998,7 +3994,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="10" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4008,69 +4004,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66.51000000000001</v>
+        <v>63.36</v>
       </c>
       <c r="C42" t="n">
-        <v>66.70999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="D42" t="n">
-        <v>63.87</v>
+        <v>63.36</v>
       </c>
       <c r="E42" t="n">
-        <v>64.62</v>
+        <v>64.72</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.6</v>
+        <v>0.11</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0016</v>
       </c>
       <c r="H42" t="n">
-        <v>2.84</v>
+        <v>1.69</v>
       </c>
       <c r="I42" t="n">
-        <v>64.51000000000001</v>
+        <v>61.03</v>
       </c>
       <c r="J42" t="n">
-        <v>64.73999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="K42" t="n">
-        <v>65.55</v>
+        <v>63.2</v>
       </c>
       <c r="L42" t="n">
-        <v>66.37</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>66.89</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>67.41</v>
+        <v>67.13</v>
       </c>
       <c r="O42" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>69.56</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4082,60 +4072,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="10" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>63.36</v>
+        <v>65.56</v>
       </c>
       <c r="C43" t="n">
-        <v>65.05</v>
+        <v>67.3</v>
       </c>
       <c r="D43" t="n">
-        <v>63.36</v>
+        <v>65.44</v>
       </c>
       <c r="E43" t="n">
-        <v>64.72</v>
+        <v>66.97</v>
       </c>
       <c r="F43" t="n">
-        <v>0.11</v>
+        <v>2.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0348</v>
       </c>
       <